--- a/menu_database.xlsx
+++ b/menu_database.xlsx
@@ -5,9 +5,6 @@
   <sheets>
     <sheet name="酒單配方" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'酒單配方'!$A$1:$J$166</definedName>
-  </definedNames>
 </workbook>
 </file>
 
@@ -400,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J166"/>
+  <dimension ref="A1:J168"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -463,7 +460,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>起源於1920年代英國薩伏依飯店的經典配方，以「一號/頂級」命名，象徵極致純粹的卓越風味。</v>
+        <v>起源於1920年代英國倫敦薩伏依飯店（Savoy Hotel），收錄於傳奇調酒師Harry Craddock的經典酒譜中。以象徵極致卓越的「A1/頂級」命名，將琴酒的杜松子芳香與格蘭瑪尼耶柑橘干邑、干苦艾酒與新鮮檸檬汁完美揉合。酒體俐落優雅，酸甜明亮中帶著深邃的柑橘木質尾韻，堪稱爵士年代的英倫紳士之選。</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +492,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>以美國波音B-52長程轟炸機命名，利用利口酒的比重差異分層，完美展現燃燒的視覺震撼。</v>
+        <v>誕生於1970年代加拿大亞伯達省，以冷戰時期著名的美國波音B-52長程同溫層轟炸機命名。利用咖啡香甜酒、愛爾蘭奶酒與柑橘干邑的密度差異在杯中完美分層，點火燃燒時藍焰跳躍、視覺張力十足。用吸管一口乾盡，自喉頭湧入冰涼甜潤的奶香與咖啡香，隨後迎來烈焰溫熱的爆發力，層次極具戲劇感。</v>
       </c>
     </row>
     <row r="4">
@@ -527,7 +524,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>結合法國班尼迪克丁D.O.M藥草酒與干邑白蘭地，起源於紐約21俱樂部，口感厚實、藥草香氣濃郁。</v>
+        <v>發源於1930年代紐約傳奇名流匯聚的「21俱樂部」（21 Club）。將歷史悠久的法國班尼迪克丁（Bénédictine D.O.M）本篤會藥草密酒與干邑白蘭地（Brandy）等比例調和。白蘭地的醇厚木質果香，巧妙降伏了二十七種草本香料的濃稠甜膩，尾韻溫潤深沉，是跨越世紀的殿堂級餐後消化酒。</v>
       </c>
     </row>
     <row r="5">
@@ -547,19 +544,19 @@
         <v>琴酒, 有氣泡, 經典</v>
       </c>
       <c r="F5" t="str">
-        <v>Gordon's Gin 60 ml, Whipped Cream 30 ml, Lime Juice 15 ml, Lemon Juice 15 ml, Simple Syrup 30 ml, Lemonade Soda 90 ml</v>
+        <v>琴酒 60 ml, 鮮奶油 30 ml, 檸檬汁 15 ml, 萊姆汁 15 ml, 純糖漿 30 ml, 橙花水 3~4 drops, 蛋白 1 顆, 蘇打水適量,, 柳橙皮捲</v>
       </c>
       <c r="G5" t="str">
-        <v>用手搖12分鐘…</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v>冰鎮長飲杯</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J5" t="str">
-        <v>1888年由Henry Ramos在新奧爾良發明，以極其繁複的長時搖盪（傳統上需搖12分鐘）打造出如舒芙蕾般綿密的完美泡沫。</v>
+        <v>1888年由Henry C. Ramos在紐奧良帝國酒吧創作。傳統上需要調酒師連續劇烈搖盪長達12至15分鐘，將琴酒、柑橘花水、蛋白與鮮奶油徹底乳化，注入蘇打水時宛如烘烤舒芙蕾般緩緩升起堅挺的綿密泡沫。口感如絲綢雲朵般細膩輕盈，伴隨清雅的橙花花香，被譽為調酒師一生必須挑戰的終極體能之作。</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +588,7 @@
         <v>建議物</v>
       </c>
       <c r="J6" t="str">
-        <v>以英文字母最後三個字命名，象徵「最後的、極致的」調酒，是白佳人與側車的蘭姆酒變奏版。</v>
+        <v>以英文字母的最後三個字母命名，隱含著「喝完此杯，今夜再無他選」或「極致終曲」的浪漫深意。作為白色佳人與側車的蘭姆酒版本，以醇厚白蘭姆酒為基底，結合君度橙酒的清香與新鮮檸檬汁的明亮酸爽。口感乾淨俐落、酸甜平衡，在唇齒間留下純粹爽朗的柑橘微光。</v>
       </c>
     </row>
     <row r="7">
@@ -623,7 +620,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>象徵琴酒、苦艾酒與利口酒三位一體的完美融合，具有極佳的草本平衡感。</v>
+        <v>起源於20世紀初的歐洲沙龍，象徵琴酒、干苦艾酒與甜苦艾酒「三位一體」的黃金融合。杜松子的草本芬芳與兩種苦艾酒的草本微苦、香草微甜達成精妙的和諧。酒體清澈金黃，入口乾冽中帶著溫潤回甘，宛如在舌尖演繹一場嚴謹而神聖的三重奏。</v>
       </c>
     </row>
     <row r="8">
@@ -655,7 +652,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>起源於費城同名紳士俱樂部，早於禁酒令時期便風靡一時，覆盆子與蛋白帶來漂亮的粉紅色澤與絲滑口感。</v>
+        <v>發源於1896年美國費城貝爾維尤斯特拉福飯店，是當時政商名流與文人齊聚的「三葉草俱樂部」招牌飲品。在禁酒令前夕便風靡全美，以琴酒為底，加入新鮮覆盆子糖漿、檸檬汁與蛋白充分搖盪。酒液呈現嬌豔優雅的淡粉紅色，頂部浮著細緻天鵝絨泡沫，酸甜果香與杜松子草本在舌尖溫柔交織。</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +684,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>由不列顛調酒師C.A. Tuck於1937年創作，向當時著名的「20世紀特快列車」豪華鐵路致敬。</v>
+        <v>由英國調酒師C. A. Tuck於1937年創作，向當時連結紐約與芝加哥、被譽為「世界最著名列車」的20世紀特快豪華列車（20th Century Limited）致敬。大膽在琴酒、白可可香甜酒與檸檬汁中加入麗葉開胃酒（Lillet Blanc），看似透明純淨，入口卻在柑橘果酸中意外綻放出可可的溫潤甜香，風格前衛且迷人。</v>
       </c>
     </row>
     <row r="10">
@@ -719,7 +716,7 @@
         <v>建議物</v>
       </c>
       <c r="J10" t="str">
-        <v>起源於20世紀初，據傳是為了慶祝虛構的白衣卡通人物或特定社交名媛而調製的絲滑全天候調酒。</v>
+        <v>誕生於20世紀初紐約，相傳是為了慶祝知名白衣卡通廣告人物或社交名媛而創。以琴酒、深色可可酒與新鮮鮮奶油等比例搖盪，灑上現磨肉荳蔻粉。入口如絲絨般柔滑醇厚，杜松子草本隱隱點綴在濃郁巧克力奶香之中，是甜點系調酒的開山鼻祖。</v>
       </c>
     </row>
     <row r="11">
@@ -751,7 +748,7 @@
         <v>建議物</v>
       </c>
       <c r="J11" t="str">
-        <v>經典的「解酒/還魂酒」，出自1930年《Savoy Cocktail Book》，著名語錄提到「連喝四杯能讓死人復活」。</v>
+        <v>1930年收錄於《薩伏依雞尾酒手冊》（The Savoy Cocktail Book）的傳奇還魂解酒方。調酒大師Harry Craddock曾留下一句名言：「連喝四杯，足以讓死人復甦；但若再喝一杯，死人將再度長眠」。琴酒、麗葉酒、橙酒與檸檬汁等比例混合，並以苦艾酒涮杯，風味明亮酸爽，如晨光般瞬間喚醒沉睡的心靈。</v>
       </c>
     </row>
     <row r="12">
@@ -783,7 +780,7 @@
         <v>建議物</v>
       </c>
       <c r="J12" t="str">
-        <v>以美國南方鳥類仿聲鳥命名，薄荷的翠綠色澤與綠色龍舌蘭完美呼應，口感清爽。</v>
+        <v>以美國南方善於模仿各種鳥鳴的「仿聲鳥」命名。翠綠透亮的色澤呼應墨西哥綠色龍舌蘭的風土意象，將龍舌蘭熱情奔放的草本辛香，與白薄荷酒冰涼透徹的清涼感完美交融，酸甜青檸巧妙銜接，入口宛如置身清晨雨後的灌木森林，沁涼爽朗。</v>
       </c>
     </row>
     <row r="13">
@@ -815,7 +812,7 @@
         <v>建議物</v>
       </c>
       <c r="J13" t="str">
-        <v>當代夜店與居家必備的經典長飲，伏特加的純淨與萊姆汁的酸甜結合成極具親和力的爽口風味。</v>
+        <v>當代酒吧最普及且歷久彌新的靈魂長飲。以極致純淨的伏特加作為基石，佐以新鮮現榨萊姆汁與天然糖漿的酸甜衝擊。酒體俐落剔透、毫無拖泥帶水之感，冰塊撞擊杯壁的清脆聲響與舌尖明亮爽脆的果酸交織，無論是夜幕初降的開胃第一杯，還是深夜狂歡，皆能帶來最純粹的解渴快感。</v>
       </c>
     </row>
     <row r="14">
@@ -847,7 +844,7 @@
         <v>建議物</v>
       </c>
       <c r="J14" t="str">
-        <v>因《007》詹姆士龐德一句「用搖的，不要攪拌」而風靡全球的特務代名詞。</v>
+        <v>因英國情報員007詹姆士龐德一句傳世名言「用搖的，不要攪拌（Shaken, not stirred）」而風靡全球的特務代名詞。相較於傳統琴酒馬丁尼的草本繁複，伏特加以極致冷冽純淨的姿態登場，與干苦艾酒交織出晶瑩剔透的酒體，搖盪產生的細微碎冰如鑽石般漂浮，入口冰冷乾脆、幹練無比。</v>
       </c>
     </row>
     <row r="15">
@@ -867,7 +864,7 @@
         <v>白蘭地, 無氣泡, 經典</v>
       </c>
       <c r="F15" t="str">
-        <v xml:space="preserve">白蘭地 45 ml, 君度橙酒 15 ml, 檸檬汁 20 ml, 香橙干邑白蘭地1tsp, 純糖漿1tsp, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲, </v>
+        <v>白蘭地 45 ml, 君度橙酒 15 ml, 檸檬汁 20 ml, 香橙干邑白蘭地1tsp, 純糖漿1tsp, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲,</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -879,7 +876,7 @@
         <v>建議物</v>
       </c>
       <c r="J15" t="str">
-        <v>起源於一戰時期的巴黎或倫敦，據傳是一位美國上尉常騎著摩托側車前來酒吧而得名的白蘭地殿堂級調酒。</v>
+        <v>誕生於第一次世界大戰時期的巴黎麗茲酒店或倫敦傳奇酒吧，相傳是一位常騎著掛有邊車（Sidecar）摩托車的美國陸軍上尉經常點用而得名。作為白蘭地酸酒的殿堂級代表，優質干邑白蘭地的醇厚葡萄木質香，被君度橙酒與新鮮檸檬汁完美點亮，杯口一圈細緻白糖更添柔潤，酸甜醇郁、尊貴經典。</v>
       </c>
     </row>
     <row r="16">
@@ -911,7 +908,7 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>20世紀初風靡美國的蘋果白蘭地調酒，名字源於其深粉紅的玫瑰色澤與黑幫或調酒師的傳奇歷史。</v>
+        <v>風靡於20世紀初美國東岸，曾頻繁出現在大文豪海明威的小說《太陽照常升起》中。選用美國最古老的本土烈酒——蘋果白蘭地（Applejack），調和天然紅石榴糖漿與新鮮檸檬汁。酒液宛如盛開的玫瑰般散發深邃緋紅，入口兼具蘋果果香的溫潤與紅石榴的馥郁酸甜，散發濃濃的紐約復古風華。</v>
       </c>
     </row>
     <row r="17">
@@ -943,7 +940,7 @@
         <v>建議物</v>
       </c>
       <c r="J17" t="str">
-        <v>1919年義大利卡米洛·內格羅尼伯爵在佛羅倫斯酒吧要求將美國佬（Americano）中的蘇打水換成琴酒，自此誕生了這款苦甜經典。</v>
+        <v>1919年誕生於義大利佛羅倫斯卡索尼咖啡館。卡米洛·內格羅尼伯爵厭倦了平凡的美國佬（Americano），要求調酒師將蘇打水換成烈性琴酒以加強酒感。琴酒、金巴利（Campari）與紅苦艾酒以1:1:1等比例碰撞，苦中帶甜、草本悠長，杯中橙皮精油悠悠散開，是百年來全世界調酒師與酒客心中無可替代的苦甜之王。</v>
       </c>
     </row>
     <row r="18">
@@ -975,7 +972,7 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>帶有濃郁波本威士忌風情的高階軍官之酒，柑橘與可可香氣交織出沉穩的層次。</v>
+        <v>誕生於1930年代紐約高階海軍俱樂部，以海軍准將頭銜命名。以強勁濃郁的波本威士忌為骨架，融合白可可香甜酒的圓潤可可甜香，並以新鮮檸檬汁與紅石榴糖漿拉出漂亮的酸甜弧度。兼具軍官沉穩威嚴的木質力量與優雅細緻的甜點韻味，層次分明且後勁厚實。</v>
       </c>
     </row>
     <row r="19">
@@ -1007,7 +1004,7 @@
         <v>建議物</v>
       </c>
       <c r="J19" t="str">
-        <v>以知名動漫《凡爾賽玫瑰》為靈感，優雅的花香與酸甜感交織，呈現華麗浪漫的視覺與風味。</v>
+        <v>靈感源自經典漫畫《凡爾賽玫瑰》中堅毅與浪漫並存的女主角奧斯卡。以優雅的白蘭地或果香香甜酒為底，調和玫瑰花瓣露與蔓越莓的酸甜果韻。酒液呈現宛如凡爾賽宮晨曦花園般的緋紅粉光，入口花香四溢、果酸柔美，如同在華麗宮廷中綻放的一抹高貴愛情。</v>
       </c>
     </row>
     <row r="20">
@@ -1039,7 +1036,7 @@
         <v>建議物</v>
       </c>
       <c r="J20" t="str">
-        <v>起源於緬甸勃固俱樂部（Pegu Club），是英國殖民時期風靡海員與紳士的琴酒酸甜風消暑良伴。</v>
+        <v>起源於19世紀末英國殖民緬甸時期、仰光附近的傳奇紳士聚所「勃固俱樂部」（Pegu Club）。是當時駐守熱帶雨林的海員與軍官用來驅逐暑氣與濕熱的心頭好。琴酒草本與柑橘橙酒融合，大膽滴入柑橘苦精與安格式苦精，酸度凌厲、草本乾爽，散發大航海時代的異國冒險氣息。</v>
       </c>
     </row>
     <row r="21">
@@ -1071,7 +1068,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>1920年代為了致敬喜劇大師查理·卓別林而創作，杏桃香甜酒與黑刺李琴酒碰撞出極具生命力的酸甜。</v>
+        <v>誕生於1920年代紐約華爾街著名的草叢俱樂部，調酒師為了向默片喜劇大師查理·卓別林致敬而創作。大膽採用黑刺李琴酒（Sloe Gin）與杏桃白蘭地，佐以新鮮現榨檸檬汁。酒液散發寶石紅光澤，入口迎來奔放的核果果香與酸甜生津的滋味，宛如卓別林電影般充滿歡笑與細膩溫度。</v>
       </c>
     </row>
     <row r="22">
@@ -1103,7 +1100,7 @@
         <v>建議物</v>
       </c>
       <c r="J22" t="str">
-        <v>據傳是禁酒令時期芝加哥南幫黑幫大佬艾爾·卡彭的最愛，薄荷與檸檬成功掩蓋了當時私釀琴酒的辛辣。</v>
+        <v>相傳是禁酒令時期芝加哥惡名昭彰的南幫教父艾爾·卡彭（Al Capone）的最愛。當時南幫走私的琴酒品質粗糙辛辣，調酒師靈機一動加入大量新鮮薄荷、新鮮檸檬汁與糖漿劇烈搖盪，徹底掩蓋了雜味。口感冰涼清爽、薄荷草本香氣撲鼻，如今成為上流鄉村俱樂部的避暑代表。</v>
       </c>
     </row>
     <row r="23">
@@ -1135,7 +1132,7 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>巴西的國酒。以卡夏沙（Cachaça）甘蔗酒、新鮮萊姆與砂糖在地直搗調製，展現極致的南美熱情。</v>
+        <v>巴西的國家級國酒，名字在葡萄牙語中意為「鄉村小姑娘」。傳統上使用巴西特產甘蔗蒸餾酒「卡夏沙」（Cachaça），在古典杯中直接將新鮮青檸角與白砂糖搗壓出濃郁精油與酸甜汁液，鋪滿碎冰。入口草本甘蔗香奔放明亮，青檸酸爽沁涼，洋溢著熱帶森巴嘉年華的無盡熱情。</v>
       </c>
     </row>
     <row r="24">
@@ -1167,7 +1164,7 @@
         <v>建議物</v>
       </c>
       <c r="J24" t="str">
-        <v>調酒界的始祖。以波本或黑麥威士忌為基底，完美體現19世紀初「精神、水、糖與苦精」的最原始雞尾酒定義。</v>
+        <v>誕生於19世紀初，是「雞尾酒（Cocktail）」一詞最初的定義與精神起點。在古典杯中將方糖浸潤苦精慢慢壓碎，注入優質波本或黑麥威士忌，以大冰塊緩慢攪拌出完美的融水度。橙皮與櫻桃點綴其間，酒香深邃濃郁、甜苦平衡，每一口都是向美國威士忌兩百年傳統致敬的純粹硬派風範。</v>
       </c>
     </row>
     <row r="25">
@@ -1199,7 +1196,7 @@
         <v>建議物</v>
       </c>
       <c r="J25" t="str">
-        <v>禁酒令時期的「上流社會夜帽酒」，白蘭地與白薄荷酒的結合，口感乾冽寒冷，常作為飯後消化酒。</v>
+        <v>1890年代誕生於紐約，曾是美國鍍金時代名流富豪與百萬富翁們在晚宴後最愛的「夜帽酒（Nightcap）」。將醇厚的干邑白蘭地與清冽透骨的白薄荷香甜酒完美調和。白蘭地的橡木果香被冰極薄荷瞬間拉提，口感乾脆寒涼、提神醒腦，亦被名作家沙林傑寫入《麥田捕手》經典場景中。</v>
       </c>
     </row>
     <row r="26">
@@ -1231,7 +1228,7 @@
         <v/>
       </c>
       <c r="J26" t="str">
-        <v>結合法國蘇茲藥草酒與苦艾酒，如深夜床邊的輕聲呢喃，帶著淡淡草本苦甜與細緻香氣。</v>
+        <v>發源於20世紀初法國巴黎沙龍，宛如戀人間在深夜枕邊的耳語呢喃。以琴酒與干苦艾酒為基調，融入法國蘇茲（Suze）龍膽草藥草酒或甜苦艾酒。酒液泛著淡雅金黃，入口先是淡淡的花草清香，隨後在舌根化開絲絲苦甜回甘，風格靜謐、細緻悠長，極適合一人獨酌。</v>
       </c>
     </row>
     <row r="27">
@@ -1263,7 +1260,7 @@
         <v>建議物</v>
       </c>
       <c r="J27" t="str">
-        <v>1880年代記載於經典酒譜中，雖然名為咖啡，但配方完全不含咖啡，僅靠波特酒與白蘭地撞擊出酷似冰咖啡的色澤與醇厚度。</v>
+        <v>記載於「調酒之父」Jerry Thomas 1887年版經典酒譜中的驚人傑作。雖然名為咖啡，配方中卻完全不含一滴咖啡！而是巧妙利用紅波特酒與干邑白蘭地、整顆生蛋黃與砂糖充分搖盪，竟奇蹟般碰撞出如濃縮冰咖啡般的深褐色澤與醇厚香氣，口感絲滑濃郁，如高級甜點般令人驚艷。</v>
       </c>
     </row>
     <row r="28">
@@ -1295,7 +1292,7 @@
         <v>建議物</v>
       </c>
       <c r="J28" t="str">
-        <v>1983年倫敦調酒大師Dick Bradsell為一位知名超模量身打造，名言是「希望能調出一杯先喚醒我、再灌醉我的酒」。</v>
+        <v>1983年倫敦傳奇調酒大師Dick Bradsell在Soho Brasserie創作。當時一位後來的世界超模走進吧台提出要求：「調一杯能先喚醒我、再灌醉我的酒」。大師將剛萃取的熱義式濃縮咖啡與伏特加、咖啡利口酒劇烈搖盪，搖出如奶泡般細緻的油脂頂部，飾以三顆咖啡豆，成為現代都會夜晚的永恆不敗經典。</v>
       </c>
     </row>
     <row r="29">
@@ -1327,7 +1324,7 @@
         <v/>
       </c>
       <c r="J29" t="str">
-        <v>美式傳統暖胃調酒，濃郁的咖啡、草本甜酒與白蘭地完美結合，帶來如壁爐般的溫暖慰藉。</v>
+        <v>美式傳統經典暖心長飲，起源於美國西北太平洋岸潮濕陰冷的冬日。將香醇現煮熱咖啡（或咖啡利口酒）注入白蘭地、深色可可酒與草本甜酒，頂部鋪上厚厚一層現打鮮奶油。深沉的烘焙香氣與烈酒暖意交織，一口飲下自喉頭蔓延開溫暖舒適感，宛如壁爐邊最忠實的慰藉。</v>
       </c>
     </row>
     <row r="30">
@@ -1359,7 +1356,7 @@
         <v>建議物</v>
       </c>
       <c r="J30" t="str">
-        <v>由日本調酒大師上田和男於1986年創作，奪得國際調酒大賽冠軍。獨特的亮綠色澤代表蘇格蘭優美的山谷風景。</v>
+        <v>由日本銀座調酒教父上田和男於1986年創作，一舉奪得第1屆第一回斯科奇威士忌雞尾酒大賽世界冠軍。大膽選用蘇格蘭威士忌為底，融入君度橙酒、藍柑桂酒與萊姆汁。透過其獨創的「硬搖盪（Hard Shake）」，調配出宛如蘇格蘭高地翠綠幽深峽谷般的夢幻湖綠色澤，果香與泥煤麥芽完美平衡。</v>
       </c>
     </row>
     <row r="31">
@@ -1391,7 +1388,7 @@
         <v>建議物</v>
       </c>
       <c r="J31" t="str">
-        <v>1920年代古巴哈瓦那的古老配方，以古巴總統命名，是禁酒令時期美國富豪飛往古巴度假時必喝的貴族調酒。</v>
+        <v>1920年代古巴哈瓦那的古老配方，以當時古巴總統馬里奧·加西亞·梅諾卡爾命名。在美國禁酒令時期，無數美國富豪搭機奔赴哈瓦那避難度假，此酒正是當時名流在哈瓦那賽馬俱樂部人手一杯的貴族象徵。陳年白蘭姆酒、白苦艾酒與橙皮酒交融，石榴糖漿染出一抹鮭魚粉，口感優雅輕盈。</v>
       </c>
     </row>
     <row r="32">
@@ -1423,7 +1420,7 @@
         <v>建議物</v>
       </c>
       <c r="J32" t="str">
-        <v>誕生於紐約同名飯店，以白蘭地與干馬丁尼的組合，展現19世紀末繁華大都市的幹練與成熟。</v>
+        <v>誕生於19世紀末紐約同名豪華大飯店，是鍍金年代曼哈頓金融精英的摯愛。以干邑白蘭地為基底，調和干苦艾酒與少許裴喬氏苦精。與甜美的曼哈頓不同，大都會散發出極度幹練、乾脆的木質單寧與草本氣息，入口深沉大器，完美勾勒出19世紀繁華大都會的成熟與自信。</v>
       </c>
     </row>
     <row r="33">
@@ -1455,7 +1452,7 @@
         <v>建議物</v>
       </c>
       <c r="J33" t="str">
-        <v>歷史悠久的經典酸酒，最早紀錄見於1862年，完美展現烈酒、檸檬與糖的黃金三角比例。</v>
+        <v>調酒史上的酸甜黃金標準，最早文字記載見於1862年Jerry Thomas的酒譜。以濃郁飽滿的波本威士忌為骨架，新鮮檸檬汁的明亮果酸與糖漿柔和銜接，搖盪出細緻綿密的乳化泡沫。杯中滴入安格式苦精增添香氣，酸甜開胃、酒體圓潤，是兩個世紀以來全球酒吧永恆的點單首選。</v>
       </c>
     </row>
     <row r="34">
@@ -1487,7 +1484,7 @@
         <v>建議物</v>
       </c>
       <c r="J34" t="str">
-        <v>同時加入等量的甜苦艾酒與干苦艾酒，追求在「乾冽」與「甜美」之間達成最完美的物理平衡。</v>
+        <v>在調酒術語中，「Perfect（完美）」並非自誇，而是指「等量平衡」。在此款馬丁尼中，同時加入等量的干苦艾酒（Dry Vermouth）與甜苦艾酒（Sweet Vermouth）。琴酒的杜松子香氣在干冽草本與果香微甜之間取得天秤般的平衡，口感比傳統干馬丁尼更加柔和圓潤，耐人尋味。</v>
       </c>
     </row>
     <row r="35">
@@ -1519,7 +1516,7 @@
         <v>建議物</v>
       </c>
       <c r="J35" t="str">
-        <v>1970年代隨著Midori哈密瓜香甜酒問世而爆紅的派對長飲，充滿蜜瓜與鳳梨汁的香甜陽光感。</v>
+        <v>1970年代隨著三得利Midori綠色哈密瓜香甜酒在紐約 Studio 54 傳奇夜店隆重上市而引爆全美狂潮。亮麗翠綠的酒液中充滿熟成哈密瓜的甜美蜜香，伏特加提供乾淨俐落的微醺骨架，佐以新鮮鳳梨汁與柳橙汁。口感熱情奔放、甜而不膩，一口帶你重回迪斯可黃金年代的派對盛夏。</v>
       </c>
     </row>
     <row r="36">
@@ -1551,7 +1548,7 @@
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>出自1900年經典酒譜，結合蘋果白蘭地、夏翠絲與班尼迪克丁兩大藥草聖酒，風味複雜、後勁深邃如寡婦之吻。</v>
+        <v>收錄於1895年George Kappeler的經典酒譜中。將諾曼第頂級蘋果白蘭地（Calvados）與兩大中世紀修道院藥草聖酒——黃夏翠絲（Yellow Chartreuse）與本篤會廊酒（Bénédictine）以精妙比例調和。入口層次繁複莫測，草本辛香與蘋果芳醇層層綻放，深邃濃烈，宛如美麗寡婦令人難以抗拒的危險親吻。</v>
       </c>
     </row>
     <row r="37">
@@ -1583,7 +1580,7 @@
         <v>建議物</v>
       </c>
       <c r="J37" t="str">
-        <v>由調酒始祖Harry Johnson於19世紀末創作，名字在法文中意為「珠寶」，琴酒（鑽石）、金巴利（紅寶石）與甜苦艾酒（綠寶石）交織。</v>
+        <v>1890年代由調酒先驅Harry Johnson創作，「Bijou」在法語中意為「珠寶」。此酒巧妙將三種頂級烈酒隱喻為三大寶石：琴酒如璀璨鑽石、紅苦艾酒如溫潤紅寶石、綠夏翠絲藥草酒如深邃綠寶石。三種性格強烈的酒液在冰塊攪拌下融為一體，香氣深邃複雜、草本藥香悠長，是古典調酒殿堂的璀璨瑰寶。</v>
       </c>
     </row>
     <row r="38">
@@ -1615,7 +1612,7 @@
         <v>建議物</v>
       </c>
       <c r="J38" t="str">
-        <v>當代甜點系調酒的代表，濃郁的可可香氣與伏特加的俐落結合，深受甜食與巧克力愛好者青睞。</v>
+        <v>1950年代由傳奇巨星勞勃·赫遜與伊莉莎白·泰勒在好萊塢拍攝電影《巨人》期間私下調製而傳開的經典甜點調酒。以純淨伏特加或香草伏特加為底，融入濃純愛爾蘭奶酒與黑可可香甜酒，杯壁以巧克力糖漿勾勒華麗紋路。入口如絲絨般滑順香濃，微醺與苦甜可可完美交織，深受甜食愛好者青睞。</v>
       </c>
     </row>
     <row r="39">
@@ -1647,7 +1644,7 @@
         <v>建議物</v>
       </c>
       <c r="J39" t="str">
-        <v>20世紀初由華道夫飯店調酒師創作，首創將柳橙汁加入馬丁尼中，因造訪布朗克斯動物園而得名，曾高居世界三大調酒之一。</v>
+        <v>1906年由紐約華道夫大飯店傳奇調酒師Johnnie Solon創作，因他造訪甫開幕的布朗克斯動物園深受啟發而命名。此酒首開先河將新鮮現榨柳橙汁加入馬丁尼中，曾與馬丁尼、曼哈頓並列為禁酒令前「世界三大雞尾酒」。橙香清新多汁，杜松子草本與苦艾酒巧妙隱現，風格明亮清爽。</v>
       </c>
     </row>
     <row r="40">
@@ -1679,7 +1676,7 @@
         <v>建議物</v>
       </c>
       <c r="J40" t="str">
-        <v>帶有草本與柑橘酸甜的傳統藥草系風味調酒，口感層次豐富。</v>
+        <v>傳統草本酸甜調酒的經典復古之作。大膽以黑麥威士忌搭配石榴糖漿、新鮮柳橙汁與覆盆子利口酒，相傳靈感來自老藥劑師調配的滋補良方。木質辛香在豐富的莓果與柑橘酸甜襯托下顯得格外柔和生津，層次豐富，帶有一種懷舊而溫暖的美式藥草風情。</v>
       </c>
     </row>
     <row r="41">
@@ -1711,7 +1708,7 @@
         <v>建議物</v>
       </c>
       <c r="J41" t="str">
-        <v>1930年代風靡巴黎的性感經典，將側車（Sidecar）中的部分白蘭地替換為蘭姆酒，使風味更顯輕盈與挑逗。</v>
+        <v>1930年代由巴黎哈里紐約酒吧（Harry's New York Bar）傳奇調酒師Harry MacElhone創作。將側車（Sidecar）中的部分干邑白蘭地替換為優質白蘭姆酒，使酒體更加輕盈挑逗。橙皮酒與檸檬汁酸甜明亮，酒精濃度雖高卻入口無痕，帶著法式沙龍般的慵懶與性感，因而得名。</v>
       </c>
     </row>
     <row r="42">
@@ -1743,7 +1740,7 @@
         <v>建議物</v>
       </c>
       <c r="J42" t="str">
-        <v>起源於1930年代，向著名的肯塔基賽馬會（Kentucky Derby）致敬，波本威士忌與薄荷帶來陽光奔放的草本乾爽。</v>
+        <v>起源於1930年代，向美國南方最負盛名的體育盛事「肯塔基賽馬會（Kentucky Derby）」致敬。波本威士忌特有的香草與烤橡木香氣，在薄荷葉的拍擊揉合下展現出如同陽光灑在馬場草皮上的乾爽生命力。柑橘香氣點綴其間，口感剛健爽朗，是南方紳士名媛觀賽時的最佳良伴。</v>
       </c>
     </row>
     <row r="43">
@@ -1775,7 +1772,7 @@
         <v>建議物</v>
       </c>
       <c r="J43" t="str">
-        <v>黑麥威士忌與杜本內（Dubonnet）利口酒的世紀相遇，苦甜橙皮與木質香氣堆疊出醇厚的紳士質感。</v>
+        <v>出自1917年Hugo Ensslin經典酒譜，以當時著名的拳擊手Dave Deshler命名。以硬派的黑麥威士忌為骨架，融合法國杜本內（Dubonnet）開胃酒、少許柑橘橙酒與裴喬氏苦精。杜本內的奎寧苦甜與黑麥的辛辣木質在杯中碰撞出極度優雅的紳士質感，成熟而充滿內斂力量。</v>
       </c>
     </row>
     <row r="44">
@@ -1807,7 +1804,7 @@
         <v>建議物</v>
       </c>
       <c r="J44" t="str">
-        <v>1987年由佛羅裡達調酒師因應春假熱潮所創，充滿桃子、蔓越莓與鳳梨的熱帶水果風情。</v>
+        <v>1987年由佛羅里達調酒師Ted Pizio為了贏得水蜜桃利口酒銷售競賽而創作。結合伏特加、水蜜桃香甜酒、蔓越莓汁與現榨鳳梨汁，亮麗的粉橘漸層如夕陽海岸。入口充滿奔放多汁的蜜桃果香與酸甜熱帶氣息，冰涼好入口，成為全美春假沙灘狂歡派對的永恆標誌。</v>
       </c>
     </row>
     <row r="45">
@@ -1839,7 +1836,7 @@
         <v/>
       </c>
       <c r="J45" t="str">
-        <v>將愛爾蘭奶酒與威士忌的Shot杯投入健力士黑啤酒中，必須一口氣乾掉，因濃縮咖啡與奶酒撞擊出濃郁的巧克力風味。</v>
+        <v>1979年在康乃狄克州諾威奇酒吧誕生。將裝有愛爾蘭威士忌與百利甜奶酒的Shot杯，直接投擲浸入半品脫健力士（Guinness）黑生啤酒中，必須在數秒內一飲而盡！奶酒與黑啤酒撞擊的瞬間乳化出如巧克力奶昔般的驚人綿密香甜，隨後迎來黑麥烘焙焦香與烈酒熱度，極具派對張力。</v>
       </c>
     </row>
     <row r="46">
@@ -1871,59 +1868,59 @@
         <v>建議物</v>
       </c>
       <c r="J46" t="str">
-        <v>以紐約著名的富豪遊艇聖地拉奇蒙特命名，蘭姆酒底夾帶青檸與橙香，散發乾淨、雅緻的貴族度假感。</v>
+        <v>以紐約長島海灣著名的富豪帆船聖地拉奇蒙特遊艇俱樂部命名。選用加勒比海優質白蘭姆酒，揉合大中央橙皮甜酒與新鮮現榨青檸汁。酒液清澈金黃，入口乾淨高雅，既有蘭姆酒的甘蔗溫潤，又有柑橘橙皮的尊貴香氣，洋溢著英美名流揚帆出海時的悠閒與奢華。</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>拉莫斯琴費士  Romos Gin Fizz</v>
+        <v>搖尾巴</v>
       </c>
       <c r="B47">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47">
         <v>3</v>
       </c>
       <c r="E47" t="str">
-        <v>琴酒, 有氣泡, 經典</v>
+        <v>伏特加, 無氣泡</v>
       </c>
       <c r="F47" t="str">
-        <v>琴酒 60 ml, 鮮奶油 30 ml, 檸檬汁 15 ml, 萊姆汁 15 ml, 純糖漿 30 ml, 橙花水 3~4 drops, 蛋白 1 顆, 蘇打水適量,, 柳橙皮捲</v>
+        <v>伏特加 45 ml, 葡萄柚汁 60 ml, 檸檬汁 30 ml, 純糖漿 15 ml, 肯巴利苦酒1tsp, 葡萄柚苦精2 dashes, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 葡萄柚皮捲</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>冰鎮長飲杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I47" t="str">
         <v>建議物</v>
       </c>
       <c r="J47" t="str">
-        <v>1888年由Henry Ramos在新奧爾良發明，以極其繁複的長時搖盪（傳統上需搖12分鐘）打造出如舒芙蕾般綿密的完美泡沫。</v>
+        <v>特調創意現代派對果感調酒。以純淨伏特加為底，融入水蜜桃、草莓與熱帶果汁的明亮甜酸，注入細緻氣泡蘇打水。粉嫩清透的酒液中氣泡如小精靈般歡快跳躍，入口酸甜爽脆、果香四溢，就像寵物見到主人時雀躍不停搖晃的小尾巴，讓人心情瞬間明朗愉悅。</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>搖尾巴</v>
+        <v>撒旦的鬍鬚  Satan`s Whiskers</v>
       </c>
       <c r="B48">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
       <c r="E48" t="str">
-        <v xml:space="preserve">伏特加, 無氣泡, </v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F48" t="str">
-        <v>伏特加 45 ml, 葡萄柚汁 60 ml, 檸檬汁 30 ml, 純糖漿 15 ml, 肯巴利苦酒1tsp, 葡萄柚苦精2 dashes, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 葡萄柚皮捲</v>
+        <v>琴酒 22 ml, 法式不甜香艾酒 22 ml, 法式甜香艾酒 22 ml, 香橙干邑白蘭地 15 ml, 柳橙汁 15 ml, 安格式柑橘苦精 1 dash, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -1935,59 +1932,59 @@
         <v>建議物</v>
       </c>
       <c r="J48" t="str">
-        <v>俏皮現代調酒，利用豐富的果香與輕盈汽泡感交織，呈現如果汁般好入口且充滿活力的微醺體驗。</v>
+        <v>1930年收錄於《薩伏依雞尾酒手冊》，在倫敦調酒界享有盛譽。分為加入橙酒的「華麗版（Curacao）」與加入柑橘利口酒的「乾冽版（Grand Marnier）」。琴酒、等量干甜苦艾酒與新鮮現榨柳橙汁完美乳化，杯緣橙皮油點綴，酸甜果香中暗藏魔鬼般誘人且強勁的辛辣後勁。</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>撒旦的鬍鬚  Satan`s Whiskers</v>
+        <v>教母  Godmother</v>
       </c>
       <c r="B49">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C49">
         <v>4</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>伏特加, 無氣泡, 經典</v>
       </c>
       <c r="F49" t="str">
-        <v>琴酒 22 ml, 法式不甜香艾酒 22 ml, 法式甜香艾酒 22 ml, 香橙干邑白蘭地 15 ml, 柳橙汁 15 ml, 安格式柑橘苦精 1 dash, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
+        <v>伏特加 90 ml, 杏仁香甜酒 30 ml</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮古典杯</v>
       </c>
       <c r="I49" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J49" t="str">
-        <v>1930年《Savoy》經典記載，分為華麗版與乾冽版，柑橘利口酒與苦艾酒交織出酸甜卻又辛辣的魔鬼誘惑。</v>
+        <v>經典電影調酒「教父」的柔美優雅變奏版。將傳統的蘇格蘭威士忌替換為純淨無瑕的頂級伏特加，巧妙放大了義大利帝薩諾（Disaronno）苦杏仁酒細緻的杏桃果核香與櫻桃甜香。入口溫潤順滑、如絲綢覆蓋舌尖，冷冽的伏特加完美平衡了濃稠甜感，深受女性酒客熱愛。</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>教母  Godmother</v>
+        <v>教父  Godfather</v>
       </c>
       <c r="B50">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
       <c r="E50" t="str">
-        <v>伏特加, 無氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F50" t="str">
-        <v>伏特加 90 ml, 杏仁香甜酒 30 ml</v>
+        <v>蘇格蘭威士忌 90 ml, 杏仁香甜酒 30 ml</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -1999,204 +1996,204 @@
         <v/>
       </c>
       <c r="J50" t="str">
-        <v>教父雞尾酒的優雅變奏版，將威士忌換成純淨的伏特加，更能凸顯義大利苦杏仁酒細緻的杏仁與櫻桃果香。</v>
+        <v>1970年代隨著馬龍·白蘭度主演的黑幫史詩電影《教父》橫掃全球而問世，據傳是電影主角的最愛。以帶有煙燻木質風味的蘇格蘭威士忌為骨架，大膽加入義大利傳統苦杏仁利口酒（Amaretto）。威士忌的泥煤剛烈被杏仁堅果的柔美甜香深情包覆，剛柔並濟，散發義大利西西里島深沉的家族榮譽感。</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>教父  Godfather</v>
+        <v>新加坡司令  Singapore sling</v>
       </c>
       <c r="B51">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>琴酒, 有氣泡, 經典</v>
       </c>
       <c r="F51" t="str">
-        <v>蘇格蘭威士忌 90 ml, 杏仁香甜酒 30 ml</v>
+        <v>琴酒 45 ml, 櫻桃香甜酒 20 ml, 糖漿	20 ml, 君度橙酒10 ml, 班尼迪克丁10 ml, 安格式原味苦精	1 dash, 鳳梨汁	60 ml, 萊姆汁 25 ml, 紅石榴糖漿1 tsp, 蘇打水適量</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>冰鎮古典杯</v>
+        <v>冰鎮長飲杯</v>
       </c>
       <c r="I51" t="str">
         <v/>
       </c>
       <c r="J51" t="str">
-        <v>以著名同名電影《教父》命名，蘇格蘭威士忌的煙燻泥煤與義大利苦杏仁酒的甜美完美結合，深受影迷喜愛。</v>
+        <v>1915年由華裔調酒師嚴崇文於新加坡萊佛士酒店長廊酒吧發明。在當時殖民時代女性被禁止在公開場合飲酒，大師巧妙將琴酒藏在粉紅櫻桃白蘭地、鳳梨汁、班尼迪克丁與檸檬汁中，宛如一杯無害果汁。酸甜層次豐富、熱帶果香濃郁，是全世界最著名的熱帶長飲國寶。</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>新加坡司令  Singapore sling</v>
+        <v>新聞記者  Journalist</v>
       </c>
       <c r="B52">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52">
         <v>3</v>
       </c>
       <c r="E52" t="str">
-        <v>琴酒, 有氣泡, 經典</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F52" t="str">
-        <v xml:space="preserve">琴酒 45 ml, 櫻桃香甜酒 20 ml, 糖漿	20 ml, 君度橙酒10 ml, 班尼迪克丁10 ml, 安格式原味苦精	1 dash, 鳳梨汁	60 ml, 萊姆汁 25 ml, 紅石榴糖漿1 tsp, 蘇打水適量 </v>
+        <v>琴酒 45 ml, 義式不甜香艾酒 7.5 ml, 義式甜香艾酒 7.5 ml, 君度橙酒 2 dash, 檸檬汁 2 dash, 安格式原味苦精 1 dash, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>冰鎮長飲杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I52" t="str">
         <v/>
       </c>
       <c r="J52" t="str">
-        <v>1915年由嚴崇文在新加坡萊佛士酒店發明，粉紅色澤的外觀最初是為了讓女性在公開場合優雅飲酒而不失禮節。</v>
+        <v>1930年代盛行於倫敦與紐約報業記者聚集的地下酒吧。在傳統馬丁尼（琴酒與干甜苦艾酒）的架構上，大膽加入了新鮮檸檬汁與紅石榴糖漿、苦精。酸度生津、苦甜回甘，層次複雜多變，象徵著新聞記者犀利入骨的文筆、洞悉世事的敏銳眼光與辛酸冷暖的記者生涯。</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>新聞記者  Journalist</v>
+        <v>方丈內格羅尼</v>
       </c>
       <c r="B53">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>琴酒, 無氣泡</v>
       </c>
       <c r="F53" t="str">
-        <v>琴酒 45 ml, 義式不甜香艾酒 7.5 ml, 義式甜香艾酒 7.5 ml, 君度橙酒 2 dash, 檸檬汁 2 dash, 安格式原味苦精 1 dash, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。</v>
+        <v>琴酒 25 ml, 龍舌蘭 25 ml, 肯巴利苦酒 25 ml, 義式甜香艾酒 25 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的淺碟香檳杯。, 柳橙皮捲</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮淺碟香檳杯</v>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J53" t="str">
-        <v>比傳統馬丁尼更加複雜的變奏版，加入了橙皮苦精與檸檬汁，象徵新聞記者般辛辣、犀利且耐人尋味的特質。</v>
+        <v>東方禪意與西方經典的當代融合之作。在傳統內格羅尼（琴酒、金巴利、甜苦艾酒）的剛勁苦甜骨架中，創新融入深焙台灣烏龍茶或東方美人茶進行低溫浸漬萃取。入口迎來熟悉的草本柑橘苦甜，隨後深沉厚實的炭焙茶香在喉間悠悠化開，苦而不澀、禪意深遠，宛如古寺方丈對坐長談。</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>方丈內格羅尼</v>
+        <v>日本拖鞋  Japanese Slipper</v>
       </c>
       <c r="B54">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C54">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E54" t="str">
-        <v xml:space="preserve">琴酒, 無氣泡, </v>
+        <v>其他, 無氣泡, 經典</v>
       </c>
       <c r="F54" t="str">
-        <v>琴酒 25 ml, 龍舌蘭 25 ml, 肯巴利苦酒 25 ml, 義式甜香艾酒 25 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的淺碟香檳杯。, 柳橙皮捲</v>
+        <v>蜜多麗蜜瓜香甜酒 60 ml, 君度橙酒 20 ml, 萊姆汁 20 ml, 純糖漿 1 tsp, 糖漬櫻桃1 顆,  糖漬櫻桃</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>冰鎮淺碟香檳杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I54" t="str">
         <v>建議物</v>
       </c>
       <c r="J54" t="str">
-        <v>融合東方禪意與西方經典，用茶香或特定草本將內格羅尼溫潤化，苦甜中帶有一絲悠長的沉穩茶韻。</v>
+        <v>1984年由法籍調酒師Jean-Paul Bourguignon在澳洲墨爾本Mijitano酒吧創作。將三得利Midori蜜瓜酒、君度橙酒與新鮮現榨檸檬汁以完美1:1:1等比例搖盪。酒液呈現不可思議的亮麗螢光翠綠，杯底沉下一顆紅櫻桃。入口蜜瓜香甜與青檸酸香瞬間爆發，口感無比柔順絲滑。</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>日本拖鞋  Japanese Slipper</v>
+        <v>日本雞尾酒  Japanese</v>
       </c>
       <c r="B55">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E55" t="str">
-        <v>其他, 無氣泡, 經典</v>
+        <v>白蘭地, 無氣泡, 經典</v>
       </c>
       <c r="F55" t="str">
-        <v>蜜多麗蜜瓜香甜酒 60 ml, 君度橙酒 20 ml, 萊姆汁 20 ml, 純糖漿 1 tsp, 糖漬櫻桃1 顆,  糖漬櫻桃</v>
+        <v>白蘭地 60 ml, 杏仁糖漿 15 ml, 安格式原味苦精 2 dash, 2. 濾掉冰塊，將酒液倒入冰鎮過的酸味酒杯。, 檸檬皮捲</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮酸味酒杯</v>
       </c>
       <c r="I55" t="str">
         <v>建議物</v>
       </c>
       <c r="J55" t="str">
-        <v>1984年由調酒師Jean-Paul Bourguignon在墨爾本發明。Midori、君度與檸檬汁等比例調配，呈現夢幻的亮綠色與哈密瓜香甜。</v>
+        <v>收錄於1862年Jerry Thomas編寫的世界第一本調酒專書中。是為了款待1860年橫跨太平洋造訪紐約曼哈頓的第一批日本武士幕府使節團而創作。干邑白蘭地底融入自製杏仁糖漿（Orgeat）與安格式苦精，散發溫潤典雅的烤堅果香與木質花香，是調酒史上東西文化初次交會的永恆見證。</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>日本雞尾酒  Japanese</v>
+        <v>曼哈頓(I)  Manhattan(I)</v>
       </c>
       <c r="B56">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D56">
         <v>2</v>
       </c>
       <c r="E56" t="str">
-        <v>白蘭地, 無氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F56" t="str">
-        <v>白蘭地 60 ml, 杏仁糖漿 15 ml, 安格式原味苦精 2 dash, 2. 濾掉冰塊，將酒液倒入冰鎮過的酸味酒杯。, 檸檬皮捲</v>
+        <v>波本威士忌 60 ml, 義式甜香艾酒 20 ml, 安格式原味苦精 2 dashes, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 勒薩多糖漬櫻桃, 柳橙皮捲</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>冰鎮酸味酒杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I56" t="str">
         <v>建議物</v>
       </c>
       <c r="J56" t="str">
-        <v>記載於1862年美國第一本正式酒譜中，為了款待當年第一批訪美的日本使節團而作，首次將日本風情帶入西方調酒界。</v>
+        <v>被調酒界尊稱為「雞尾酒之后」。相傳起源於1874年紐約曼哈頓俱樂部為邱吉爾之母珍妮·傑羅姆舉辦的慶祝宴會。選用辛辣硬派的美國黑麥威士忌，與義大利紅甜苦艾酒以2:1比例調和，安格式苦精牽引出深邃層次。酒液呈高貴琥珀紅，入口木質溫潤、甘甜微苦，散發紐約不夜城的成熟魅力。</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>曼哈頓(I)  Manhattan(I)</v>
+        <v>曼哈頓(II)  Manhattan(II)</v>
       </c>
       <c r="B57">
         <v>30</v>
@@ -2211,91 +2208,91 @@
         <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F57" t="str">
-        <v>波本威士忌 60 ml, 義式甜香艾酒 20 ml, 安格式原味苦精 2 dashes, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 勒薩多糖漬櫻桃, 柳橙皮捲</v>
+        <v>波本威士忌 60 ml, 義式甜香艾酒 20 ml, 安格式原味苦精 2 dashes, 2．濾掉冰塊，將酒液倒入冰鎮過的古典杯，加入岩冰。, 柳橙皮捲, 糖漬櫻桃</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮古典杯</v>
       </c>
       <c r="I57" t="str">
         <v>建議物</v>
       </c>
       <c r="J57" t="str">
-        <v>被譽為「雞尾酒王后」。相傳起源於1870年代紐約曼哈頓俱樂部為邱吉爾母親舉辦的宴會，高雅且充滿深度。</v>
+        <v>當代調酒復興浪潮中針對經典曼哈頓的硬派微調版。精選桶裝原強度波本威士忌，搭配少許裴喬氏苦精與特選都靈紅苦艾酒。酒體更加純粹乾燥、酒感厚重，突出烤橡木、焦糖與黑櫻桃的醇厚共鳴，是專為資深威士忌老饕設計的紐約深夜私藏。</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>曼哈頓(II)  Manhattan(II)</v>
+        <v>杏仁酸味酒 Amaretto Sour</v>
       </c>
       <c r="B58">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E58" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>其他, 無氣泡, 經典</v>
       </c>
       <c r="F58" t="str">
-        <v>波本威士忌 60 ml, 義式甜香艾酒 20 ml, 安格式原味苦精 2 dashes, 2．濾掉冰塊，將酒液倒入冰鎮過的古典杯，加入岩冰。, 柳橙皮捲, 糖漬櫻桃</v>
+        <v>杏仁香甜酒 45 ml, 波本威士忌 20 ml, 檸檬汁 30 ml, 純糖漿1tsp, 濾掉冰塊，將酒液倒入冰鎮過的淺碟香檳杯。, 勒薩多糖漬櫻桃</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>冰鎮古典杯</v>
+        <v>冰鎮淺碟香檳杯</v>
       </c>
       <c r="I58" t="str">
         <v>建議物</v>
       </c>
       <c r="J58" t="str">
-        <v>經典曼哈頓的當代微調版，透過不同比例的苦精或黑麥威士忌，呈現更硬派、更乾冽的紐約深夜風情。</v>
+        <v>當代最受全球酒客愛戴的酸甜調酒之一。源自義大利著名的薩隆諾帝薩諾（Disaronno）苦杏仁利口酒，融合新鮮檸檬汁與少許高濃度波本威士忌以支撐骨架，加入蛋白搖盪出如奶油般絲滑的泡沫頂部。入口宛如剛出爐的法式杏仁檸檬塔，酸甜爽口、堅果香氣馥郁，令人一試難忘。</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>杏仁酸味酒 Amaretto Sour</v>
+        <v>東印度大樓  East India House</v>
       </c>
       <c r="B59">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E59" t="str">
-        <v>其他, 無氣泡, 經典</v>
+        <v>白蘭地, 無氣泡, 經典</v>
       </c>
       <c r="F59" t="str">
-        <v>杏仁香甜酒 45 ml, 波本威士忌 20 ml, 檸檬汁 30 ml, 純糖漿1tsp, 濾掉冰塊，將酒液倒入冰鎮過的淺碟香檳杯。, 勒薩多糖漬櫻桃</v>
+        <v>白蘭地 52 ml, 白蘭姆酒 7.5 ml, 香橙干邑白蘭地 7.5 ml, 鳳梨汁 7.5 ml, 安格式柑橘苦精 1 dash, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲, 糖漬櫻桃</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>冰鎮淺碟香檳杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I59" t="str">
         <v>建議物</v>
       </c>
       <c r="J59" t="str">
-        <v>當代最受歡迎的酸酒之一，義大利苦杏仁酒的濃郁核果甜香與新鮮檸檬汁完美中和，呈現如檸檬塔般的美味。</v>
+        <v>記載於19世紀末歐洲酒譜，向大航海時代威震七海的東印度公司致敬。以法國優質干邑白蘭地為基石，調和大中央利口酒、少許覆盆子糖漿與紅石榴汁。深沉的白蘭地木質單寧被熱帶橙皮與香料氣息層層包覆，酒體金紅澄澈，散發著大航海時代運回歐洲的珍貴異國香料風情。</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>東印度大樓  East India House</v>
+        <v>東方  Oriental</v>
       </c>
       <c r="B60">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C60">
         <v>4</v>
@@ -2304,10 +2301,10 @@
         <v>3</v>
       </c>
       <c r="E60" t="str">
-        <v>白蘭地, 無氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F60" t="str">
-        <v>白蘭地 52 ml, 白蘭姆酒 7.5 ml, 香橙干邑白蘭地 7.5 ml, 鳳梨汁 7.5 ml, 安格式柑橘苦精 1 dash, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲, 糖漬櫻桃</v>
+        <v>裸麥威士忌 45 ml, 香橙干邑白蘭地 20 ml, 法式甜香艾酒 20 ml, 檸檬汁 15 ml, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯, 勒薩多糖漬櫻桃</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2319,91 +2316,91 @@
         <v>建議物</v>
       </c>
       <c r="J60" t="str">
-        <v>向大航海時代的東印度公司致敬，白蘭地配上紅石榴與橙皮甜酒，散發濃郁的熱帶辛香料與東方異國風情。</v>
+        <v>出自1924年Harry McElhone的《Cocktails by ABC》。黑麥威士忌與義大利紅甜苦艾酒的厚實基調中，大膽注入新鮮現榨柳橙汁與白庫拉索橙皮酒。東方異國情調的甜美柑橘果香，柔化了黑麥威士忌的剛猛辛辣，入口酸甜圓潤、尾韻溫暖悠長，如同一抹來自遠東神秘面紗下的暖陽。</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>東方  Oriental</v>
+        <v>林地潘趣  Woodland Punch</v>
       </c>
       <c r="B61">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D61">
         <v>3</v>
       </c>
       <c r="E61" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>蘭姆酒, 無氣泡, 經典</v>
       </c>
       <c r="F61" t="str">
-        <v>裸麥威士忌 45 ml, 香橙干邑白蘭地 20 ml, 法式甜香艾酒 20 ml, 檸檬汁 15 ml, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯, 勒薩多糖漬櫻桃</v>
+        <v>南方安逸香甜酒 60 ml, 鳳梨汁 90 ml, 紅石榴糖漿1 tsp, 蘇打水 適量</v>
       </c>
       <c r="G61" t="str">
-        <v/>
+        <v>放入冰塊，攪拌冰杯後將融水倒出。</v>
       </c>
       <c r="H61" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>加入蘇打水至滿杯，稍加攪拌。</v>
       </c>
       <c r="I61" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J61" t="str">
-        <v>1920年代的經典東方想像，黑麥威士忌與甜苦艾酒中大膽加入新鮮柳橙汁，酸甜中帶有厚實的木質尾韻。</v>
+        <v>充滿歐洲古老黑森林意象的自然系長飲。以帶有深邃杜松子與松針草本香氣的精釀琴酒為底，加入接骨木花利口酒、野生莓果泥與現榨青檸汁，頂部填滿冰鎮蘇打水。入口清脆爽冽、草本芬芳撲鼻，宛如清晨漫步於晨霧繚繞的歐洲林地，每一步都踏著沁人心脾的芬多精。</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>林地潘趣  Woodland Punch</v>
+        <v>柏林站長  Berlin Station Chief</v>
       </c>
       <c r="B62">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" t="str">
-        <v>蘭姆酒, 無氣泡, 經典</v>
+        <v>其他, 無氣泡, 經典</v>
       </c>
       <c r="F62" t="str">
-        <v>南方安逸香甜酒 60 ml, 鳳梨汁 90 ml, 紅石榴糖漿1 tsp, 蘇打水 適量</v>
+        <v>琴酒 60 ml, 艾雷島威士忌 15 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 橄欖, 檸檬皮捲, 煙燻風味馬丁尼</v>
       </c>
       <c r="G62" t="str">
-        <v>放入冰塊，攪拌冰杯後將融水倒出。</v>
+        <v/>
       </c>
       <c r="H62" t="str">
-        <v>加入蘇打水至滿杯，稍加攪拌。</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J62" t="str">
-        <v>充滿森林意象的草本派對長飲，豐富的水果與木質調琴酒交織，呈現如沐浴在晨曦森林中的清爽。</v>
+        <v>靈感源自冷戰時期間諜重鎮柏林查理檢查哨的神秘風雲。以德國黑麥威士忌或剛烈的草本藥酒為底，調和干苦艾酒與煙燻泥煤蘇格蘭威士忌。酒液深沉如夜，入口迎來乾冽的草本微苦與冷峻的泥煤木質香，厚重、內斂且充滿警惕，宛如身處東西德邊界情報站長深不可測的從容氣場。</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>柏林站長  Berlin Station Chief</v>
+        <v>柯夢波丹  Cosmopolitan</v>
       </c>
       <c r="B63">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="str">
-        <v>其他, 無氣泡, 經典</v>
+        <v>伏特加, 無氣泡, 經典</v>
       </c>
       <c r="F63" t="str">
-        <v>琴酒 60 ml, 艾雷島威士忌 15 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 橄欖, 檸檬皮捲, 煙燻風味馬丁尼</v>
+        <v>伏特加 60 ml, 蔓越莓汁 25 ml, 萊姆汁 15 ml, 純糖漿 15 ml, 君度橙酒1tsp, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲, 蔓越莓</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2415,27 +2412,27 @@
         <v>建議物</v>
       </c>
       <c r="J63" t="str">
-        <v>以冷戰時期的諜報基地柏林為靈感，剛硬的烈酒底結合深沉的草本苦甜，充滿神祕且剛烈的情報員風格。</v>
+        <v>1980年代由紐約調酒教父Toby Cecchini在彩虹酒吧完美定型，後因傳奇美劇《慾望城市》四位女主角在曼哈頓酒吧頻繁點用而紅遍全球。以柑橘伏特加為底，融入君度橙酒、新鮮蔓越莓汁與現榨萊姆汁。酒液透著璀璨晶瑩的寶石粉紅，入口酸甜明亮、果香四溢，是摩登都會獨立女性的時尚圖騰。</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>柯夢波丹  Cosmopolitan</v>
+        <v>歌劇  Opera</v>
       </c>
       <c r="B64">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E64" t="str">
-        <v>伏特加, 無氣泡, 經典</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F64" t="str">
-        <v>伏特加 60 ml, 蔓越莓汁 25 ml, 萊姆汁 15 ml, 純糖漿 15 ml, 君度橙酒1tsp, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲, 蔓越莓</v>
+        <v>琴酒 60 ml, 多寶力 15 ml, 勒薩多黑櫻桃酒 7.5 ml, 安格式柑橘苦精 1 dash, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲, 勒薩多糖漬櫻桃</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2447,27 +2444,27 @@
         <v>建議物</v>
       </c>
       <c r="J64" t="str">
-        <v>因影集《慾望城市》女主角凱莉的熱愛而風靡全球的都會時尚象徵，蔓越莓的酸甜與伏特加的俐落完美平衡。</v>
+        <v>誕生於20世紀初巴黎歌劇院旁的沙龍酒吧。琴酒的杜松子香氣中，大膽融入法國杜本內（Dubonnet）利口酒的奎寧草本苦甜，並滴入微量視界綠（Chartreuse）修道院藥草酒提香。酒體如紅寶石般透亮高貴，草本花香在口中層層綻放，宛如欣賞一場氣勢磅礴又扣人心弦的巴黎古典歌劇。</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>歌劇  Opera</v>
+        <v>沉默第三者  Silent Third</v>
       </c>
       <c r="B65">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C65">
         <v>4</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F65" t="str">
-        <v>琴酒 60 ml, 多寶力 15 ml, 勒薩多黑櫻桃酒 7.5 ml, 安格式柑橘苦精 1 dash, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲, 勒薩多糖漬櫻桃</v>
+        <v>波本威士忌 60 ml, 君度橙酒 20 ml, 萊姆汁 30 ml, 純糖漿1tsp, 安格式原味苦精 1 dash, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2479,27 +2476,27 @@
         <v>建議物</v>
       </c>
       <c r="J65" t="str">
-        <v>起源於20世紀初巴黎，琴酒基底中加入法國杜本內利口酒與微量視界綠香甜酒，風味高雅悠長如一場歌劇盛宴。</v>
+        <v>經典白蘭地側車（Sidecar）在愛爾蘭與蘇格蘭的硬漢變奏版。將傳統的干邑白蘭地替換為煙燻麥芽蘇格蘭威士忌或愛爾蘭威士忌。威士忌的煙燻麥香甘心退居幕後，充當「沉默的第三者」，烘托出君度橙酒的香甜與檸檬的酸爽，入口圓潤且尾韻帶有深邃的木質回甘。</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>沉默第三者  Silent Third</v>
+        <v>油漬馬丁尼  Dirty Martini</v>
       </c>
       <c r="B66">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>伏特加, 琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F66" t="str">
-        <v>波本威士忌 60 ml, 君度橙酒 20 ml, 萊姆汁 30 ml, 純糖漿1tsp, 安格式原味苦精 1 dash, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
+        <v>琴酒 90 ml, 法式不甜香艾酒 30 ml, 橄欖汁 20 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲, 橄欖。</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2511,12 +2508,12 @@
         <v>建議物</v>
       </c>
       <c r="J66" t="str">
-        <v>白蘭地側車（Sidecar）的威士忌變奏版，蘇格蘭威士忌的煙燻感退居幕後成為沉默的第三者，烘托出柑橘酸甜。</v>
+        <v>相傳起源於1901年紐約調酒師John O'Connor首創將橄欖汁壓入馬丁尼中，因羅斯福總統在白宮喜愛飲用而廣為人知。在冰鎮琴酒與干苦艾酒中大膽注入特製橄欖鹽水（Olive Brine），酒液呈現神秘的微混濁「髒」感，草本酒香與海洋鹹鮮美妙交織，風味獨樹一幟。</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>油漬馬丁尼  Dirty Martini</v>
+        <v>沾染到蒼白的色彩  Obituary Cocktail</v>
       </c>
       <c r="B67">
         <v>32</v>
@@ -2525,13 +2522,13 @@
         <v>5</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" t="str">
-        <v>伏特加, 琴酒, 無氣泡, 經典</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F67" t="str">
-        <v>琴酒 90 ml, 法式不甜香艾酒 30 ml, 橄欖汁 20 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲, 橄欖。</v>
+        <v>琴酒 45 ml, 義式不甜香艾酒 7.5 ml, 義式甜香艾酒 7.5 ml,</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2540,82 +2537,82 @@
         <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I67" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J67" t="str">
-        <v>在傳統乾馬丁尼中加入橄欖鹽水（Olive Brine），酒液呈現微混濁（髒）狀態，帶來獨特的鹹鮮與海洋風味。</v>
+        <v>又名「訃聞雞尾酒」，是紐奧良調酒史上帶著哥德式神秘色彩的暗黑經典。在純粹乾冽的琴酒與干苦艾酒馬丁尼中，滴入神秘的綠色苦艾酒（Absinthe）。入口極度冰涼寒烈，八角茴香與苦艾草香如幽靈般在舌尖遊蕩，後勁深邃肅穆，令人不禁對其傳奇配方肅然起敬。</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>沾染到蒼白的色彩  Obituary Cocktail</v>
+        <v>法式豆漿</v>
       </c>
       <c r="B68">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D68">
         <v>1</v>
       </c>
       <c r="E68" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>其他, 無氣泡</v>
       </c>
       <c r="F68" t="str">
-        <v>琴酒 45 ml, 義式不甜香艾酒 7.5 ml, 義式甜香艾酒 7.5 ml,</v>
+        <v>苦艾酒 30 ml, 白巧克力香甜酒 30 ml, 鮮奶 30 ml, 班尼迪克丁 1 tsp</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮淺碟香檳杯</v>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J68" t="str">
-        <v>又稱「訃聞雞尾酒」，紐奧良的經典禁忌配方。在乾馬丁尼中滴入苦艾酒，風味強烈、乾冽，後勁令人敬畏。</v>
+        <v>當代台法跨文化撞擊的驚艷創意融合調酒。將台灣傳統現磨濃郁無糖豆漿，低溫慢速融入法國頂級干邑白蘭地或杏仁香甜酒，佐以少許黑糖與現刨肉豆蔻粉。大豆天然的醇厚植物奶香，被白蘭地的葡萄果香與橡木桶香優雅提亮，口感如天鵝絨般絲滑溫潤，顛覆你對調酒的所有想像。</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>法式豆漿</v>
+        <v>法蘭西斯‧亞伯特  Francis Albert</v>
       </c>
       <c r="B69">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D69">
         <v>1</v>
       </c>
       <c r="E69" t="str">
-        <v xml:space="preserve">其他, 無氣泡, </v>
+        <v>琴酒, 威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F69" t="str">
-        <v>苦艾酒 30 ml, 白巧克力香甜酒 30 ml, 鮮奶 30 ml, 班尼迪克丁 1 tsp</v>
+        <v>琴酒 45 ml, 日本威士忌 45 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>冰鎮淺碟香檳杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I69" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J69" t="str">
-        <v>極具創意的當代亞洲融合調酒，將法式香甜酒與傳統豆漿結合，碰撞出滑順、帶有堅果奶香的奇妙新滋味。</v>
+        <v>向美國傳奇歌王法蘭克·辛納屈（Frank Sinatra，本名Francis Albert）致敬的極致硬漢調酒。由日本傳奇調酒大師在東京所創，大膽將辛納屈生前最鍾愛的野生火雞（Wild Turkey）101高濃度波本威士忌，與坦奎利（Tanqueray）琴酒以1:1等比例攪拌。純烈乾脆、毫無糖分妥協，散發著老派爵士歌王桀驁不馴的靈魂。</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>法蘭西斯‧亞伯特  Francis Albert</v>
+        <v>法蘭西集團  French Connection</v>
       </c>
       <c r="B70">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C70">
         <v>5</v>
@@ -2624,155 +2621,155 @@
         <v>1</v>
       </c>
       <c r="E70" t="str">
-        <v>琴酒, 威士忌, 無氣泡, 經典</v>
+        <v>白蘭地, 無氣泡, 經典</v>
       </c>
       <c r="F70" t="str">
-        <v>琴酒 45 ml, 日本威士忌 45 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。</v>
+        <v>白蘭地 45 ml, 杏仁香甜酒 15 ml,</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮古典杯</v>
       </c>
       <c r="I70" t="str">
         <v/>
       </c>
       <c r="J70" t="str">
-        <v>以傳奇歌王法蘭克·辛納屈的本名命名。大膽將野生火雞波本威士忌與坦奎利琴酒等比例混合，極度剛烈硬派。</v>
+        <v>誕生於1970年代，以金獎同名黑幫警匪電影《霹靂神探（The French Connection）》命名。將法國頂級干邑白蘭地與義大利帝薩諾（Disaronno）苦杏仁酒以1:1等比例在古典杯中攪拌。白蘭地的深邃木質果香被杏仁糖蜜的溫潤甜美完美包覆，口感奢華圓潤，散發著歐陸黑幫教父般的雍容風度。</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>法蘭西集團  French Connection</v>
+        <v>泡泡  Spumoni</v>
       </c>
       <c r="B71">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C71">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" t="str">
-        <v>白蘭地, 無氣泡, 經典</v>
+        <v>其他, 有氣泡, 經典</v>
       </c>
       <c r="F71" t="str">
-        <v>白蘭地 45 ml, 杏仁香甜酒 15 ml,</v>
+        <v>肯巴利苦酒 20 ml, 通寧水 190 ml, 葡萄柚汁 40 ml, 2.. 將酒液倒入冰鎮過的颶風杯，加入冰塊至九分滿。, 3. 加入通寧水至滿杯，稍加攪拌。, 葡萄柚皮捲</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>冰鎮古典杯</v>
+        <v>冰鎮颶風杯</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J71" t="str">
-        <v>干邑白蘭地與義大利杏仁酒的奢華結合，名字源於經典同名電影，口感圓潤、甜美，散發濃郁歐陸貴族氣息。</v>
+        <v>發源於義大利、在日本各大日系酒吧發揚光大的清爽開胃聖品。「Spumoni」在義大利語中意為「泡沫」。以金巴利（Campari）苦甜利口酒為底，加入新鮮現榨葡萄柚汁，填入冰鎮通寧水。艷麗的粉紅色酒液中氣泡升騰，葡萄柚果酸與金巴利的草本苦甜完美契合，極致清爽解膩。</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>泡泡  Spumoni</v>
+        <v>波本庫斯塔  Bourbon Crusta</v>
       </c>
       <c r="B72">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D72">
         <v>3</v>
       </c>
       <c r="E72" t="str">
-        <v>其他, 有氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F72" t="str">
-        <v>肯巴利苦酒 20 ml, 通寧水 190 ml, 葡萄柚汁 40 ml, 2.. 將酒液倒入冰鎮過的颶風杯，加入冰塊至九分滿。, 3. 加入通寧水至滿杯，稍加攪拌。, 葡萄柚皮捲</v>
+        <v>波本威士忌 60 ml, 君度橙酒 15 ml, 勒薩多黑櫻桃酒 15 ml, 檸檬汁 15 ml, 安格式柑橘苦精 2 dash, 濾掉冰塊，將酒液倒入冰鎮過糖口馬丁尼杯。, 柳橙皮捲</v>
       </c>
       <c r="G72" t="str">
-        <v/>
+        <v>馬丁尼。1. 以馬丁尼杯製作糖口杯，並冰鎮。</v>
       </c>
       <c r="H72" t="str">
-        <v>冰鎮颶風杯</v>
+        <v/>
       </c>
       <c r="I72" t="str">
         <v>建議物</v>
       </c>
       <c r="J72" t="str">
-        <v>起源於義大利的消暑聖品，金巴利（Campari）的苦甜、葡萄柚汁的酸爽與通寧水汽泡結合，極具解膩效果。</v>
+        <v>起源於1850年代紐奧良義大利調酒先驅Joseph Santini發明的Crusta系列。杯口均勻沾滿一整圈晶瑩剔透的粗粒砂糖，杯壁內鑲嵌一整條削下的完整柳橙皮。波本威士忌的厚實橡木香氣，在橙皮精油、黑櫻桃酒與檸檬汁襯托下顯得無比尊榮，每一口嘴唇觸碰糖圈皆帶來極致奢華感。</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>波本庫斯塔  Bourbon Crusta</v>
+        <v>海明威黛綺莉  Hemingway Daiquiri</v>
       </c>
       <c r="B73">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E73" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>蘭姆酒, 無氣泡, 經典</v>
       </c>
       <c r="F73" t="str">
-        <v>波本威士忌 60 ml, 君度橙酒 15 ml, 勒薩多黑櫻桃酒 15 ml, 檸檬汁 15 ml, 安格式柑橘苦精 2 dash, 濾掉冰塊，將酒液倒入冰鎮過糖口馬丁尼杯。, 柳橙皮捲</v>
+        <v>白蘭姆酒 60 ml, 勒薩多黑櫻桃酒 10 ml, 純糖漿 30 ml, 檸檬汁 30 ml, 葡萄柚汁 20 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 葡萄柚皮捲</v>
       </c>
       <c r="G73" t="str">
-        <v>馬丁尼。1. 以馬丁尼杯製作糖口杯，並冰鎮。</v>
+        <v/>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I73" t="str">
         <v>建議物</v>
       </c>
       <c r="J73" t="str">
-        <v>19世紀新奧爾良的華麗經典。杯口沾滿大顆白糖，並用整圈柳橙皮線條裝飾，波本威士忌在糖圈襯托下更顯香醇。</v>
+        <v>大文豪海明威旅居古巴哈瓦那期間，在傳奇酒吧「小佛羅里達（El Floridita）」的專屬配方。因海明威患有糖尿病且嗜酒如命，他要求調酒師「不加一粒糖、酒量加倍（Papa Doble）」，並加入葡萄柚汁與黑櫻桃利口酒調味。果酸凌厲、酒體剛勁，散發著文學硬漢與加勒比海浪搏擊的豪邁風範。</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>海明威黛綺莉  Hemingway Daiquiri</v>
+        <v>海風  Sea Breeze</v>
       </c>
       <c r="B74">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E74" t="str">
-        <v>蘭姆酒, 無氣泡, 經典</v>
+        <v>伏特加, 無氣泡, 經典</v>
       </c>
       <c r="F74" t="str">
-        <v>白蘭姆酒 60 ml, 勒薩多黑櫻桃酒 10 ml, 純糖漿 30 ml, 檸檬汁 30 ml, 葡萄柚汁 20 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 葡萄柚皮捲</v>
+        <v>伏特加 45 ml, 蔓越莓汁 60 ml, 葡萄柚汁 60 ml, 通寧水 30 ml, 2. 將酒液倒入冰鎮過的颶風杯，加入冰塊至九分滿。, 3. 加入通寧水至滿杯，稍加攪拌。, 葡萄柚皮捲</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮颶風杯</v>
       </c>
       <c r="I74" t="str">
         <v>建議物</v>
       </c>
       <c r="J74" t="str">
-        <v>大文豪海明威在哈瓦那「小佛羅裡達」酒吧的專屬配方。因為他患有糖尿病，所以要求不加糖、雙倍烈酒，並加入葡萄柚汁。</v>
+        <v>起源於1920年代，在1980年代全美海岸度假勝地全面爆紅的經典消暑長飲。在極致純淨的伏特加中，注入三分之二蔓越莓汁與三分之一葡萄柚汁。雙重紅色水果的酸甜微澀與晶亮冰塊撞擊，宛如加州陽光下帶著海鹽微鹹與沁涼的海風拂過臉頰，暢快俐落、毫無負擔。</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>海風  Sea Breeze</v>
+        <v>湯姆可林斯  Tom Collins</v>
       </c>
       <c r="B75">
         <v>12</v>
@@ -2781,94 +2778,94 @@
         <v>2</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E75" t="str">
-        <v>伏特加, 無氣泡, 經典</v>
+        <v>琴酒, 有氣泡, 經典</v>
       </c>
       <c r="F75" t="str">
-        <v>伏特加 45 ml, 蔓越莓汁 60 ml, 葡萄柚汁 60 ml, 通寧水 30 ml, 2. 將酒液倒入冰鎮過的颶風杯，加入冰塊至九分滿。, 3. 加入通寧水至滿杯，稍加攪拌。, 葡萄柚皮捲</v>
+        <v>老湯姆琴酒 45 ml, 蘇打水 135 ml, 檸檬汁 15 ml, 純糖漿 15 ml, 2．將酒液倒入冰鎮過的可林杯，加入冰塊至八分滿。, 3．再加入蘇打水至滿杯，稍加攪拌。, 柳橙片, 糖漬櫻桃</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>冰鎮颶風杯</v>
+        <v>冰鎮可林杯</v>
       </c>
       <c r="I75" t="str">
         <v>建議物</v>
       </c>
       <c r="J75" t="str">
-        <v>1980年代風靡全美海岸的清爽長飲，伏特加底與蔓越莓汁、葡萄柚汁結合，如海風拂面般酸甜消暑。</v>
+        <v>源於1874年風靡紐約與倫敦的「湯姆可林斯惡作劇」傳奇。以帶有微甜草本風味的老湯姆琴酒（Old Tom Gin）為靈魂，加入新鮮檸檬汁、糖漿，最後在可林杯中注滿冒泡的冰鎮蘇打水。微甜果酸與碳酸氣泡在舌尖躍動，是兩個世紀以來全世界公認最清爽解渴的夏日琴酒長飲。</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>湯姆可林斯  Tom Collins</v>
+        <v>猛牛  Brave Bull</v>
       </c>
       <c r="B76">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E76" t="str">
-        <v>琴酒, 有氣泡, 經典</v>
+        <v>龍舌蘭, 無氣泡, 經典</v>
       </c>
       <c r="F76" t="str">
-        <v>老湯姆琴酒 45 ml, 蘇打水 135 ml, 檸檬汁 15 ml, 純糖漿 15 ml, 2．將酒液倒入冰鎮過的可林杯，加入冰塊至八分滿。, 3．再加入蘇打水至滿杯，稍加攪拌。, 柳橙片, 糖漬櫻桃</v>
+        <v>龍舌蘭 60 ml, 咖啡香甜酒 20 ml</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>冰鎮可林杯</v>
+        <v>冰鎮古典杯</v>
       </c>
       <c r="I76" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J76" t="str">
-        <v>源於1874年風靡倫敦與紐約的「湯姆可林斯惡作劇」。老湯姆琴酒、檸檬汁與蘇打水的組合，是夏日長飲的終極經典。</v>
+        <v>黑色俄羅斯（Black Russian）在熱情墨西哥的狂野變奏版。將傳統純淨的伏特加，替換為帶有濃郁大地植物風土與胡椒辛香的墨西哥龍舌蘭酒，搭配甘露（Kahlúa）咖啡利口酒。咖啡的厚重烘焙甜香被龍舌蘭的狂野氣息瞬間撕開，入口剛烈奔放、充滿公牛衝撞般的野性爆發力。</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>猛牛  Brave Bull</v>
+        <v>猴上腺素  Monkey Gland</v>
       </c>
       <c r="B77">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C77">
         <v>4</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77" t="str">
-        <v>龍舌蘭, 無氣泡, 經典</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F77" t="str">
-        <v>龍舌蘭 60 ml, 咖啡香甜酒 20 ml</v>
+        <v>琴酒 30 ml, 柳橙汁 30 ml, 苦艾酒 1 dash, 紅石榴糖漿 1 dash, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>冰鎮古典杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J77" t="str">
-        <v>黑色俄羅斯（Black Russian）的龍舌蘭變奏版。龍舌蘭特有的植物大地香氣與咖啡香甜酒結合，剛烈且充滿野性。</v>
+        <v>1920年代由巴黎哈里紐約酒吧大師Harry MacElhone創作。名字戲謔地取自當時歐洲名流間盛行的俄裔醫生「移植猴子腺體以追求長生不老」的荒誕醫學手術。琴酒草本與現榨新鮮柳橙汁結合，加入少許紅石榴糖漿並以苦艾酒涮杯，風味甜美中帶著神秘草藥香，風格大膽獨特。</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>猴上腺素  Monkey Gland</v>
+        <v>王者的微笑  Royal Smile</v>
       </c>
       <c r="B78">
         <v>22</v>
@@ -2880,10 +2877,10 @@
         <v>3</v>
       </c>
       <c r="E78" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>琴酒, 白蘭地, 無氣泡, 經典</v>
       </c>
       <c r="F78" t="str">
-        <v>琴酒 30 ml, 柳橙汁 30 ml, 苦艾酒 1 dash, 紅石榴糖漿 1 dash, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
+        <v>蘋果白蘭地 45 ml, 琴酒 15 ml, 紅石榴糖漿 15 ml, 檸檬汁 15 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -2895,27 +2892,27 @@
         <v>建議物</v>
       </c>
       <c r="J78" t="str">
-        <v>1920年代由巴黎哈里紐約酒吧大師創作，大膽加入苦艾酒與紅石榴，名字諷刺了當時盛行的「猴子器官移植長生術」。</v>
+        <v>20世紀初英國調酒師為了款待來訪的歐洲王室貴冑所創之經典。精選諾曼第蘋果白蘭地（Calvados）與倫敦乾琴酒，調和新鮮檸檬汁與紅石榴糖漿。酒液呈現明亮優雅的金橙色澤，蘋果芬芳與杜松子草本在酸甜中達成極致平衡，入口明朗愉悅，宛如尊貴國王在品味後展露的滿意微笑。</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>王者的微笑  Royal Smile</v>
+        <v>玫瑰  Rose</v>
       </c>
       <c r="B79">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" t="str">
-        <v>琴酒, 白蘭地, 無氣泡, 經典</v>
+        <v>其他, 無氣泡, 經典</v>
       </c>
       <c r="F79" t="str">
-        <v>蘋果白蘭地 45 ml, 琴酒 15 ml, 紅石榴糖漿 15 ml, 檸檬汁 15 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲</v>
+        <v>法式不甜香艾酒 60 ml, 勒薩多櫻桃蒸餾酒 30 ml, 覆盆子糖漿 1 tsp, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 糖漬櫻桃</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -2927,27 +2924,27 @@
         <v>建議物</v>
       </c>
       <c r="J79" t="str">
-        <v>20世紀初為了款待王室成員而調製，蘋果白蘭地與琴酒碰撞出高雅的果香，金黃酒液宛如國王滿意的微笑。</v>
+        <v>1920年代巴黎「咆哮的二十年代（Années folles）」最著名的沙龍雞尾酒。由巴黎查塔姆飯店調酒師Johnny Mitta發明。以干苦艾酒為底，融入櫻桃白蘭地（Kirsch）與天然紅石榴糖漿。酒液如盛開的粉紅玫瑰般嬌豔動人，口感乾冽帶有淡雅櫻桃果香，充滿海明威與費茲傑羅筆下浪漫巴黎的文藝氣息。</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>玫瑰  Rose</v>
+        <v>琴瑞奇  Gin Rickey</v>
       </c>
       <c r="B80">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E80" t="str">
-        <v>其他, 無氣泡, 經典</v>
+        <v>琴酒, 有氣泡, 經典</v>
       </c>
       <c r="F80" t="str">
-        <v>法式不甜香艾酒 60 ml, 勒薩多櫻桃蒸餾酒 30 ml, 覆盆子糖漿 1 tsp, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 糖漬櫻桃</v>
+        <v>琴酒 45 ml, 檸檬汁15 ml, 雪碧 180 ml</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -2956,30 +2953,30 @@
         <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I80" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J80" t="str">
-        <v>1920年代巴黎「瘋狂年代」的象徵，櫻桃白蘭地與乾苦艾酒交織出優雅的粉紅玫瑰色澤，口感乾冽帶甜。</v>
+        <v>1880年代誕生於華盛頓特區休梅克酒吧，以喬·瑞奇上校命名。這款調酒最大的特色在於「完全不加一滴糖」！僅以琴酒、新鮮現切萊姆汁與冰鎮蘇打水在球杯中直調。極度乾冽、純淨無瑕，杜松子草本與萊姆果酸在氣泡中直接衝擊味蕾，是炎夏裡最硬派、最無負擔的純粹解渴聖品。</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>琴瑞奇  Gin Rickey</v>
+        <v>琴蕾  Gimlet</v>
       </c>
       <c r="B81">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D81">
         <v>4</v>
       </c>
       <c r="E81" t="str">
-        <v>琴酒, 有氣泡, 經典</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F81" t="str">
-        <v>琴酒 45 ml, 檸檬汁15 ml, 雪碧 180 ml</v>
+        <v>琴酒 60 ml, 檸檬汁 20 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲,</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -2988,143 +2985,143 @@
         <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I81" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J81" t="str">
-        <v>1880年代誕生於華盛頓，傳統上完全不加糖，僅靠琴酒、新鮮萊姆與蘇打水，極致追求極度乾爽、純粹的解渴風味。</v>
+        <v>起源於19世紀英國皇家海軍，相傳由金萊特（Gimlet）海軍軍醫首創將琴酒混合濃縮萊姆汁以預防壞血病。後來在雷蒙·錢德勒的冷硬派推理名著《漫長的告別》中名垂青史，名句提到：「真正的琴蕾是琴酒與玫瑰牌萊姆汁等量調和，不加其他東西」。酒體銳利如錐，酸甜緊緻，散發著孤傲硬漢的沉穩與深情。</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>琴蕾  Gimlet</v>
+        <v>琴通寧  Gin Tonic</v>
       </c>
       <c r="B82">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E82" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>琴酒, 有氣泡, 經典</v>
       </c>
       <c r="F82" t="str">
-        <v xml:space="preserve">琴酒 60 ml, 檸檬汁 20 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲, </v>
+        <v>琴酒 45 ml, 通寧水 190 ml, 檸檬角</v>
       </c>
       <c r="G82" t="str">
-        <v/>
+        <v>１．可林杯放入冰塊，攪拌冰杯後將融水倒出。。２．倒入琴酒，擠入檸檬汁，最後補滿通寧水，稍加攪拌。。檸檬角。消暑解熱必備良方</v>
       </c>
       <c r="H82" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮可林杯</v>
       </c>
       <c r="I82" t="str">
         <v>建議物</v>
       </c>
       <c r="J82" t="str">
-        <v>起源於19世紀英國海軍，傳說由金萊特（Gimlet）軍醫首創讓水兵混合琴酒與萊姆汁以預防壞血病，現為硬漢派代表。</v>
+        <v>起源於大航海時代英國東印度公司駐印軍隊的防瘧良方。將含有微苦奎寧的通寧水加入烈性琴酒中以利服藥，意外造就了全世界最偉大的長飲奇蹟。通寧水的微苦氣泡將琴酒內蘊的杜松子、胡荽籽與柑橘皮精油瞬間蒸騰釋放，杯口青檸角點睛，是測試一間酒吧基酒水準的終極試金石。</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>琴通寧  Gin Tonic</v>
+        <v>琴霸克  Gin Buck</v>
       </c>
       <c r="B83">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C83">
         <v>2</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" t="str">
         <v>琴酒, 有氣泡, 經典</v>
       </c>
       <c r="F83" t="str">
-        <v>琴酒 45 ml, 通寧水 190 ml, 檸檬角</v>
+        <v>琴酒 45 ml, 辛口薑汁汽水 135 ml, 檸檬角</v>
       </c>
       <c r="G83" t="str">
-        <v>１．可林杯放入冰塊，攪拌冰杯後將融水倒出。。２．倒入琴酒，擠入檸檬汁，最後補滿通寧水，稍加攪拌。。檸檬角。消暑解熱必備良方</v>
+        <v>1. 長飲杯放入冰塊，攪拌冰杯後將融水倒出。。2．倒入琴酒，擠入檸檬汁，最後補滿薑汁汽水，稍加攪拌。。檸檬角。暢快享受琴酒的必試飲法</v>
       </c>
       <c r="H83" t="str">
-        <v>冰鎮可林杯</v>
+        <v>冰鎮長飲杯</v>
       </c>
       <c r="I83" t="str">
         <v>建議物</v>
       </c>
       <c r="J83" t="str">
-        <v>起源於東印度公司的醫療良方。通寧水中的奎寧與琴酒結合，如今成為全世界最普及、最能測試琴酒本質的殿堂長飲。</v>
+        <v>誕生於19世紀末的傳統「鹿肉風（Buck）」長飲調酒。以英式琴酒為基底，佐以新鮮檸檬汁，最後填滿帶有辛辣香氣的薑汁汽水（Ginger Ale）。生薑的溫熱辛香與琴酒的杜松子草本在氣泡中完美融合，酸甜開胃中帶著回甘的微辣爽快感，無論春夏秋冬皆極度易飲。</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>琴霸克  Gin Buck</v>
+        <v>瑪格莉特  Margarita</v>
       </c>
       <c r="B84">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E84" t="str">
-        <v>琴酒, 有氣泡, 經典</v>
+        <v>龍舌蘭, 無氣泡, 經典</v>
       </c>
       <c r="F84" t="str">
-        <v>琴酒 45 ml, 辛口薑汁汽水 135 ml, 檸檬角</v>
+        <v>龍舌蘭 60 ml, 君度橙酒 20 ml, 萊姆汁 30 ml, 純糖漿 15 ml, 濾掉冰塊，將酒液倒入冰鎮過的鹽口馬丁尼杯。, 檸檬片,</v>
       </c>
       <c r="G84" t="str">
-        <v>1. 長飲杯放入冰塊，攪拌冰杯後將融水倒出。。2．倒入琴酒，擠入檸檬汁，最後補滿薑汁汽水，稍加攪拌。。檸檬角。暢快享受琴酒的必試飲法</v>
+        <v>１．以馬丁尼杯製作鹽口杯，並冰鎮。</v>
       </c>
       <c r="H84" t="str">
-        <v>冰鎮長飲杯</v>
+        <v>馬丁尼杯</v>
       </c>
       <c r="I84" t="str">
         <v>建議物</v>
       </c>
       <c r="J84" t="str">
-        <v>傳統「鹿肉風」長飲調酒，琴酒與薑汁汽水、檸檬汁結合，帶有辛辣的薑香與明亮的柑橘酸。</v>
+        <v>全球銷量冠軍的龍舌蘭傳奇調酒。相傳是墨西哥調酒師為了紀念不幸在狩獵意外中中流彈身亡的愛人Margarita而作。以龍舌蘭酒、君度橙酒與新鮮萊姆汁調和，杯口精心抹上一圈海鹽圈。入口鹽粒微鹹瞬間激發出龍舌蘭的草本甘甜與柑橘酸爽，被無數酒客比喻為「懷念愛人時深情又微鹹的淚水」。</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>瑪格莉特  Margarita</v>
+        <v>瑪莉．畢克馥  Mary Pickford</v>
       </c>
       <c r="B85">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E85" t="str">
-        <v>龍舌蘭, 無氣泡, 經典</v>
+        <v>蘭姆酒, 無氣泡, 經典</v>
       </c>
       <c r="F85" t="str">
-        <v>龍舌蘭 60 ml, 君度橙酒 20 ml, 萊姆汁 30 ml, 純糖漿 15 ml, 濾掉冰塊，將酒液倒入冰鎮過的鹽口馬丁尼杯。, 檸檬片,</v>
+        <v>陳年蘭姆酒 60 ml, 鳳梨汁 45 ml, 紅石榴糖漿 10 ml, 勒薩多黑櫻桃酒1tsp。, 勒薩多糖漬櫻桃</v>
       </c>
       <c r="G85" t="str">
-        <v>１．以馬丁尼杯製作鹽口杯，並冰鎮。</v>
+        <v/>
       </c>
       <c r="H85" t="str">
-        <v>馬丁尼杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I85" t="str">
         <v>建議物</v>
       </c>
       <c r="J85" t="str">
-        <v>調酒界最浪漫的傳奇。傳說為墨西哥調酒師為了紀念不幸早逝的戀人Margarita而作，杯口的鹽圈象徵懷念的淚水。</v>
+        <v>1920年代由哈瓦那國民飯店調酒師為造訪古巴的美國無聲電影時代好萊塢巨星「美國甜心」瑪莉·畢克馥量身打造。以古巴白蘭姆酒為底，加入現榨新鮮鳳梨汁、少許黑櫻桃酒與紅石榴糖漿。酒液呈嬌豔的緋粉色，口感圓潤酸甜、熱帶果香四溢，優雅地詮釋出無聲黑白影壇初代巨星的甜美風采。</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>瑪莉．畢克馥  Mary Pickford</v>
+        <v>瓦倫西亞  Valencia</v>
       </c>
       <c r="B86">
         <v>18</v>
@@ -3136,190 +3133,190 @@
         <v>3</v>
       </c>
       <c r="E86" t="str">
-        <v>蘭姆酒, 無氣泡, 經典</v>
+        <v>白蘭地, 無氣泡, 經典</v>
       </c>
       <c r="F86" t="str">
-        <v>陳年蘭姆酒 60 ml, 鳳梨汁 45 ml, 紅石榴糖漿 10 ml, 勒薩多黑櫻桃酒1tsp。, 勒薩多糖漬櫻桃</v>
+        <v>杏桃白蘭地 45 ml, 檸檬汁 10 ml, 柳橙汁 80 ml, 安格式柑橘苦精2 dashes。, 柳橙皮捲,</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮古典杯</v>
       </c>
       <c r="I86" t="str">
         <v>建議物</v>
       </c>
       <c r="J86" t="str">
-        <v>1920年代古巴調酒師為造訪哈瓦那的美國無聲電影甜心天后瑪莉·畢克馥量身打造，充滿熱帶櫻桃與鳳梨香甜。</v>
+        <v>以盛產頂級多汁甜橙的西班牙地中海陽光古城瓦倫西亞命名。以香甜濃郁的杏桃白蘭地（Apricot Brandy）為靈魂基酒，大膽融入大量現榨鮮甜柳橙汁，滴入橙皮苦精增添層次。金黃燦爛的酒體散發出極致明媚的果香，酸甜適口、溫潤怡人，每一口都彷彿沐浴在南歐蔚藍海岸溫暖明亮的陽光之中。</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>瓦倫西亞  Valencia</v>
+        <v>白色佳人  White Lady</v>
       </c>
       <c r="B87">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87" t="str">
-        <v>白蘭地, 無氣泡, 經典</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F87" t="str">
-        <v>杏桃白蘭地 45 ml, 檸檬汁 10 ml, 柳橙汁 80 ml, 安格式柑橘苦精2 dashes。, 柳橙皮捲,</v>
+        <v>琴酒 40 ml, 君度橙酒 20 ml, 萊姆汁 15 ml, 純糖漿 1 tsp, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>冰鎮古典杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I87" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J87" t="str">
-        <v>以西班牙著名的柳橙產地瓦倫西亞命名，杏桃白蘭地與大量新鮮柳橙汁結合，散發滿滿的地中海陽光果香。</v>
+        <v>1929年由傳奇調酒大師Harry MacElhone在巴黎哈里紐約酒吧完美定型。琴酒的杜松子草本、君度橙酒的香甜與現榨檸檬汁以精準比例混合，加入蛋白劇烈搖盪出雪白綿密的泡沫頂部。純淨無瑕的乳白酒液散發著高貴純潔的氣質，口感絲滑細膩、酸甜平衡，被譽為調酒世界裡永不褪色的純白婚紗。</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>白色佳人  White Lady</v>
+        <v>白色俄羅斯  White Russian</v>
       </c>
       <c r="B88">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C88">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D88">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E88" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>伏特加, 無氣泡, 經典</v>
       </c>
       <c r="F88" t="str">
-        <v>琴酒 40 ml, 君度橙酒 20 ml, 萊姆汁 15 ml, 純糖漿 1 tsp, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。</v>
+        <v>伏特加 60 ml, 咖啡香甜酒 30 ml, 鮮奶 30 ml, 咖啡、鮮奶</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮古典杯</v>
       </c>
       <c r="I88" t="str">
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>1929年由調酒大師Harry MacElhone在巴黎完美定型，琴酒、橙酒與檸檬汁的黃金比例，口感絲滑、高雅純潔。</v>
+        <v>1960年代誕生於黑色俄羅斯的優雅升級版，更因1998年科恩兄弟經典邪典電影《謀殺綠腳趾》中男主角督爺（The Dude）整天捧著狂飲而徹底封神。在濃郁咖啡伏特加的基底上，輕柔浮上一層冰涼厚實的鮮奶油。黑白分明的視覺在舌尖化開如微醺冰卡布奇諾般的絲滑甜美，令人徹底放鬆沉淪。</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>白色俄羅斯  White Russian</v>
+        <v>白色吊帶襪</v>
       </c>
       <c r="B89">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C89">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E89" t="str">
-        <v>伏特加, 無氣泡, 經典</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F89" t="str">
-        <v>伏特加 60 ml, 咖啡香甜酒 30 ml, 鮮奶 30 ml, 咖啡、鮮奶</v>
+        <v>陳年蘭姆酒 60 ml, 香橙干邑白蘭地 22 ml, 杏仁糖漿 15 ml, 檸檬汁 7.5 ml, 柳橙汁 7.5 ml, 安格式原味苦精 1 dash, 安格式柑橘苦精 1 drop。, 鳳梨片, 糖漬櫻桃</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>冰鎮古典杯</v>
+        <v>冰鎮Tiki杯</v>
       </c>
       <c r="I89" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J89" t="str">
-        <v>黑色俄羅斯的經典變奏版，在咖啡伏特加底之上鋪上一層鮮奶油，因經典電影《謀殺綠腳趾》主角的狂熱而爆紅。</v>
+        <v>充滿現代挑逗感與視覺誘惑的甜點系調酒。以純淨伏特加或白蘭姆酒為底，融入香甜椰子香甜酒、白巧克力與新鮮鮮奶油。純白無瑕的酒液如同一層輕薄細膩的絲質蕾絲，入口椰香濃郁、奶香滑順，甜而不膩，帶著一絲若即若離的微醺挑逗，是夜色深沉時最迷人的溫柔陷阱。</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>白色吊帶襪</v>
+        <v>白蘭地亞歷山大  Brandy Alexander</v>
       </c>
       <c r="B90">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E90" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>白蘭地, 無氣泡, 經典</v>
       </c>
       <c r="F90" t="str">
-        <v>陳年蘭姆酒 60 ml, 香橙干邑白蘭地 22 ml, 杏仁糖漿 15 ml, 檸檬汁 7.5 ml, 柳橙汁 7.5 ml, 安格式原味苦精 1 dash, 安格式柑橘苦精 1 drop。, 鳳梨片, 糖漬櫻桃</v>
+        <v>白蘭地 30 ml, 黑巧克力香甜酒 30 ml, 鮮奶油 30 ml, 2．加入冰塊搖盪均勻，濾冰倒入已冰鎮的馬丁尼杯。, 荳蔻粉, 可可粉</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>冰鎮Tiki杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I90" t="str">
         <v>建議物</v>
       </c>
       <c r="J90" t="str">
-        <v>充滿現代挑逗感與視覺誘惑的甜點系調酒，乳白色澤下帶有細緻的椰香與奶香，柔順好入口。</v>
+        <v>亞歷山大調酒在20世紀最受推崇的升級版本。將原本的琴酒替換為尊貴醇厚的法國干邑白蘭地，與棕色可可香甜酒、新鮮鮮奶油等比例搖盪，頂部灑上現磨肉豆蔻粉。白蘭地的橡木果香被香濃可可與天鵝絨般的奶泡完美烘托，入口宛如頂級液態松露巧克力冰淇淋，是奢華餐後酒的永恆代表。</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>白蘭地亞歷山大  Brandy Alexander</v>
+        <v>白蘭地庫斯塔  Brandy Crusta</v>
       </c>
       <c r="B91">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C91">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E91" t="str">
         <v>白蘭地, 無氣泡, 經典</v>
       </c>
       <c r="F91" t="str">
-        <v>白蘭地 30 ml, 黑巧克力香甜酒 30 ml, 鮮奶油 30 ml, 2．加入冰塊搖盪均勻，濾冰倒入已冰鎮的馬丁尼杯。, 荳蔻粉, 可可粉</v>
+        <v>白蘭地 60 ml, 勒薩多黑櫻桃酒 10 ml, 君度橙酒 10 ml, 檸檬汁 10 ml, 濾掉冰塊，倒入已冰鎮的糖口杯。, 檸檬皮捲</v>
       </c>
       <c r="G91" t="str">
-        <v/>
+        <v>1. 製作糖口杯，將成品置於冷凍庫冰鎮。</v>
       </c>
       <c r="H91" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮香檳杯</v>
       </c>
       <c r="I91" t="str">
         <v>建議物</v>
       </c>
       <c r="J91" t="str">
-        <v>亞歷山大的最著名版本，將琴酒換成干邑白蘭地，可可豆香、鮮奶油與白蘭地融合出如巧克力冰淇淋般的醇厚。</v>
+        <v>1852年由紐奧良義大利裔調酒大師Joseph Santini創作，是日後聞名世界的側車（Sidecar）的最早始祖。精緻的杯口均勻滾上一整圈晶瑩白砂糖，杯內嵌著一整圈長條橙皮，注入干邑白蘭地、橙酒與黑櫻桃酒。酒液透過糖圈入口，醇厚的葡萄果木香在舌尖與糖晶碰撞，散發19世紀美國南方的極致奢華感。</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>白蘭地庫斯塔  Brandy Crusta</v>
+        <v>百家得雞尾酒  Bacardi Cocktail</v>
       </c>
       <c r="B92">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C92">
         <v>4</v>
@@ -3328,13 +3325,13 @@
         <v>3</v>
       </c>
       <c r="E92" t="str">
-        <v>白蘭地, 無氣泡, 經典</v>
+        <v>蘭姆酒, 無氣泡, 經典</v>
       </c>
       <c r="F92" t="str">
-        <v>白蘭地 60 ml, 勒薩多黑櫻桃酒 10 ml, 君度橙酒 10 ml, 檸檬汁 10 ml, 濾掉冰塊，倒入已冰鎮的糖口杯。, 檸檬皮捲</v>
+        <v>白蘭姆酒 45 ml, 萊姆汁 25 ml, 純糖漿 20 ml, 紅石榴糖漿 2 tsp, 2．濾掉冰塊，將酒液倒入冰鎮過的香檳杯。, 檸檬皮捲</v>
       </c>
       <c r="G92" t="str">
-        <v>1. 製作糖口杯，將成品置於冷凍庫冰鎮。</v>
+        <v/>
       </c>
       <c r="H92" t="str">
         <v>冰鎮香檳杯</v>
@@ -3343,50 +3340,50 @@
         <v>建議物</v>
       </c>
       <c r="J92" t="str">
-        <v>1852年由Joseph Santini在新奧爾良發明，是經典側車（Sidecar）的始祖，精緻的杯口糖圈與長條整圈橙皮為其註冊商標。</v>
+        <v>調酒史上最具傳奇色彩的法律判決名酒！1930年代紐約最高法院做出劃時代判決：此酒「必須且只能」使用百家得（Bacardi）蘭姆酒調製，否則視為違法詐欺。百家得白蘭姆酒結合新鮮青檸汁與天然紅石榴糖漿，酒液呈粉紅玫瑰寶石光澤，酸爽生津、甘蔗果香明亮，是蘭姆酒界的權威經典。</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>百家得雞尾酒  Bacardi Cocktail</v>
+        <v>皇家基爾  Kir Royale</v>
       </c>
       <c r="B93">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C93">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D93">
         <v>3</v>
       </c>
       <c r="E93" t="str">
-        <v>蘭姆酒, 無氣泡, 經典</v>
+        <v>其他, 有氣泡, 經典</v>
       </c>
       <c r="F93" t="str">
-        <v>白蘭姆酒 45 ml, 萊姆汁 25 ml, 純糖漿 20 ml, 紅石榴糖漿 2 tsp, 2．濾掉冰塊，將酒液倒入冰鎮過的香檳杯。, 檸檬皮捲</v>
+        <v>香檳 180 ml, 黑醋栗香甜酒2tsp</v>
       </c>
       <c r="G93" t="str">
-        <v/>
+        <v>1. 倒入少許黑醋栗香甜酒於香檳杯，依甜味的喜好調整用量。。２．倒入已充分冰鎮的香檳約八分滿杯。。讓香檳更受歡迎的神奇魔法</v>
       </c>
       <c r="H93" t="str">
-        <v>冰鎮香檳杯</v>
+        <v>冰鎮香甜酒杯</v>
       </c>
       <c r="I93" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J93" t="str">
-        <v>紐約最高法院曾於1936年做出歷史性判決：此酒「必須且只能」使用百家得蘭姆酒調製，紅石榴糖漿帶來誘人粉紅色澤。</v>
+        <v>法國勃艮第地區最著名的國寶級餐前開胃酒。二戰後由第戎市傳奇市長費利克斯·基爾（Félix Kir）大力推廣。將黑醋栗利口酒（Crème de Cassis）注入細長香檳笛杯底，緩緩注入冰鎮法國頂級香檳。深紫紅糖漿在金色氣泡中冉冉升騰，黑醋栗果香與香檳酵母香氣完美交織，盡顯法式宮廷的高雅浪漫。</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>皇家基爾  Kir Royale</v>
+        <v>皮姆之杯  Pimm_s Cup</v>
       </c>
       <c r="B94">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94">
         <v>3</v>
@@ -3395,103 +3392,103 @@
         <v>其他, 有氣泡, 經典</v>
       </c>
       <c r="F94" t="str">
-        <v>香檳 180 ml, 黑醋栗香甜酒2tsp</v>
+        <v>皮姆一號 45 ml, 辛口薑汁汽水 120 ml</v>
       </c>
       <c r="G94" t="str">
-        <v>1. 倒入少許黑醋栗香甜酒於香檳杯，依甜味的喜好調整用量。。２．倒入已充分冰鎮的香檳約八分滿杯。。讓香檳更受歡迎的神奇魔法</v>
+        <v>1. 放入冰塊，攪拌冰杯後將融水倒出。。2. 倒入皮姆一號，最後補滿薑汁汽水，稍加攪拌。</v>
       </c>
       <c r="H94" t="str">
-        <v>冰鎮香甜酒杯</v>
+        <v>可林杯</v>
       </c>
       <c r="I94" t="str">
         <v/>
       </c>
       <c r="J94" t="str">
-        <v>法國經典餐前酒，將黑醋栗利口酒（Champagne）與冰鎮香檳結合，細緻的汽泡烘托出高貴奢華的果香。</v>
+        <v>英國溫布頓網球錦標賽與皇家雅士谷賽馬會的官方指定國民夏日飲品！由倫敦牡蠣吧老闆James Pimm於1840年代調製。以皮姆一號草本浸泡酒為基底，加入大量新鮮黃瓜片、薄荷葉、草莓與柑橘水果，填入薑汁汽水。入口清脆爽冽、草本果香撲鼻，是英倫莊園草地上最優雅的夏日風景。</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>皮姆之杯  Pimm_s Cup</v>
+        <v>皮斯可酸酒  Pisco Sour</v>
       </c>
       <c r="B95">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D95">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E95" t="str">
-        <v>其他, 有氣泡, 經典</v>
+        <v>其他, 無氣泡, 經典</v>
       </c>
       <c r="F95" t="str">
-        <v>皮姆一號 45 ml, 辛口薑汁汽水 120 ml</v>
+        <v>皮斯可 75 ml, 檸檬汁 20 ml, 純糖漿 20 ml, 蛋白 1 個, 2．加入冰塊搖盪均勻，濾冰倒入已冰鎮的淺碟香檳杯, 原味苦精</v>
       </c>
       <c r="G95" t="str">
-        <v>1. 放入冰塊，攪拌冰杯後將融水倒出。。2. 倒入皮姆一號，最後補滿薑汁汽水，稍加攪拌。</v>
+        <v/>
       </c>
       <c r="H95" t="str">
-        <v>可林杯</v>
+        <v>冰鎮淺碟香檳杯</v>
       </c>
       <c r="I95" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J95" t="str">
-        <v>英國溫布頓網球公開賽的官方指定飲品！皮姆一號香草利口酒配上大量新鮮黃瓜、薄荷與水果，充滿英倫夏日風情。</v>
+        <v>秘魯與智利爭相立法的國寶級調酒，1920年代由美國調酒師Victor Morris在秘魯利馬莫里斯酒吧創作。以未經橡木桶陳年、純粹保留麝香葡萄香氣的皮斯可（Pisco）白蘭地為底，加入新鮮檸檬汁、糖漿與蛋白搖盪，頂部滴上安格式苦精。泡沫綿密如雪，果酸緊緻明亮，展現南美安地斯山脈純淨的陽光風土。</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>皮斯可酸酒  Pisco Sour</v>
+        <v>瞎瞎俄羅斯  Blind Russian</v>
       </c>
       <c r="B96">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C96">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D96">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E96" t="str">
-        <v>其他, 無氣泡, 經典</v>
+        <v>伏特加, 無氣泡, 經典</v>
       </c>
       <c r="F96" t="str">
-        <v>皮斯可 75 ml, 檸檬汁 20 ml, 純糖漿 20 ml, 蛋白 1 個, 2．加入冰塊搖盪均勻，濾冰倒入已冰鎮的淺碟香檳杯, 原味苦精</v>
+        <v>伏特加 60 ml, 咖啡香甜酒 20 ml, 奶酒 15 ml</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>冰鎮淺碟香檳杯</v>
+        <v>冰鎮古典杯</v>
       </c>
       <c r="I96" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J96" t="str">
-        <v>秘魯與智利的國寶級調酒。皮斯可葡萄白蘭地與檸檬、蛋白搖盪出綿密泡沫，頂部滴上苦精，酸爽無比。</v>
+        <v>白色俄羅斯（White Russian）的極限硬核重裝版！調酒師大膽拋棄了傳統的無酒精鮮奶油，直接將其替換為濃郁香甜的愛爾蘭百利甜奶酒（Baileys）。伏特加的烈度與咖啡利口酒的烘焙香，在奶酒的注入下酒精濃度與濃稠度瞬間翻倍。入口甜美無比卻暗藏兇猛後勁，喝完宛如雙眼摸黑般微醺沉醉，因而得名。</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>瞎瞎俄羅斯  Blind Russian</v>
+        <v>破冰船  Ice-Breaker</v>
       </c>
       <c r="B97">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C97">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E97" t="str">
-        <v>伏特加, 無氣泡, 經典</v>
+        <v>龍舌蘭, 無氣泡, 經典</v>
       </c>
       <c r="F97" t="str">
-        <v>伏特加 60 ml, 咖啡香甜酒 20 ml, 奶酒 15 ml</v>
+        <v>龍舌蘭 30 ml, 君度橙酒 15 ml, 葡萄柚汁 30 ml, 紅石榴糖漿1tsp, 將酒液倒入冰鎮過的古典杯，加入冰塊。, 柳橙皮捲</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -3500,126 +3497,126 @@
         <v>冰鎮古典杯</v>
       </c>
       <c r="I97" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J97" t="str">
-        <v>白色俄羅斯的硬派瘋狂版！大膽將配方中的鮮奶油直接替換為愛爾蘭奶酒（Baileys），濃郁度與酒精濃度雙重大飆升。</v>
+        <v>以航行於極地破開冰封海洋的巨型「破冰船」命名。選用熱情奔放的墨西哥龍舌蘭酒為底，調和新鮮現榨葡萄柚汁與少許紅石榴糖漿。酒液呈現溫暖璀璨的日落橙粉色，龍舌蘭的草本胡椒氣息被葡萄柚的明朗微苦酸香完美破開，入口溫暖而富有衝擊力，宛如在冰封派對中瞬間打破僵局的社交破冰利器。</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>破冰船  Ice-Breaker</v>
+        <v>神風特攻隊  Kamikaze</v>
       </c>
       <c r="B98">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C98">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D98">
         <v>4</v>
       </c>
       <c r="E98" t="str">
-        <v>龍舌蘭, 無氣泡, 經典</v>
+        <v>伏特加, 無氣泡, 經典</v>
       </c>
       <c r="F98" t="str">
-        <v>龍舌蘭 30 ml, 君度橙酒 15 ml, 葡萄柚汁 30 ml, 紅石榴糖漿1tsp, 將酒液倒入冰鎮過的古典杯，加入冰塊。, 柳橙皮捲</v>
+        <v>伏特加 60 ml, 君度橙酒 20 ml, 萊姆汁 20 ml, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>冰鎮古典杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I98" t="str">
         <v>建議物</v>
       </c>
       <c r="J98" t="str">
-        <v>龍舌蘭與葡萄柚、紅石榴的熱帶相遇，亮麗的粉橙色澤宛如破冰船在極地破開冰雪，帶來溫暖陽光的南美氣息。</v>
+        <v>二戰後美軍佔領日本期間，在東京橫須賀美軍基地酒吧誕生的高人氣經典。將純淨伏特加、君度橙酒與現榨檸檬汁以1:1:1等比例冰鎮搖盪。口感冷冽乾脆、酸爽強勁，毫無拖泥帶水，像極了神風特攻隊般直接、凌厲且後勁迅猛，如今亦是全世界各大派對上最受歡迎的靈魂Shot酒之一。</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>神風特攻隊  Kamikaze</v>
+        <v>科羅拉多鬥牛犬  Colorado Bulldog</v>
       </c>
       <c r="B99">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C99">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D99">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E99" t="str">
-        <v>伏特加, 無氣泡, 經典</v>
+        <v>伏特加, 有氣泡, 經典</v>
       </c>
       <c r="F99" t="str">
-        <v>伏特加 60 ml, 君度橙酒 20 ml, 萊姆汁 20 ml, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲</v>
+        <v>伏特加 60 ml, 咖啡香甜酒 20 ml, 鮮奶油 15 ml, 可口可樂, 適量, 加入適量可樂，稍加攪拌</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮古典杯</v>
       </c>
       <c r="I99" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J99" t="str">
-        <v>二戰後誕生於駐日美軍酒吧。伏特加、橙酒與檸檬汁等比例混合，如神風特攻隊般直接、辛辣且後勁凌厲，現為著名Shot酒。</v>
+        <v>白色俄羅斯（White Russian）在美國西部最具趣味的俏皮變奏。在伏特加、甘露咖啡香甜酒與鮮奶油調和的經典杯中，最後大膽注入一注冰鎮可口可樂。氣泡在濃郁奶香中嘶嘶沸騰，入口既有奶昔般的絲滑溫潤，又有碳酸可樂的暢快跳躍，宛如大人版的微醺漂浮可樂，口感豐富且令人嘴角上揚。</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>科羅拉多鬥牛犬  Colorado Bulldog</v>
+        <v>突發奇想  Caprice</v>
       </c>
       <c r="B100">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D100">
         <v>2</v>
       </c>
       <c r="E100" t="str">
-        <v>伏特加, 有氣泡, 經典</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F100" t="str">
-        <v>伏特加 60 ml, 咖啡香甜酒 20 ml, 鮮奶油 15 ml, 可口可樂, 適量, 加入適量可樂，稍加攪拌</v>
+        <v>琴酒 45 ml, 法式不甜香艾酒 15 ml, 班尼迪克丁 15 ml, 安格式柑橘苦精 1 dash, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲, 糖漬櫻桃</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>冰鎮古典杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I100" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J100" t="str">
-        <v>白色俄羅斯（White Russian）的趣味變奏版！最後大膽加入可樂，汽泡感與奶香結合，口感激似微醺版的漂浮可樂。</v>
+        <v>誕生於20世紀中葉歐洲沙龍，名字「Caprice」在法語中意為「靈感乍現、美麗的突發奇想」。精選倫敦乾琴酒，調和法國本篤會廊酒（Bénédictine D.O.M）與干苦艾酒。廊酒二十多種藥草的蜜香，巧妙柔化了琴酒與苦艾酒的乾冽骨架，酒體澄澈金黃，草本層次繁複幽雅，如同一首優美跳躍的即興隨想曲。</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>突發奇想  Caprice</v>
+        <v>第八區  Ward 8</v>
       </c>
       <c r="B101">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C101">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E101" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F101" t="str">
-        <v>琴酒 45 ml, 法式不甜香艾酒 15 ml, 班尼迪克丁 15 ml, 安格式柑橘苦精 1 dash, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲, 糖漬櫻桃</v>
+        <v>波本威士忌 45 ml, 檸檬汁 15 ml, 柳橙汁 15 ml, 紅石榴糖漿1tsp, 2.. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -3631,27 +3628,27 @@
         <v>建議物</v>
       </c>
       <c r="J101" t="str">
-        <v>琴酒與法國廊酒（Benedictine）、干苦艾酒的優雅結合，如美麗的靈感突發奇想，散發多層次的複雜草本香氣。</v>
+        <v>1919年誕生於波士頓著名的洛克-奧伯（Locke-Ober）傳奇餐廳。是為了慶祝當地第八選區政壇大佬馬丁·洛馬斯尼（Martin Lomasney）第25次順利勝選而特別調製。以辛辣黑麥威士忌為基底，加入新鮮現榨檸檬汁、柳橙汁與天然紅石榴糖漿。酒液呈勝利般的緋紅金光，酸甜生津中帶有厚實木質香，是波士頓的政治傳奇。</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>第八區  Ward 8</v>
+        <v>紅獅  Red Lion</v>
       </c>
       <c r="B102">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C102">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D102">
         <v>3</v>
       </c>
       <c r="E102" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F102" t="str">
-        <v>波本威士忌 45 ml, 檸檬汁 15 ml, 柳橙汁 15 ml, 紅石榴糖漿1tsp, 2.. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
+        <v>琴酒 30 ml, 香橙干邑白蘭地 20 ml, 柳橙汁 30 ml, 檸檬汁 10 ml, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -3660,18 +3657,18 @@
         <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I102" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J102" t="str">
-        <v>1919年誕生於波士頓，為了慶祝當地第八選區政壇大佬馬丁·洛馬斯尼順利勝選而創，波本與紅石榴帶來亮眼色澤。</v>
+        <v>奪得1933年倫敦世界調酒錦標賽冠軍的殿堂級經典，由傳奇調酒師Arthur Tarling創作。以倫敦乾琴酒與格蘭瑪尼耶（Grand Marnier）柑橘干邑甜酒為骨架，融合新鮮現榨柳橙汁與檸檬汁，杯口抹上細緻糖圈。柑橘果香濃郁飽滿，草本杜松子與陳年干邑香氣在舌尖優雅共鳴，散發大英帝國全盛時期的王者霸氣。</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>紅獅  Red Lion</v>
+        <v>紐約  New York</v>
       </c>
       <c r="B103">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C103">
         <v>4</v>
@@ -3680,10 +3677,10 @@
         <v>3</v>
       </c>
       <c r="E103" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F103" t="str">
-        <v>琴酒 30 ml, 香橙干邑白蘭地 20 ml, 柳橙汁 30 ml, 檸檬汁 10 ml, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。</v>
+        <v>波本威士忌 60 ml, 檸檬汁 30 ml, 紅石榴糖漿2tsp, 純糖漿 10 ml, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲, 糖漬櫻桃</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -3692,33 +3689,33 @@
         <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I103" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J103" t="str">
-        <v>奪得1933年倫敦世界調酒大賽冠軍，琴酒與大中央利口酒（Grand Marnier）完美平衡，帶有濃郁的倫敦硬派柑橘香。</v>
+        <v>1920年代風靡大蘋果紐約的經典都會調酒。以辛烈純正的美國黑麥威士忌為靈魂，加入新鮮現榨檸檬汁、砂糖與天然紅石榴糖漿，杯壁噴上新鮮柳橙皮精油。酒液呈現宛如紐約秋日黃昏般深邃的琥珀紅，入口酸甜明快，隨後在舌根化開黑麥溫暖厚實的辛香與橡木桶香氣，充滿曼哈頓都會精英的成熟魅力。</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>紐約  New York</v>
+        <v>紫霾  Purple Haze</v>
       </c>
       <c r="B104">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D104">
         <v>3</v>
       </c>
       <c r="E104" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>伏特加, 無氣泡, 經典</v>
       </c>
       <c r="F104" t="str">
-        <v>波本威士忌 60 ml, 檸檬汁 30 ml, 紅石榴糖漿2tsp, 純糖漿 10 ml, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲, 糖漬櫻桃</v>
+        <v>伏特加 60 ml, 香橙干邑白蘭地 22.5 ml, 檸檬汁 20 ml, 純糖漿 15 ml, 火龍果1tsp, 葡萄 8 個, 3．濾掉冰塊及果渣，將酒液倒入冰鎮過的馬丁尼杯。</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>1. 雪克杯加入紅肉火龍果、葡萄及Grand Marnier。</v>
       </c>
       <c r="H104" t="str">
         <v>冰鎮馬丁尼杯</v>
@@ -3727,91 +3724,91 @@
         <v>建議物</v>
       </c>
       <c r="J104" t="str">
-        <v>1920年代風靡大蘋果紐約的經典，黑麥威士忌與新鮮檸檬汁、紅石榴糖漿結合，酸甜中帶有硬朗的木質調性。</v>
+        <v>向搖滾吉他之神吉米·罕醉克斯（Jimi Hendrix）1967年傳奇名曲《Purple Haze》致敬的派對靈魂長飲。以純淨伏特加為底，加入黑色黑醋栗利口酒（Chambord）與酸甜蔓越莓汁，注入蘇打水。酒液在燈光下散發迷幻深邃的紫羅蘭霧光，莓果香氣馥郁酸甜，充滿著迷幻搖滾年代不羈狂放的音樂靈魂。</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>紫霾  Purple Haze</v>
+        <v>綠眼  Green Eyes</v>
       </c>
       <c r="B105">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C105">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D105">
         <v>3</v>
       </c>
       <c r="E105" t="str">
-        <v>伏特加, 無氣泡, 經典</v>
+        <v>伏特加, 其他, 經典</v>
       </c>
       <c r="F105" t="str">
-        <v>伏特加 60 ml, 香橙干邑白蘭地 22.5 ml, 檸檬汁 20 ml, 純糖漿 15 ml, 火龍果1tsp, 葡萄 8 個, 3．濾掉冰塊及果渣，將酒液倒入冰鎮過的馬丁尼杯。</v>
+        <v>白蘭姆酒 30 ml, 蜜多麗蜜瓜香甜酒 25 ml, 椰漿 15 ml, 鳳梨汁 45 ml, 檸檬汁 15 ml, 柳橙片, 糖漬櫻桃</v>
       </c>
       <c r="G105" t="str">
-        <v>1. 雪克杯加入紅肉火龍果、葡萄及Grand Marnier。</v>
+        <v/>
       </c>
       <c r="H105" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮颶風杯</v>
       </c>
       <c r="I105" t="str">
         <v>建議物</v>
       </c>
       <c r="J105" t="str">
-        <v>以傳奇吉他手Jimi Hendrix的同名神曲命名，果香香甜酒與伏特加撞擊出神祕浪漫的深紫色，充滿搖滾靈魂。</v>
+        <v>為1984年美國洛杉磯奧運會創作的官方指定慶祝調酒。將三得利Midori綠色蜜瓜香甜酒、椰子蘭姆酒與新鮮鳳梨汁、現榨萊姆汁劇烈搖盪。酒液呈現宛如波斯貓綠寶石眼眸般神秘清澈的亮翠綠色，充滿濃郁奔放的熱帶海島果香與椰香，彷彿在加州燦爛陽光下凝視著一雙充滿活力的神秘綠眼。</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>綠眼  Green Eyes</v>
+        <v>綠色幻覺  Illusion</v>
       </c>
       <c r="B106">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D106">
         <v>3</v>
       </c>
       <c r="E106" t="str">
-        <v>伏特加, 其他, 經典</v>
+        <v>伏特加, 無氣泡, 經典</v>
       </c>
       <c r="F106" t="str">
-        <v>白蘭姆酒 30 ml, 蜜多麗蜜瓜香甜酒 25 ml, 椰漿 15 ml, 鳳梨汁 45 ml, 檸檬汁 15 ml, 柳橙片, 糖漬櫻桃</v>
+        <v>蜜多麗蜜瓜香甜酒 45 ml, 伏特加 15 ml, 君度橙酒 15 ml, 鳳梨汁 45 ml, 萊姆汁 20 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
       </c>
       <c r="G106" t="str">
         <v/>
       </c>
       <c r="H106" t="str">
-        <v>冰鎮颶風杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I106" t="str">
         <v>建議物</v>
       </c>
       <c r="J106" t="str">
-        <v>為了慶祝1984年洛杉磯奧運會而創作的官方指定色調酒，哈密瓜與椰子蘭姆酒交織出如同綠色貓眼般的熱帶迷幻。</v>
+        <v>風靡全球派對島嶼與熱帶海灘的迷幻長飲。將Midori蜜瓜香甜酒、君度橙酒、伏特加與新鮮鳳梨汁完美調和。亮麗螢光的熱帶翠綠酒液在杯中宛如發光的液態寶石，哈密瓜的香甜與鳳梨果酸在舌尖爆發出令人沉醉的熱帶節奏，一口飲下彷彿瞬間穿越至無憂無慮的加勒比海幻境，因而得名。</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>綠色幻覺  Illusion</v>
+        <v>綠色蚱蜢  Grasshopper</v>
       </c>
       <c r="B107">
         <v>15</v>
       </c>
       <c r="C107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D107">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E107" t="str">
-        <v>伏特加, 無氣泡, 經典</v>
+        <v>其他, 無氣泡, 經典</v>
       </c>
       <c r="F107" t="str">
-        <v>蜜多麗蜜瓜香甜酒 45 ml, 伏特加 15 ml, 君度橙酒 15 ml, 鳳梨汁 45 ml, 萊姆汁 20 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
+        <v>綠薄荷香甜酒 25 ml, 白巧克力香甜酒 25 ml, 鮮奶 50 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 薄荷葉</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -3823,27 +3820,27 @@
         <v>建議物</v>
       </c>
       <c r="J107" t="str">
-        <v>風靡全球派對的迷幻系長飲，亮綠色的翠綠液體中洋溢著哈密瓜、橙香與鳳梨汁的甜美，讓人產生置身海島的幻覺。</v>
+        <v>1918年由新奧爾良法國區歷史名店Tujague's的老闆Guillaume Tujague創作。將綠薄荷香甜酒、白可可香甜酒與新鮮鮮奶油以精準1:1:1等比例劇烈搖盪。酒液呈現宛如薄荷草葉般夢幻的粉嫩淺綠色，入口冰涼絲滑，薄荷的沁涼與可可奶香在舌尖曼妙交融，宛如融化的高級薄荷巧克力冰淇淋，甜美無比。</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>綠色蚱蜢  Grasshopper</v>
+        <v>羅伯洛伊  Rob Roy</v>
       </c>
       <c r="B108">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" t="str">
-        <v>其他, 無氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F108" t="str">
-        <v>綠薄荷香甜酒 25 ml, 白巧克力香甜酒 25 ml, 鮮奶 50 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 薄荷葉</v>
+        <v>蘇格蘭威士忌 60 ml, 法式甜香艾酒 20 ml, 安格式原味苦精 1 dash, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -3855,59 +3852,59 @@
         <v>建議物</v>
       </c>
       <c r="J108" t="str">
-        <v>1918年由新奧爾良傳統老店創作，綠薄荷酒、白可可酒與鮮奶油等比例搖盪，呈現如薄荷巧克力冰淇淋般的極致甜點風味。</v>
+        <v>被調酒界譽為「蘇格蘭版的曼哈頓」。1894年紐約華道夫大飯店調酒師為了慶祝同名歌劇在百老匯首演而創，以被稱為「蘇格蘭羅賓漢」的傳奇英雄羅伯·洛伊（Rob Roy）命名。將辛辣的黑麥威士忌替換為帶有泥煤煙燻與麥芽香氣的蘇格蘭威士忌，搭配紅甜苦艾酒與苦精，口感深邃雄渾、煙燻回甘。</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>羅伯洛伊  Rob Roy</v>
+        <v>美國佬  Americano</v>
       </c>
       <c r="B109">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C109">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D109">
         <v>2</v>
       </c>
       <c r="E109" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>其他, 有氣泡, 經典</v>
       </c>
       <c r="F109" t="str">
-        <v>蘇格蘭威士忌 60 ml, 法式甜香艾酒 20 ml, 安格式原味苦精 1 dash, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲</v>
+        <v>肯巴利苦酒 30 ml, 義式甜香艾酒 30 ml, 蘇打水, 再加入適量蘇打水，攪拌均勻。, 柳橙片</v>
       </c>
       <c r="G109" t="str">
         <v/>
       </c>
       <c r="H109" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮古典杯</v>
       </c>
       <c r="I109" t="str">
         <v>建議物</v>
       </c>
       <c r="J109" t="str">
-        <v>被譽為「蘇格蘭的曼哈頓」。1894年為了慶祝同名歌劇在紐約首演而創，以蘇格蘭羅賓漢（Rob Roy）命名，煙燻感十足。</v>
+        <v>發源於1860年代義大利米蘭的賈斯帕·金巴利酒吧，原名「Milano-Torino」。因在1900年代初期深受湧入義大利度假的美國遊客狂熱喜愛而更名為「美國佬」。金巴利（Campari）的草本微苦與都靈紅甜苦艾酒等比例混合，注入冒泡的蘇打水與橙片。它是龐德系列小說中007點的第一杯調酒，苦甜平衡、清爽開胃。</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>美國佬  Americano</v>
+        <v>老夥伴  Old Pal</v>
       </c>
       <c r="B110">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C110">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D110">
         <v>2</v>
       </c>
       <c r="E110" t="str">
-        <v>其他, 有氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F110" t="str">
-        <v>肯巴利苦酒 30 ml, 義式甜香艾酒 30 ml, 蘇打水, 再加入適量蘇打水，攪拌均勻。, 柳橙片</v>
+        <v>裸麥威士忌 30 ml, 義式甜香艾酒 22 ml, 肯巴利苦酒 22 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的古典杯。, 柳橙皮捲</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -3919,27 +3916,27 @@
         <v>建議物</v>
       </c>
       <c r="J110" t="str">
-        <v>歷史悠久的義大利經典，金巴利與甜苦艾酒加蘇打水。因深受早期美國遊客喜愛而得名，也是佔姆士龐德點的第一款調酒。</v>
+        <v>1920年代由巴黎《紐約先驅論壇報》體育編輯William "Sparrow" Robertson創製，是內格羅尼（Negroni）更為硬朗的兄弟版。將琴酒換成剛勁辛辣的美國黑麥威士忌，將甜苦艾酒換成干苦艾酒（Dry Vermouth），與金巴利等比例混合。酒體乾冽強勁、苦感純粹，散發著老報人與老酒友之間歷經滄桑卻歷久彌堅的真摯情誼。</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>老夥伴  Old Pal</v>
+        <v>老廣場  Vieux Carre</v>
       </c>
       <c r="B111">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C111">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D111">
         <v>2</v>
       </c>
       <c r="E111" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>威士忌, 白蘭地, 無氣泡, 經典</v>
       </c>
       <c r="F111" t="str">
-        <v>裸麥威士忌 30 ml, 義式甜香艾酒 22 ml, 肯巴利苦酒 22 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的古典杯。, 柳橙皮捲</v>
+        <v>白蘭地 25 ml, 裸麥威士忌 25 ml, 法式甜香艾酒 25 ml, 安格式原味苦精 1 dash, 裴喬氏芳香苦精 1 dash, 班尼迪克丁 1 tsp, 檸檬皮捲, 柳橙皮</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -3951,44 +3948,44 @@
         <v>建議物</v>
       </c>
       <c r="J111" t="str">
-        <v>1920年代由巴黎體育記者創製，內格羅尼（Negroni）的硬派變奏版。將琴酒換成黑麥威士忌、甜苦艾換成干苦艾，乾冽苦甜。</v>
+        <v>1938年由紐奧良傳奇飯店蒙特雷昂（Hotel Monteleone）旋轉旋轉木馬酒吧調酒師Walter Bergeron創作。「Vieux Carré」在法語中正是紐奧良著名「法國區老廣場」之意。黑麥威士忌、干邑白蘭地、甜苦艾酒、班尼迪克丁廊酒與兩種苦精的大師級融合，入口醇厚溫暖、層次無比豐富，濃縮了整個紐奧良的爵士浪漫。</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>老廣場  Vieux Carre</v>
+        <v>老爺車  Classic Car</v>
       </c>
       <c r="B112">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C112">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E112" t="str">
-        <v>威士忌, 白蘭地, 無氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F112" t="str">
-        <v>白蘭地 25 ml, 裸麥威士忌 25 ml, 法式甜香艾酒 25 ml, 安格式原味苦精 1 dash, 裴喬氏芳香苦精 1 dash, 班尼迪克丁 1 tsp, 檸檬皮捲, 柳橙皮</v>
+        <v>陳年蘭姆酒 70 ml, 班尼迪克丁 20 ml, 安格式原味苦精 1 dash, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
       </c>
       <c r="G112" t="str">
         <v/>
       </c>
       <c r="H112" t="str">
-        <v>冰鎮古典杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I112" t="str">
         <v>建議物</v>
       </c>
       <c r="J112" t="str">
-        <v>1930年代誕生於新奧爾良法國區同名大飯店。黑麥威士忌、干邑白蘭地與草本酒、苦精大融合，完美濃縮了當地的老廣場風情。</v>
+        <v>經典調酒「側車（Sidecar）」在高階古典沙龍中的優雅當代致敬版。以陳年干邑白蘭地為核心，精準調和干苦艾酒與柑橘香甜酒。酒體展現出更加內斂沉穩的橡木桶皮革與杏桃香氣，沒有過度甜膩，線條流暢乾淨，宛如一輛行駛在落葉大道上線條優雅迷人的復古歐陸老爺車，值得靜心慢品。</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>老爺車  Classic Car</v>
+        <v>臨別一語  Last Word</v>
       </c>
       <c r="B113">
         <v>25</v>
@@ -3997,13 +3994,13 @@
         <v>4</v>
       </c>
       <c r="D113">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E113" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F113" t="str">
-        <v>陳年蘭姆酒 70 ml, 班尼迪克丁 20 ml, 安格式原味苦精 1 dash, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
+        <v>琴酒 25 ml, 勒薩多黑櫻桃酒 25 ml, 夏特勒茲(綠) 25 ml, 萊姆汁 25 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲, 檸檬皮捲</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -4015,82 +4012,82 @@
         <v>建議物</v>
       </c>
       <c r="J113" t="str">
-        <v>白蘭地側車（Sidecar）的高雅當代變奏，透過更精緻的柑橘利口酒比例，呈現如古董老爺車般沉穩、優雅的歐陸線條。</v>
+        <v>禁酒令前夕誕生於底特律體育俱樂部，後在2004年由西雅圖調酒教父Murray Stenson重新挖掘而震撼全球調酒界。將琴酒、夏翠絲綠藥草酒（Green Chartreuse）、黑櫻桃利口酒與新鮮現榨青檸汁以完美的1:1:1:1等比例搖盪。草本複雜度、甜美果香與銳利果酸在此達成不可思議的奇蹟平衡，餘韻悠長難忘。</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>臨別一語  Last Word</v>
+        <v>自由古巴  Cuba Libre</v>
       </c>
       <c r="B114">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C114">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D114">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E114" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>蘭姆酒, 有氣泡, 經典</v>
       </c>
       <c r="F114" t="str">
-        <v>琴酒 25 ml, 勒薩多黑櫻桃酒 25 ml, 夏特勒茲(綠) 25 ml, 萊姆汁 25 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲, 檸檬皮捲</v>
+        <v>白蘭姆酒 60 ml, 可口可樂 120 ml, 檸檬角</v>
       </c>
       <c r="G114" t="str">
-        <v/>
+        <v>1. 可林杯放入冰塊，攪拌冰杯後將融水倒出。。２．倒入蘭姆酒、擠入檸檬汁，最後補滿可樂，稍加攪拌。。檸檬角。古巴歷史的見證者</v>
       </c>
       <c r="H114" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>可林杯</v>
       </c>
       <c r="I114" t="str">
         <v>建議物</v>
       </c>
       <c r="J114" t="str">
-        <v>禁酒令時期誕生於底特律體育俱樂部。琴酒、夏翠絲綠藥草酒、櫻桃黑利口酒與青檸汁等比例結合，風味極度複雜且餘韻悠長。</v>
+        <v>1900年美西戰爭結束古巴獨立之際，誕生於哈瓦那的歷史之飲。一名美國通訊兵在當地酒吧將剛引進古巴的美式可口可樂倒入陳年古巴白蘭姆酒中，擠入新鮮青檸汁，舉杯高喊「Viva Cuba Libre！（古巴自由萬歲！）」。蘭姆酒的甘蔗溫潤、可樂的焦糖碳酸與青檸的酸爽，共同銘刻下加勒比海自由的歷史篇章。</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>自由古巴  Cuba Libre</v>
+        <v>自由派  Liberal</v>
       </c>
       <c r="B115">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D115">
         <v>2</v>
       </c>
       <c r="E115" t="str">
-        <v>蘭姆酒, 有氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F115" t="str">
-        <v>白蘭姆酒 60 ml, 可口可樂 120 ml, 檸檬角</v>
+        <v>裸麥威士忌 45 ml, 義式甜香艾酒 15 ml, 皮康橙香開胃酒 7.5 ml, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
       </c>
       <c r="G115" t="str">
-        <v>1. 可林杯放入冰塊，攪拌冰杯後將融水倒出。。２．倒入蘭姆酒、擠入檸檬汁，最後補滿可樂，稍加攪拌。。檸檬角。古巴歷史的見證者</v>
+        <v/>
       </c>
       <c r="H115" t="str">
-        <v>可林杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I115" t="str">
         <v>建議物</v>
       </c>
       <c r="J115" t="str">
-        <v>1900年美西戰爭結束後誕生於古巴哈瓦那，美國可樂、古巴蘭姆酒與新鮮萊姆的結合，共同高喊「自由古巴」的歷史見證。</v>
+        <v>出自1895年George Kappeler的經典酒譜《Modern American Drinks》。是曼哈頓（Manhattan）調酒在世紀之交最著名的複雜進化版。在黑麥威士忌與紅甜苦艾酒的經典架構中，大膽注入義大利阿瑪羅（Amer Picon）苦橙草本利口酒。入口微苦深沉、橙皮芬芳悠長，完美體現19世紀末自由派思想家獨立不羈的精神。</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>自由派  Liberal</v>
+        <v>花花公子  Boulevardier</v>
       </c>
       <c r="B116">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C116">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D116">
         <v>2</v>
@@ -4099,7 +4096,7 @@
         <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F116" t="str">
-        <v>裸麥威士忌 45 ml, 義式甜香艾酒 15 ml, 皮康橙香開胃酒 7.5 ml, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
+        <v>波本威士忌 30 ml, 肯巴利苦酒 30 ml, 法式甜香艾酒 30 ml, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯, 柳橙皮捲</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -4111,15 +4108,15 @@
         <v>建議物</v>
       </c>
       <c r="J116" t="str">
-        <v>經典曼哈頓（Manhattan）的複雜辛辣變奏版，額外加入了義大利阿瑪羅（Amaro）苦甜酒，充滿自由不羈的深沉層次。</v>
+        <v>1927年誕生於巴黎哈里紐約酒吧，調酒傳奇Harry McElhone專為其好友——僑居巴黎的美國富豪兼文學雜誌《The Boulevardier（花花公子）》創辦人Erskine Gwynne調製。將內格羅尼中的琴酒替換為醇厚厚實的波本威士忌。波本的焦糖香草橡木桶甜香，將金巴利的苦澀馴化為溫暖圓潤的琥珀微醺，是秋冬深夜的無敵經典。</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>花花公子  Boulevardier</v>
+        <v>苦艾酒芙萊蓓  Absinthe Frappe</v>
       </c>
       <c r="B117">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C117">
         <v>4</v>
@@ -4128,283 +4125,283 @@
         <v>2</v>
       </c>
       <c r="E117" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>其他, 有氣泡, 經典</v>
       </c>
       <c r="F117" t="str">
-        <v>波本威士忌 30 ml, 肯巴利苦酒 30 ml, 法式甜香艾酒 30 ml, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯, 柳橙皮捲</v>
+        <v>苦艾酒 45 ml, 純糖漿1tsp, 蘇打水, 裴喬氏芳香苦精 3 dashes</v>
       </c>
       <c r="G117" t="str">
-        <v/>
+        <v>1. 長飲杯加入碎冰至五分滿，並加入苦艾酒及糖漿，攪拌均勻。。２．把碎冰補滿，加入蘇打水，稍加攪拌。。３．再抖灑苦精，漂浮至上方。。檸檬皮捲。風靡歐洲的經典雞尾酒</v>
       </c>
       <c r="H117" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>長飲杯</v>
       </c>
       <c r="I117" t="str">
         <v>建議物</v>
       </c>
       <c r="J117" t="str">
-        <v>1927年誕生於巴黎哈里紐約酒吧，專為文學雜誌《花花公子》創辦人調製。將內格羅尼中的琴酒換成波本威士忌，醇厚溫暖。</v>
+        <v>1874年由紐奧良綠沙龍調酒傳奇Cayetano Ferrér發明，是19世紀南美與歐陸名流文人解暑提神的秘密儀式。將被稱為「綠色繆斯」的烈性苦艾酒（Absinthe）與茴香利口酒、少許糖水倒入裝滿碎冰的杯中劇烈攪拌至杯身結霜。入口冰極透骨，茴香與草本香氣如暴風雨般席捲味蕾，極度清涼提神。</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>苦艾酒芙萊蓓  Absinthe Frappe</v>
+        <v>茉莉  Jasmine</v>
       </c>
       <c r="B118">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C118">
         <v>4</v>
       </c>
       <c r="D118">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E118" t="str">
-        <v>其他, 有氣泡, 經典</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F118" t="str">
-        <v>苦艾酒 45 ml, 純糖漿1tsp, 蘇打水, 裴喬氏芳香苦精 3 dashes</v>
+        <v>琴酒 45 ml, 君度橙酒 30 ml, 肯巴利苦酒 22 ml, 檸檬汁 15 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲</v>
       </c>
       <c r="G118" t="str">
-        <v>1. 長飲杯加入碎冰至五分滿，並加入苦艾酒及糖漿，攪拌均勻。。２．把碎冰補滿，加入蘇打水，稍加攪拌。。３．再抖灑苦精，漂浮至上方。。檸檬皮捲。風靡歐洲的經典雞尾酒</v>
+        <v/>
       </c>
       <c r="H118" t="str">
-        <v>長飲杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I118" t="str">
         <v>建議物</v>
       </c>
       <c r="J118" t="str">
-        <v>1874年由新奧爾良著名調酒師發明，將極具爭議的神秘苦艾酒與碎冰、茴香甜酒大火搖盪，呈現極度冰涼、解熱的草本衝擊。</v>
+        <v>1990年代中葉由加州調酒師Paul Harrington在加州大學柏克萊分校旁酒吧意外創作。大師以琴酒、君度橙酒、金巴利（Campari）與新鮮現榨檸檬汁搖盪。奇妙的是，配方中完全沒有使用一滴茶葉，金巴利與柑橘酸甜在琴酒杜松子襯托下，竟神奇地碰撞出如高雅清新的新鮮茉莉花茶香氣，令人讚嘆不已。</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>茉莉  Jasmine</v>
+        <v>莫希多  Mojito</v>
       </c>
       <c r="B119">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C119">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D119">
         <v>4</v>
       </c>
       <c r="E119" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>蘭姆酒, 有氣泡, 經典</v>
       </c>
       <c r="F119" t="str">
-        <v>琴酒 45 ml, 君度橙酒 30 ml, 肯巴利苦酒 22 ml, 檸檬汁 15 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲</v>
+        <v>白蘭姆酒 60 ml, 檸檬角, 切塊 半顆, 薄荷葉 15 片, 蘇打水, 適量, 砂糖, 適量</v>
       </c>
       <c r="G119" t="str">
-        <v/>
+        <v>1. 長飲杯放入薄荷葉與砂糖，用搗棒輕壓出香氣。。２. 加入切塊檸檬，用搗棒壓出汁（或直接加入檸檬汁20ml）。。３. 加入蘭姆酒及碎冰至八分滿，攪拌均勻。。４. 再加入蘇打水至全滿，稍加攪拌。。薄荷葉</v>
       </c>
       <c r="H119" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>長飲杯</v>
       </c>
       <c r="I119" t="str">
         <v>建議物</v>
       </c>
       <c r="J119" t="str">
-        <v>1990年代由調酒師Paul Harrington意外創作，琴酒與金巴利、橙酒結合，神奇地在完全沒加茶葉的狀況下撞擊出高雅的茉莉茶香。</v>
+        <v>源自16世紀英國海盜德雷克船長的防病良方，日後在古巴哈瓦那街頭蛻變為舉世聞名的國寶長飲，更是大文豪海明威每天在「小雜貨鋪酒吧（La Bodeguita del Medio）」必喝的靈魂甘霖。將新鮮綠薄荷葉與砂糖輕柔揉壓出精油，融入古巴白蘭姆酒與青檸，注滿碎冰與蘇打水。沁涼透徹、薄荷清香撲鼻，是夏日最純粹的救贖。</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>莫希多  Mojito</v>
+        <v>薄荷茱莉普  Mint Julep</v>
       </c>
       <c r="B120">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D120">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E120" t="str">
-        <v>蘭姆酒, 有氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F120" t="str">
-        <v>白蘭姆酒 60 ml, 檸檬角, 切塊 半顆, 薄荷葉 15 片, 蘇打水, 適量, 砂糖, 適量</v>
+        <v>波本威士忌 75 ml, 純糖漿 15 ml, 薄荷葉, 4 株</v>
       </c>
       <c r="G120" t="str">
-        <v>1. 長飲杯放入薄荷葉與砂糖，用搗棒輕壓出香氣。。２. 加入切塊檸檬，用搗棒壓出汁（或直接加入檸檬汁20ml）。。３. 加入蘭姆酒及碎冰至八分滿，攪拌均勻。。４. 再加入蘇打水至全滿，稍加攪拌。。薄荷葉</v>
+        <v>1. 茱莉普杯放入薄荷葉與糖漿，用搗棒輕壓出薄荷香氣。。２．杯中加入45ml的波本威士忌、糖漿及碎冰，攪拌均勻。。３．加入碎冰至全滿，並加入剩下的波本威士忌，攪拌至茱莉普杯結霜。。柳橙皮捲</v>
       </c>
       <c r="H120" t="str">
-        <v>長飲杯</v>
+        <v>純銅杯</v>
       </c>
       <c r="I120" t="str">
         <v>建議物</v>
       </c>
       <c r="J120" t="str">
-        <v>發源於古巴的百年消暑聖品。新鮮薄荷、砂糖與白蘭姆酒的組合，也是大文豪海明威每天必喝的夏日最愛。</v>
+        <v>美國南方歷史最悠久的傳統調酒，自1938年起成為全美最頂級賽事「肯塔基賽馬會」的官方指定飲品，每年賽事兩天內便消耗超過十二萬杯！大把新鮮薄荷葉與糖漿在精緻的純銀或白鑞金屬杯中輕搗，填滿高聳碎冰，緩緩注入醇厚波本威士忌直到金屬杯外壁凝結出一層厚厚冰霜。入口寒涼透骨、薄荷草本與焦糖木質香氣迴盪。</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>薄荷茱莉普  Mint Julep</v>
+        <v>薇絲朋  Vesper</v>
       </c>
       <c r="B121">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C121">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D121">
         <v>2</v>
       </c>
       <c r="E121" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>琴酒, 伏特加, 無氣泡, 經典</v>
       </c>
       <c r="F121" t="str">
-        <v>波本威士忌 75 ml, 純糖漿 15 ml, 薄荷葉, 4 株</v>
+        <v>琴酒 45 ml, 伏特加 15 ml, 麗葉酒 15 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲,</v>
       </c>
       <c r="G121" t="str">
-        <v>1. 茱莉普杯放入薄荷葉與糖漿，用搗棒輕壓出薄荷香氣。。２．杯中加入45ml的波本威士忌、糖漿及碎冰，攪拌均勻。。３．加入碎冰至全滿，並加入剩下的波本威士忌，攪拌至茱莉普杯結霜。。柳橙皮捲</v>
+        <v/>
       </c>
       <c r="H121" t="str">
-        <v>純銅杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I121" t="str">
         <v>建議物</v>
       </c>
       <c r="J121" t="str">
-        <v>美國南方歷史最悠久的傳統調酒，肯塔基賽馬會的官方指定飲品！大把新鮮薄荷與波本威士忌在精緻銀杯中撞擊出極致冰涼。</v>
+        <v>英國情報小說之父伊恩·佛萊明在1953年第一部龐德小說《皇家賭場》中，為詹姆士·龐德量身打造的專屬原創馬丁尼：「三份高登琴酒、一份伏特加、半份麗葉酒（Kina Lillet），用搖的直到冰透，加一大片檸檬皮」。以龐德一生唯一深愛、卻背負雙面間諜悲劇命運的女特務薇絲朋·蓮德命名，清冽乾脆中暗藏苦甜與深情。</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>薇絲朋  Vesper</v>
+        <v>藍色夏威夷  Blue Hawaii</v>
       </c>
       <c r="B122">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C122">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E122" t="str">
-        <v>琴酒, 伏特加, 無氣泡, 經典</v>
+        <v>蘭姆酒, 其他, 經典</v>
       </c>
       <c r="F122" t="str">
-        <v>琴酒 45 ml, 伏特加 15 ml, 麗葉酒 15 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲,</v>
+        <v>白蘭姆酒 45 ml, 伏特加 15 ml, 藍柑橘香甜酒 10 ml, 鳳梨汁 45 ml, 萊姆汁 15 ml, 純糖漿 15 ml, 鳳梨片, 糖漬櫻桃</v>
       </c>
       <c r="G122" t="str">
         <v/>
       </c>
       <c r="H122" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮颶風杯</v>
       </c>
       <c r="I122" t="str">
         <v>建議物</v>
       </c>
       <c r="J122" t="str">
-        <v>伊恩·佛萊明在1953年《皇家賭場》小說中為龐德量身創作的專屬馬丁尼，以龐德一生摯愛的雙面女特務薇絲朋命名。</v>
+        <v>1957年由檀香山凱撒夏威夷人飯店傳奇調酒大師Harry Yee受酒商委託推廣藍柑桂酒（Bols Blue Curaçao）而創作。將白蘭姆酒、伏特加、藍柑橘香甜酒與新鮮鳳梨汁、酸甜汁混合搖盪。酒液呈現加勒比海與太平洋最純淨透明的蔚藍寶石色，飾以鳳梨角與小雨傘，一口飲下宛如立刻置身夏威夷威基基海灘的熱情浪花中。</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>藍色夏威夷  Blue Hawaii</v>
+        <v>蘿西塔  Rosita</v>
       </c>
       <c r="B123">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C123">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D123">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E123" t="str">
-        <v>蘭姆酒, 其他, 經典</v>
+        <v>龍舌蘭, 無氣泡, 經典</v>
       </c>
       <c r="F123" t="str">
-        <v>白蘭姆酒 45 ml, 伏特加 15 ml, 藍柑橘香甜酒 10 ml, 鳳梨汁 45 ml, 萊姆汁 15 ml, 純糖漿 15 ml, 鳳梨片, 糖漬櫻桃</v>
+        <v>龍舌蘭 45 ml, 義式不甜香艾酒 15 ml, 義式甜香艾酒 15 ml, 肯巴利苦酒 15 ml, 安格式原味苦精 1 dash, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
       </c>
       <c r="G123" t="str">
         <v/>
       </c>
       <c r="H123" t="str">
-        <v>冰鎮颶風杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I123" t="str">
         <v>建議物</v>
       </c>
       <c r="J123" t="str">
-        <v>1957年由傳奇調酒大師Harry Yee在檀香山為推廣藍色橙皮酒而作，藍柑橘與鳳梨汁呈現加勒比海如寶石般的蔚藍。</v>
+        <v>最早記載於1988年調酒指南，並由雞尾酒復興教父Gary Regan發揚光大的龍舌蘭殿堂之作。是內格羅尼在墨西哥的大師級進化版：大膽同時使用等量的干苦艾酒與紅甜苦艾酒，與金巴利共同烘托頂級金龍舌蘭酒。龍舌蘭特有的泥土與白胡椒香氣在苦甜雙苦艾酒中被圓潤包裹，層次宏大而精細。</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>蘿西塔  Rosita</v>
+        <v>蜜月  Honeymoon</v>
       </c>
       <c r="B124">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C124">
         <v>4</v>
       </c>
       <c r="D124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E124" t="str">
-        <v>龍舌蘭, 無氣泡, 經典</v>
+        <v>白蘭地, 無氣泡, 經典</v>
       </c>
       <c r="F124" t="str">
-        <v>龍舌蘭 45 ml, 義式不甜香艾酒 15 ml, 義式甜香艾酒 15 ml, 肯巴利苦酒 15 ml, 安格式原味苦精 1 dash, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
+        <v>蘋果白蘭地 40 ml, 君度橙酒 10 ml, 班尼迪克丁 10 ml, 檸檬汁 15 ml, 濾掉冰塊，將酒液倒入冰鎮過的淺碟香檳杯。, 柳橙皮捲</v>
       </c>
       <c r="G124" t="str">
         <v/>
       </c>
       <c r="H124" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮淺碟香檳杯</v>
       </c>
       <c r="I124" t="str">
         <v>建議物</v>
       </c>
       <c r="J124" t="str">
-        <v>琴酒內格羅尼（Negroni）的龍舌蘭版本，大膽同時使用干苦艾酒與甜苦艾酒，完美襯托出龍舌蘭粗獷的大地與胡椒香氣。</v>
+        <v>出自1916年紐約調酒名家Hugo Ensslin的經典酒譜《Recipes for Mixed Drinks》。以諾曼第蘋果白蘭地（Calvados）為靈魂，結合法國本篤會廊酒（Bénédictine）、橙皮甜酒與現榨新鮮檸檬汁。蘋果的溫潤果香與廊酒的草本蜜糖在酸度平衡下完美交織，口感如絲綢般圓潤溫暖，充滿新婚蜜月般的濃情蜜意與幸福溫度。</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>蜜月  Honeymoon</v>
+        <v>螺絲起子  Screwdriver</v>
       </c>
       <c r="B125">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C125">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E125" t="str">
-        <v>白蘭地, 無氣泡, 經典</v>
+        <v>伏特加, 無氣泡, 經典</v>
       </c>
       <c r="F125" t="str">
-        <v>蘋果白蘭地 40 ml, 君度橙酒 10 ml, 班尼迪克丁 10 ml, 檸檬汁 15 ml, 濾掉冰塊，將酒液倒入冰鎮過的淺碟香檳杯。, 柳橙皮捲</v>
+        <v>伏特加 40 ml, 柳橙汁 120 ml</v>
       </c>
       <c r="G125" t="str">
-        <v/>
+        <v>１．可林杯放入冰塊，攪拌冰杯後將融水倒出。</v>
       </c>
       <c r="H125" t="str">
-        <v>冰鎮淺碟香檳杯</v>
+        <v>冰鎮可林杯</v>
       </c>
       <c r="I125" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J125" t="str">
-        <v>出自1916年古老酒譜，蘋果白蘭地與法國廊酒（Benedictine）、檸檬汁的完美結合，酸甜溫潤，充滿新婚蜜月般的幸福感。</v>
+        <v>20世紀中期風靡全球的純粹長飲。傳說起源於二戰後在中東波斯灣油田工作的美國石油工人，在炎熱的工作間隙偷偷將純淨的伏特加倒入罐裝柳橙汁中掩人耳目，因手邊沒有調酒長匙，順手抽出工具袋裡的「螺絲起子」進行攪拌，因而得名。純淨伏特加完全隱匿在濃郁柳橙汁中，清爽解渴、易飲易醉。</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>螺絲起子  Screwdriver</v>
+        <v>血腥瑪麗  Bloody Mary</v>
       </c>
       <c r="B126">
         <v>12</v>
@@ -4416,91 +4413,91 @@
         <v>2</v>
       </c>
       <c r="E126" t="str">
-        <v>伏特加, 無氣泡, 經典</v>
+        <v>伏特加, 其他, 經典</v>
       </c>
       <c r="F126" t="str">
-        <v>伏特加 40 ml, 柳橙汁 120 ml</v>
+        <v>伏特加 45 ml, 蕃茄汁 120 ml, 檸檬汁 15 ml, 塔巴斯可辣醬 2dash, 辣醬油/烏斯特黑醋醬。, 橄欖、檸檬皮、西洋芹</v>
       </c>
       <c r="G126" t="str">
-        <v>１．可林杯放入冰塊，攪拌冰杯後將融水倒出。</v>
+        <v/>
       </c>
       <c r="H126" t="str">
         <v>冰鎮可林杯</v>
       </c>
       <c r="I126" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J126" t="str">
-        <v>傳說起源於20世紀美國石油工人，在私下將伏特加混入柳橙汁時，順手拿手邊的「螺絲起子」來攪拌而得名的經典長飲。</v>
+        <v>1920年代由巴黎哈里紐約酒吧調酒師Fernand Petiot創作，後在紐約瑞吉飯店聖羅吉斯酒吧昇華為早午餐經典。以英格蘭殘酷女王瑪麗一世的綽號命名。伏特加與新鮮番茄汁大膽結合李派林烏斯特黑醋、塔巴斯科辣醬、芹菜鹽與現磨黑胡椒。風味辛辣鹹鮮、層次厚重，被全球酒客尊為最強大的「宿醉還魂終結者」。</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>血腥瑪麗  Bloody Mary</v>
+        <v>血與沙  Blood and Sand</v>
       </c>
       <c r="B127">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C127">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D127">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E127" t="str">
-        <v>伏特加, 其他, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F127" t="str">
-        <v>伏特加 45 ml, 蕃茄汁 120 ml, 檸檬汁 15 ml, 塔巴斯可辣醬 2dash, 辣醬油/烏斯特黑醋醬。, 橄欖、檸檬皮、西洋芹</v>
+        <v>蘇格蘭威士忌 25 ml, 義式甜香艾酒 25 ml, 櫻桃香甜酒 25 ml, 柳橙汁 25 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的淺碟香檳杯。, 柳橙皮捲</v>
       </c>
       <c r="G127" t="str">
         <v/>
       </c>
       <c r="H127" t="str">
-        <v>冰鎮可林杯</v>
+        <v>冰鎮淺碟香檳杯</v>
       </c>
       <c r="I127" t="str">
         <v>建議物</v>
       </c>
       <c r="J127" t="str">
-        <v>1920年代巴黎哈里酒吧的傑作。伏特加與番茄汁大膽結合芹菜鹽、黑胡椒與辣醬，被譽為「調酒界的宿醉終結者」。</v>
+        <v>以1922年好萊塢巨星魯道夫·瓦倫蒂諾主演的傳奇鬥牛士默片電影《血與沙》命名。將蘇格蘭威士忌的煙燻麥香、櫻桃白蘭地（Cherry Heering）的艷紅（象徵鬥牛士灑在黃沙上的鮮血）、甜苦艾酒與新鮮柳橙汁以完美的1:1:1:1等比例調和。煙燻與果香奇妙碰撞，甜美中帶著悲壯而浪漫的英雄史詩層次。</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>血與沙  Blood and Sand</v>
+        <v>賽澤瑞克(I)  Sazerac(I)</v>
       </c>
       <c r="B128">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C128">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E128" t="str">
         <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F128" t="str">
-        <v>蘇格蘭威士忌 25 ml, 義式甜香艾酒 25 ml, 櫻桃香甜酒 25 ml, 柳橙汁 25 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的淺碟香檳杯。, 柳橙皮捲</v>
+        <v>白蘭地 60 ml, 裴喬氏芳香苦精 3 dashes, 苦艾酒1tsp, 純糖漿 1 tsp, 2．濾掉冰塊，將酒液倒入涮過苦艾酒的冰鎮古典杯。, 檸檬皮捲</v>
       </c>
       <c r="G128" t="str">
         <v/>
       </c>
       <c r="H128" t="str">
-        <v>冰鎮淺碟香檳杯</v>
+        <v>最早有名字的第一杯雞尾酒</v>
       </c>
       <c r="I128" t="str">
         <v>建議物</v>
       </c>
       <c r="J128" t="str">
-        <v>以1922年好萊塢傳奇鬥牛士同名電影命名。蘇格蘭威士忌的煙燻、櫻桃白蘭地的紅（血）與甜苦艾酒，呈現悲壯的層次。</v>
+        <v>被正式立法尊為紐奧良官方雞尾酒，亦被視為美國調酒史上最早誕生的雞尾酒始祖之一。起源於19世紀中葉皇家街的Sazerac咖啡館。在特製古典杯壁以神秘苦艾酒均勻涮杯塗香，將黑麥威士忌與浸潤裴喬氏苦精的方糖慢速攪拌。酒體深邃乾燥，茴香草本與黑麥木質辛香直擊鼻腔，是老派硬漢的至高純粹殿堂。</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>賽澤瑞克(I)  Sazerac(I)</v>
+        <v>賽澤瑞克(II)  Sazerac(II)</v>
       </c>
       <c r="B129">
         <v>30</v>
@@ -4512,27 +4509,27 @@
         <v>1</v>
       </c>
       <c r="E129" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>白蘭地, 無氣泡, 經典</v>
       </c>
       <c r="F129" t="str">
-        <v>白蘭地 60 ml, 裴喬氏芳香苦精 3 dashes, 苦艾酒1tsp, 純糖漿 1 tsp, 2．濾掉冰塊，將酒液倒入涮過苦艾酒的冰鎮古典杯。, 檸檬皮捲</v>
+        <v>裸麥威士忌 60 ml, 裴喬氏芳香苦精 3 dash, 苦艾酒1tsp, 純糖漿 1 tsp, 濾掉冰塊，將酒液倒入涮過苦艾酒的冰鎮古典杯。, 檸檬皮捲</v>
       </c>
       <c r="G129" t="str">
         <v/>
       </c>
       <c r="H129" t="str">
-        <v>最早有名字的第一杯雞尾酒</v>
+        <v>冰鎮古典杯</v>
       </c>
       <c r="I129" t="str">
         <v>建議物</v>
       </c>
       <c r="J129" t="str">
-        <v>被譽為美國第一款雞尾酒！源於新奧爾良，傳統上使用美式黑麥威士忌、苦精與沾了苦艾酒香氣的冰鎮杯，硬派極致。</v>
+        <v>回歸1850年代紐奧良最原始誕生的干邑白蘭地版本。在法國葡萄根瘤蚜蟲害摧毀歐洲葡萄園之前，最早的賽澤瑞克正是使用進口的法國Sazerac de Forge et Fils干邑白蘭地調製。白蘭地的奢華葡萄果香與橡木單寧，在苦艾酒香氣與裴喬氏苦精襯托下顯得無比貴族大器，重現美國南北戰爭前紐奧良老沙龍的奢靡風華。</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>賽澤瑞克(II)  Sazerac(II)</v>
+        <v>路易斯安那雞尾酒  De La Louisiane</v>
       </c>
       <c r="B130">
         <v>30</v>
@@ -4541,45 +4538,45 @@
         <v>5</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130" t="str">
-        <v>白蘭地, 無氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F130" t="str">
-        <v>裸麥威士忌 60 ml, 裴喬氏芳香苦精 3 dash, 苦艾酒1tsp, 純糖漿 1 tsp, 濾掉冰塊，將酒液倒入涮過苦艾酒的冰鎮古典杯。, 檸檬皮捲</v>
+        <v>裸麥威士忌 22 ml, 義式甜香艾酒 22 ml, 班尼迪克丁 22 ml, 裴喬氏芳香苦精 3 dashes, 法式茴香酒 3 dashes, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 勒薩多糖漬櫻桃</v>
       </c>
       <c r="G130" t="str">
         <v/>
       </c>
       <c r="H130" t="str">
-        <v>冰鎮古典杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I130" t="str">
         <v>建議物</v>
       </c>
       <c r="J130" t="str">
-        <v>回歸最初19世紀中葉的最原始版本，使用干邑白蘭地作為基底，重現美國南北戰爭前紐奧良老酒吧的尊榮醇厚風味。</v>
+        <v>1885年誕生於紐奧良法國區著名的拉路易斯安那高檔法式餐廳，是紐奧良調酒黃金時代的瑰寶。以辛烈黑麥威士忌為骨架，調和義大利紅甜苦艾酒、班尼迪克丁本篤會廊酒、裴喬氏苦精與少許苦艾酒。草本蜜香與威士忌的辛香交織出華麗複雜的層次，優雅濃郁，宛如將路易斯安那百年法式繁榮濃縮於一杯之中。</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>路易斯安那雞尾酒  De La Louisiane</v>
+        <v>邁泰  Mai Tai</v>
       </c>
       <c r="B131">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C131">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D131">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E131" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>蘭姆酒, 無氣泡, 經典</v>
       </c>
       <c r="F131" t="str">
-        <v>裸麥威士忌 22 ml, 義式甜香艾酒 22 ml, 班尼迪克丁 22 ml, 裴喬氏芳香苦精 3 dashes, 法式茴香酒 3 dashes, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 勒薩多糖漬櫻桃</v>
+        <v>陳年蘭姆酒 55 ml, 君度橙酒 10 ml, 檸檬汁 20 ml, 純糖漿 10 ml, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯, 檸檬皮捲</v>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -4591,140 +4588,140 @@
         <v>建議物</v>
       </c>
       <c r="J131" t="str">
-        <v>1885年新奧爾良同名高檔餐廳的招牌。黑麥威士忌與草本甜酒、苦艾酒的奢華交織，展現美南路易斯安那的繁華。</v>
+        <v>1944年由加州Tiki熱帶調酒始祖Trader Vic（維克商人）在奧克蘭創作。大師以陳年十七年牙買加蘭姆酒、橙酒、杏仁糖漿（Orgeat）與青檸汁調製，遞給兩位來自大溪地的朋友品嚐，好友驚艷得大喊「Maita'i roa ae！（大溪地語：太棒了，完全是極致世界級！）」因而得名。熱帶蘭姆酒香氣奔放，是熱帶海島風情的無冕之王。</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>邁泰  Mai Tai</v>
+        <v>郝思嘉  Scarlett O_Hara</v>
       </c>
       <c r="B132">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C132">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D132">
         <v>3</v>
       </c>
       <c r="E132" t="str">
-        <v>蘭姆酒, 無氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F132" t="str">
-        <v>陳年蘭姆酒 55 ml, 君度橙酒 10 ml, 檸檬汁 20 ml, 純糖漿 10 ml, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯, 檸檬皮捲</v>
+        <v>南方安逸香甜酒 60 ml, 蔓越莓汁 40 ml, 檸檬汁 20 ml, 濾掉冰塊，將酒液倒入冰鎮過的淺碟香檳杯。, 檸檬片</v>
       </c>
       <c r="G132" t="str">
         <v/>
       </c>
       <c r="H132" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮淺碟香檳杯</v>
       </c>
       <c r="I132" t="str">
         <v>建議物</v>
       </c>
       <c r="J132" t="str">
-        <v>1944年由Tiki文化始祖Trader Vic發明，大受大溪地朋友讚賞大喊「Mai Tai」（大溪地語：極致完美！），成為熱帶蘭姆酒之王。</v>
+        <v>1939年為了慶祝好萊塢世紀巨作《亂世佳人（Gone with the Wind）》上映而創作，以片中桀驁不馴、堅毅美麗的南方女主角郝思嘉命名。選用充滿美國南方風土的「南方安逸（Southern Comfort）」桃子香料威士忌利口酒為底，加入大量新鮮蔓越莓汁與新鮮檸檬汁。入口酸甜明麗、蜜桃果香濃郁，展現出南方千金傲立風雨中的傲骨風情。</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>郝思嘉  Scarlett O_Hara</v>
+        <v>野格炸彈  Jagermeister Bomb</v>
       </c>
       <c r="B133">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C133">
         <v>3</v>
       </c>
       <c r="D133">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E133" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>其他, 有氣泡, 經典</v>
       </c>
       <c r="F133" t="str">
-        <v>南方安逸香甜酒 60 ml, 蔓越莓汁 40 ml, 檸檬汁 20 ml, 濾掉冰塊，將酒液倒入冰鎮過的淺碟香檳杯。, 檸檬片</v>
+        <v>野格 30 ml, 辛口薑汁汽水, 適量</v>
       </c>
       <c r="G133" t="str">
-        <v/>
+        <v>將冰鎮過的高球杯加入五分滿的薑汁汽水。將烈酒杯投入高球杯中，Bomb！</v>
       </c>
       <c r="H133" t="str">
-        <v>冰鎮淺碟香檳杯</v>
+        <v>烈酒杯加入野格</v>
       </c>
       <c r="I133" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J133" t="str">
-        <v>以《亂世佳人》女主角郝思嘉命名。南方安逸（Southern Comfort）桃子利口酒與蔓越莓汁結合，展現美國南方名媛的酸甜傲骨。</v>
+        <v>跨越世紀席捲全球夜店與音樂節的派對核彈！將產自德國沃爾芬比特爾、由五十六種天然草本植物釀製的深邃野格（Jägermeister）藥草利口酒倒入Shot杯中，垂直擲入盛有冰鎮紅牛（Red Bull）能量飲料的大高球杯中一飲而盡。草本甘草香與維他命牛磺酸的酸甜氣泡劇烈碰撞，瞬間引爆全場狂歡活力。</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>野格炸彈  Jagermeister Bomb</v>
+        <v>鏽釘  Rusty Nail</v>
       </c>
       <c r="B134">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C134">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" t="str">
-        <v>其他, 有氣泡, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F134" t="str">
-        <v>野格 30 ml, 辛口薑汁汽水, 適量</v>
+        <v>蘇格蘭威士忌 60 ml, 吉寶蜂蜜威士忌 10 ml, 超簡派卻不失其深度的威士忌雞尾酒</v>
       </c>
       <c r="G134" t="str">
-        <v>將冰鎮過的高球杯加入五分滿的薑汁汽水。將烈酒杯投入高球杯中，Bomb！</v>
+        <v/>
       </c>
       <c r="H134" t="str">
-        <v>烈酒杯加入野格</v>
+        <v>冰鎮古典杯</v>
       </c>
       <c r="I134" t="str">
         <v/>
       </c>
       <c r="J134" t="str">
-        <v>全球夜店必備的派對核彈！將德國野格藥草酒的Shot杯直接投入紅牛（Red Bull）能量飲料中，激發出無限的狂歡活力。</v>
+        <v>起源於1930年代，在1960年代因好萊塢法蘭克·辛納屈率領的傳奇兄弟會「鼠黨（Rat Pack）」在紐約21俱樂部通宵暢飲而揚名天下。以強勁剛烈的蘇格蘭威士忌，搭配以蜂蜜、石楠花與草本香料釀製的蘇格蘭國寶級杜林標（Drambuie）利口酒。金黃酒液如生鏽鐵釘般深邃，麥芽煙燻被溫潤蜜香深情包裹，醇厚無比。</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>鏽釘  Rusty Nail</v>
+        <v>長島冰茶  Long Island Iced Tea</v>
       </c>
       <c r="B135">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C135">
         <v>5</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E135" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>琴酒, 伏特加, 蘭姆酒, 龍舌蘭, 經典</v>
       </c>
       <c r="F135" t="str">
-        <v>蘇格蘭威士忌 60 ml, 吉寶蜂蜜威士忌 10 ml, 超簡派卻不失其深度的威士忌雞尾酒</v>
+        <v>伏特加 15 ml, 琴酒 15 ml, 白蘭姆酒 15 ml, 龍舌蘭 15 ml, 君度橙酒1tsp, 檸檬汁 20 ml, 純糖漿 15 ml, 可口可樂 40 ml, 2．將酒液倒入冰鎮過的司令杯，加入冰塊至九分滿。, 3．再加入可樂，稍加攪拌。, 檸檬片</v>
       </c>
       <c r="G135" t="str">
         <v/>
       </c>
       <c r="H135" t="str">
-        <v>冰鎮古典杯</v>
+        <v/>
       </c>
       <c r="I135" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J135" t="str">
-        <v>蘇格蘭威士忌與杜林標（Drambuie）蜂蜜草本酒的絕妙組合，是1960年代「鼠黨（Rat Pack）」演藝巨星們的最愛。</v>
+        <v>1972年由紐約長島橡樹灘客棧調酒師Robert "Rosebud" Butt在一場調酒競賽中發明。雖然名為冰茶，配方中卻完全沒有一滴茶葉！而是巧妙將伏特加、琴酒、白蘭姆酒、龍舌蘭酒四種烈酒與橙酒、檸檬汁結合，最後倒入少許可樂染出琥珀紅茶色澤。入口酸甜清涼如檸檬冰茶，後勁卻如海嘯般兇猛，是酒吧最著名的微醺偽裝者。</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>長島冰茶  Long Island Iced Tea</v>
+        <v>長島冰茶二代  Long Island Iced Tea．II</v>
       </c>
       <c r="B136">
         <v>28</v>
@@ -4739,248 +4736,248 @@
         <v>琴酒, 伏特加, 蘭姆酒, 龍舌蘭, 經典</v>
       </c>
       <c r="F136" t="str">
-        <v>伏特加 15 ml, 琴酒 15 ml, 白蘭姆酒 15 ml, 龍舌蘭 15 ml, 君度橙酒1tsp, 檸檬汁 20 ml, 純糖漿 15 ml, 可口可樂 40 ml, 2．將酒液倒入冰鎮過的司令杯，加入冰塊至九分滿。, 3．再加入可樂，稍加攪拌。, 檸檬片</v>
+        <v>伏特加 15 ml, 龍舌蘭 15 ml, 蘇格蘭威士忌 15 ml, 咖啡香甜酒 15 ml, 法式不甜香艾酒 15 ml, 檸檬汁 15 ml, 純糖漿 15 ml, 將酒液倒入冰鎮過的鹽口古典杯，加入岩冰。, 檸檬片</v>
       </c>
       <c r="G136" t="str">
         <v/>
       </c>
       <c r="H136" t="str">
-        <v/>
+        <v>冰鎮鹽口古典杯</v>
       </c>
       <c r="I136" t="str">
         <v>建議物</v>
       </c>
       <c r="J136" t="str">
-        <v>1970年代誕生於紐約長島，雖然完全不含茶葉，卻利用四種烈酒與可樂調製出激似紅茶的色澤與高酒精度的偽裝長飲。</v>
+        <v>傳奇長島冰茶在頂級俱樂部的奢華硬派升級版。將四種高濃度純烈基酒（伏特加、琴酒、白蘭姆、龍舌蘭）與柑橘橙酒的黃金比例重新提振，拋棄了原本平價的可口可樂，最後大膽填滿冰鎮法國頂級干型香檳或高品質氣泡酒。氣泡在舌尖如珠玉迸發，加速了酒精在血液中的擴散，既尊貴華麗，後勁又凌厲過人。</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>長島冰茶二代  Long Island Iced Tea．II</v>
+        <v>阿岡昆  Algonquin</v>
       </c>
       <c r="B137">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C137">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D137">
         <v>3</v>
       </c>
       <c r="E137" t="str">
-        <v>琴酒, 伏特加, 蘭姆酒, 龍舌蘭, 經典</v>
+        <v>威士忌, 無氣泡, 經典</v>
       </c>
       <c r="F137" t="str">
-        <v>伏特加 15 ml, 龍舌蘭 15 ml, 蘇格蘭威士忌 15 ml, 咖啡香甜酒 15 ml, 法式不甜香艾酒 15 ml, 檸檬汁 15 ml, 純糖漿 15 ml, 將酒液倒入冰鎮過的鹽口古典杯，加入岩冰。, 檸檬片</v>
+        <v>裸麥威士忌 60 ml, 法式不甜香艾酒 30 ml, 鳳梨汁 30 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 糖漬櫻桃</v>
       </c>
       <c r="G137" t="str">
         <v/>
       </c>
       <c r="H137" t="str">
-        <v>冰鎮鹽口古典杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I137" t="str">
         <v>建議物</v>
       </c>
       <c r="J137" t="str">
-        <v>長島冰茶的奢華硬派升級版，大膽將最後填滿的可樂換成法國頂級香檳或汽泡酒，汽泡讓高酒精後勁來得更快更猛烈。</v>
+        <v>以1920年代紐約曼哈頓著名的阿岡昆大飯店命名，這裡是當時由桃樂絲·帕克等頂尖文豪、劇作家齊聚的「阿岡昆圓桌文學會」大本營。大膽將辛烈黑麥威士忌與新鮮現榨鳳梨汁、干苦艾酒完美搖盪。鳳梨的酸甜多汁出人意料地柔化了黑麥威士忌的粗獷木質，乾爽生津、不落俗套，展現曼哈頓文人文思泉湧的幹練風骨。</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>阿岡昆  Algonquin</v>
+        <v>阿拉巴馬監獄  Alabama Slammer</v>
       </c>
       <c r="B138">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C138">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D138">
         <v>3</v>
       </c>
       <c r="E138" t="str">
-        <v>威士忌, 無氣泡, 經典</v>
+        <v>琴酒, 威士忌, 經典</v>
       </c>
       <c r="F138" t="str">
-        <v>裸麥威士忌 60 ml, 法式不甜香艾酒 30 ml, 鳳梨汁 30 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 糖漬櫻桃</v>
+        <v>野莓琴酒 30 ml, 杏仁香甜酒 30 ml, 南方安逸香甜酒 30 ml, 柳橙汁 60 ml, 濾掉冰塊，將酒液倒入冰鎮過的長飲杯，加入碎冰至全滿。, 檸檬片, 柳橙片, 糖漬櫻桃</v>
       </c>
       <c r="G138" t="str">
         <v/>
       </c>
       <c r="H138" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮長飲杯</v>
       </c>
       <c r="I138" t="str">
         <v>建議物</v>
       </c>
       <c r="J138" t="str">
-        <v>以紐約著名的圓桌文學俱樂部阿岡昆飯店命名。黑麥威士忌大膽配上新鮮鳳梨汁與干苦艾酒，酸甜乾爽，極具文人幹練。</v>
+        <v>1970年代誕生於阿拉巴馬大學校園酒吧，隨後在全美大學生與南方酒吧引爆狂歡風潮。以濃郁英倫黑刺李琴酒（Sloe Gin）、南方安逸桃子香甜酒、杏仁利口酒（Amaretto）與新鮮現榨柳橙汁混合。亮麗的艷橙紅酒液洋溢著豐富的野生莓果、水蜜桃與烤杏仁甜香，口感濃郁順滑、果香甜美，是美國南方派對的青春印記。</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>阿拉巴馬監獄  Alabama Slammer</v>
+        <v>阿拉斯加  Alaska</v>
       </c>
       <c r="B139">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C139">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D139">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E139" t="str">
-        <v>琴酒, 威士忌, 經典</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F139" t="str">
-        <v>野莓琴酒 30 ml, 杏仁香甜酒 30 ml, 南方安逸香甜酒 30 ml, 柳橙汁 60 ml, 濾掉冰塊，將酒液倒入冰鎮過的長飲杯，加入碎冰至全滿。, 檸檬片, 柳橙片, 糖漬櫻桃</v>
+        <v>琴酒 60 ml, 夏特勒茲(綠) 15 ml, 安格式柑橘苦精 1 dash, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
       </c>
       <c r="G139" t="str">
         <v/>
       </c>
       <c r="H139" t="str">
-        <v>冰鎮長飲杯</v>
+        <v>阿拉斯加，一杯就瞎</v>
       </c>
       <c r="I139" t="str">
         <v>建議物</v>
       </c>
       <c r="J139" t="str">
-        <v>1970年代風靡全美大學校園與南方酒吧的狂歡長飲，黑刺李琴酒與南方安逸桃子酒帶來濃郁的南方莓果與蜜桃甜香。</v>
+        <v>1910年代記載於Jacques Straub經典酒譜中，向冰封遼闊的美國北方大地阿拉斯加致敬。以強勁純粹的英倫乾琴酒為骨架，融入被譽為「利口酒女王」、由修道士以一百三十種阿爾卑斯草本釀製的黃夏翠絲（Yellow Chartreuse）藥草酒。金黃純淨的酒液不加任何果汁冰塊，入口冷冽冰徹、草本芬芳深邃，宛如極地冰原般神聖剛烈。</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>阿拉斯加  Alaska</v>
+        <v>阿爾諾  Arnaud</v>
       </c>
       <c r="B140">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C140">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140" t="str">
         <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F140" t="str">
-        <v>琴酒 60 ml, 夏特勒茲(綠) 15 ml, 安格式柑橘苦精 1 dash, 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 柳橙皮捲</v>
+        <v>琴酒 30 ml, 法式不甜香艾酒 30 ml, 黑醋栗香甜酒 30 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲</v>
       </c>
       <c r="G140" t="str">
         <v/>
       </c>
       <c r="H140" t="str">
-        <v>阿拉斯加，一杯就瞎</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I140" t="str">
         <v>建議物</v>
       </c>
       <c r="J140" t="str">
-        <v>黃色沙翠絲（Chartreuse）藥草酒與琴酒的純烈結合。金黃色的酒液不帶任何冰塊，宛如阿拉斯加凍土般冰冷、純粹且剛烈。</v>
+        <v>以紐奧良法國區擁有超過百年歷史的頂級法式名店阿爾諾餐廳（Arnaud's）命名。以倫敦乾琴酒的純粹草本杜松子為基石，調和法國黑醋栗利口酒（Cassis）與干苦艾酒。酒液散發著高貴迷人的紅寶石光澤，黑醋栗的幽雅深邃果香被干苦艾酒完美收束，口感乾爽高雅，散發著老紐奧良法國貴族的矜持與雍容。</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>阿爾諾  Arnaud</v>
+        <v>雙倍老爸  Papa Doble</v>
       </c>
       <c r="B141">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C141">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D141">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E141" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>蘭姆酒, 無氣泡, 經典</v>
       </c>
       <c r="F141" t="str">
-        <v>琴酒 30 ml, 法式不甜香艾酒 30 ml, 黑醋栗香甜酒 30 ml, 2. 濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲</v>
+        <v>陳年蘭姆酒 90 ml, 勒薩多黑櫻桃酒 15 ml, 檸檬汁 30 ml, 葡萄柚汁 45 ml,  檸檬片</v>
       </c>
       <c r="G141" t="str">
         <v/>
       </c>
       <c r="H141" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮古典杯</v>
       </c>
       <c r="I141" t="str">
         <v>建議物</v>
       </c>
       <c r="J141" t="str">
-        <v>以紐奧良法國區著名的阿爾諾餐廳命名。琴酒、黑醋栗利口酒與干苦艾酒的優雅比例，呈現高雅乾冽的貴族寶石紅色澤。</v>
+        <v>海明威黛綺莉在古巴「小佛羅里達」酒吧的最純粹硬漢終極版。「Papa（老爸）」是古巴哈瓦那當地人對海明威的尊稱。因海明威極度嗜酒，他不加糖漿，而是直接將正常配方的古巴白蘭姆酒份量加至「雙倍（整整四盎司！）」，僅佐以新鮮葡萄柚汁、萊姆汁與大量碎冰。酒體剛猛無匹、果酸如利刃出鞘，是大文豪專屬的無畏豪飲。</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>雙倍老爸  Papa Doble</v>
+        <v>雪莉酷伯樂  Sherry Cobbler</v>
       </c>
       <c r="B142">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C142">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D142">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E142" t="str">
-        <v>蘭姆酒, 無氣泡, 經典</v>
+        <v>其他, 無氣泡, 經典</v>
       </c>
       <c r="F142" t="str">
-        <v>陳年蘭姆酒 90 ml, 勒薩多黑櫻桃酒 15 ml, 檸檬汁 30 ml, 葡萄柚汁 45 ml,  檸檬片</v>
+        <v>雪莉酒(不甜) 60 ml, 檸檬汁 15 ml, 純糖漿 15 ml, 柳橙片 2~3 片, 鳳梨片  2~3 片, 碎冰至滿杯。</v>
       </c>
       <c r="G142" t="str">
-        <v/>
+        <v>雪克杯加入柳橙及鳳梨，搗壓出汁。</v>
       </c>
       <c r="H142" t="str">
-        <v>冰鎮古典杯</v>
+        <v>冰鎮長飲杯</v>
       </c>
       <c r="I142" t="str">
         <v>建議物</v>
       </c>
       <c r="J142" t="str">
-        <v>海明威黛綺莉（Hemingway Daiquiri）的終極硬漢版。去除了所有的糖與水分，直接倒滿「雙倍容量」的白蘭姆酒，大文豪的專屬豪飲。</v>
+        <v>19世紀中葉風靡全美與歐洲的劃時代消暑神作，曾出現在狄更斯名著中。此酒最大的歷史意義在於它普及了「碎冰」與「塑膠吸管」在全世界酒吧的誕生！將優質西班牙雪莉酒（Sherry）與少許糖漿、新鮮柳橙角與碎冰充分搖盪，飾以大量新鮮莓果。雪莉酒特有的烤堅果香氣與柑橘果酸在碎冰中極致綻放，清涼暢快、回甘悠長。</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>雪莉酷伯樂  Sherry Cobbler</v>
+        <v>霜凍瑪格莉特  Frozen Margarita</v>
       </c>
       <c r="B143">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C143">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D143">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E143" t="str">
-        <v>其他, 無氣泡, 經典</v>
+        <v>龍舌蘭, 無氣泡, 經典</v>
       </c>
       <c r="F143" t="str">
-        <v>雪莉酒(不甜) 60 ml, 檸檬汁 15 ml, 純糖漿 15 ml, 柳橙片 2~3 片, 鳳梨片  2~3 片, 碎冰至滿杯。</v>
+        <v>龍舌蘭 60 ml, 君度橙酒 15 ml, 萊姆汁 30 ml, 純糖漿 20 ml, 冰塊, 將成品倒入冰鎮過的鹽口瑪格莉特杯。, 檸檬片</v>
       </c>
       <c r="G143" t="str">
-        <v>雪克杯加入柳橙及鳳梨，搗壓出汁。</v>
+        <v/>
       </c>
       <c r="H143" t="str">
-        <v>冰鎮長飲杯</v>
+        <v>製作鹽口杯，並冰鎮。</v>
       </c>
       <c r="I143" t="str">
         <v>建議物</v>
       </c>
       <c r="J143" t="str">
-        <v>19世紀風靡全美的消暑殿堂級調酒！歷史上首款大膽使用「吸管」與「碎冰」的調酒，雪莉酒的堅果香與新鮮水果極度解渴。</v>
+        <v>1971年由達拉斯餐廳老闆Mariano Martinez受軟冰淇淋機啟發而改裝出世界第一台「冰沙調酒機」，引爆全球熱帶度假浪潮。將墨西哥龍舌蘭酒、君度橙酒與新鮮萊姆汁與細密碎冰打成如天鵝絨般綿密的雪白冰沙，杯口精心抹滿一圈海鹽。入口冰沙瞬間在舌尖融化，酸甜冰爽與微鹹海鹽直擊靈魂，夏日海灘的無敵避暑神飲。</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>霜凍瑪格莉特  Frozen Margarita</v>
+        <v>霜凍黛綺莉  Frozen Daiquiri</v>
       </c>
       <c r="B144">
         <v>15</v>
@@ -4992,202 +4989,202 @@
         <v>4</v>
       </c>
       <c r="E144" t="str">
-        <v>龍舌蘭, 無氣泡, 經典</v>
+        <v>蘭姆酒, 無氣泡, 經典</v>
       </c>
       <c r="F144" t="str">
-        <v>龍舌蘭 60 ml, 君度橙酒 15 ml, 萊姆汁 30 ml, 純糖漿 20 ml, 冰塊, 將成品倒入冰鎮過的鹽口瑪格莉特杯。, 檸檬片</v>
+        <v>白蘭姆酒 60 ml, 萊姆汁 15 ml, 純糖漿 22 ml, 冰塊, 適量, 2．將成品倒入冰鎮過的馬丁尼杯。, 檸檬片</v>
       </c>
       <c r="G144" t="str">
         <v/>
       </c>
       <c r="H144" t="str">
-        <v>製作鹽口杯，並冰鎮。</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I144" t="str">
         <v>建議物</v>
       </c>
       <c r="J144" t="str">
-        <v>當代夏日海灘的度假代名詞。將經典瑪格莉特與碎冰丟入冰沙機中高速綿密化，鹽圈與青檸冰沙帶來極致的沁涼。</v>
+        <v>大文豪海明威在古巴炎炎夏日午後最魂牽夢縈的消暑救贖。由哈瓦那傳奇調酒師Constantino Ribalaigua在小佛羅里達酒吧將古巴白蘭姆酒、新鮮青檸汁、砂糖與大量晶瑩碎冰高速打成如雪糕般細緻綿密的純白冰沙。入口細膩幼滑如絲綢，加勒比海甘蔗香與青檸清香隨冰沙在口中融化，瞬間驅散所有暑氣。</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>霜凍黛綺莉  Frozen Daiquiri</v>
+        <v>霧之刃  Fog Cutter</v>
       </c>
       <c r="B145">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C145">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E145" t="str">
-        <v>蘭姆酒, 無氣泡, 經典</v>
+        <v>蘭姆酒, 琴酒, 白蘭地, 經典</v>
       </c>
       <c r="F145" t="str">
-        <v>白蘭姆酒 60 ml, 萊姆汁 15 ml, 純糖漿 22 ml, 冰塊, 適量, 2．將成品倒入冰鎮過的馬丁尼杯。, 檸檬片</v>
+        <v>白蘭姆酒 60 ml, 白蘭地 30 ml, 琴酒 15 ml, 雪莉酒(較甜) 15 ml, 檸檬汁 60 ml, 柳橙汁 30 ml, 杏仁糖漿 15 ml, 2. 將酒液倒入冰鎮過的煙囪型雞尾酒杯，加入冰塊至九分滿。, 3. 加入雪莉酒，漂浮至上方。</v>
       </c>
       <c r="G145" t="str">
         <v/>
       </c>
       <c r="H145" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮煙囪型雞尾酒杯</v>
       </c>
       <c r="I145" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J145" t="str">
-        <v>大文豪海明威在哈瓦那炎熱午後的最愛。將白蘭姆酒、青檸與大量碎冰打成如雪糕般細緻的冰沙，是加勒比海的消暑聖品。</v>
+        <v>1940年代由Tiki熱帶調酒始祖Trader Vic（維克商人）發明的傳奇大師級調酒。大師曾留下一句幽默名言：「喝下一杯，能幫你切開眼前的濃霧；但若是喝下兩杯，你將陷入更深的迷霧之中！」。大膽融合白蘭姆酒、干邑白蘭地與琴酒三種烈酒，調和柳橙汁、檸檬汁與杏仁糖漿，最後漂浮一層雪莉酒，層次繁複洶湧。</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>霧之刃  Fog Cutter</v>
+        <v>飄仙紅茶  Pimm_s Black Tea</v>
       </c>
       <c r="B146">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C146">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D146">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E146" t="str">
-        <v>蘭姆酒, 琴酒, 白蘭地, 經典</v>
+        <v>其他, 無氣泡, 經典</v>
       </c>
       <c r="F146" t="str">
-        <v>白蘭姆酒 60 ml, 白蘭地 30 ml, 琴酒 15 ml, 雪莉酒(較甜) 15 ml, 檸檬汁 60 ml, 柳橙汁 30 ml, 杏仁糖漿 15 ml, 2. 將酒液倒入冰鎮過的煙囪型雞尾酒杯，加入冰塊至九分滿。, 3. 加入雪莉酒，漂浮至上方。</v>
+        <v>皮姆一號 50 ml, 紅茶香甜酒 20 ml, 陳年蘭姆酒 20 ml, 安格式原味苦精 2 dashes, 柳橙皮捲</v>
       </c>
       <c r="G146" t="str">
         <v/>
       </c>
       <c r="H146" t="str">
-        <v>冰鎮煙囪型雞尾酒杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I146" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J146" t="str">
-        <v>由Tiki調酒大師維克商人創作，名言是「喝三杯能幫你切開眼前的濃霧，但喝四杯會讓你陷入更深的迷霧」，混用了多種烈酒。</v>
+        <v>英倫皇家優雅莊園風情的當代品味延伸。將英國著名的皮姆一號（Pimm's No.1）柑橘草本浸泡酒，融入低溫冰鎮的頂級大吉嶺或阿薩姆純黑紅茶，佐以新鮮黃瓜條、檸檬片與薄荷葉。濃郁的麥芽紅茶茶韻，完美烘托出皮姆酒中細緻的草本香料與甜橙氣息，口感清爽回甘、茶香悠長，極具英式午後慢活格調。</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>飄仙紅茶  Pimm_s Black Tea</v>
+        <v>飛行  Aviation</v>
       </c>
       <c r="B147">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C147">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D147">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E147" t="str">
-        <v>其他, 無氣泡, 經典</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F147" t="str">
-        <v>皮姆一號 50 ml, 紅茶香甜酒 20 ml, 陳年蘭姆酒 20 ml, 安格式原味苦精 2 dashes, 柳橙皮捲</v>
+        <v>琴酒 60ml, 紫羅蘭香甜酒 15ml, 萊姆汁 15ml, 勤薩多黑櫻桃酒2tsp, 馬丁尼杯 Shake</v>
       </c>
       <c r="G147" t="str">
         <v/>
       </c>
       <c r="H147" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v/>
       </c>
       <c r="I147" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J147" t="str">
-        <v>英倫優雅風的當代延伸，將傳統皮姆一號草本酒與冰鎮優質紅茶結合，散發迷人的佛手柑茶香與莊園度假感。</v>
+        <v>1916年由紐約華爾街著名的霍斯托克飯店（Hotel Wallick）德裔調酒大師Hugo Ensslin創作。向人類剛征服藍天不久的航空探索黃金年代致敬。琴酒的杜松子芳香中，融入黑櫻桃利口酒、新鮮檸檬汁與最關鍵的神秘紫羅蘭利口酒（Crème de Violette）。酒液呈現拂曉破曉時天空那抹令人屏息的淡藍紫色，花香縹緲高雅。</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>飛行  Aviation</v>
+        <v>香檳雞尾酒  Champagne Cocktail</v>
       </c>
       <c r="B148">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C148">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D148">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E148" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>其他, 有氣泡, 經典</v>
       </c>
       <c r="F148" t="str">
-        <v>琴酒 60ml, 紫羅蘭香甜酒 15ml, 萊姆汁 15ml, 勤薩多黑櫻桃酒2tsp, 馬丁尼杯 Shake</v>
+        <v>香檳, 適量, 安格式原味苦精 1 dash, 方糖 1 顆</v>
       </c>
       <c r="G148" t="str">
-        <v/>
+        <v>加入已充分冰鎮的香檳約八分滿杯。檸檬皮捲</v>
       </c>
       <c r="H148" t="str">
-        <v/>
+        <v>杯中放入方糖，抖灑苦精。</v>
       </c>
       <c r="I148" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J148" t="str">
-        <v>20世紀初由Hugo Ensslin在紐約發明，紫羅蘭利口酒（Crème de Violette）為酒液染上一層如拂曉天空般浪漫的淡藍紫色。</v>
+        <v>記載於1862年Jerry Thomas編寫的第一本正式酒譜，曾出現在電影《北非諜影》與《大亨小傳》中。在晶瑩剔透的香檳笛杯底投入一顆吸飽安格式苦精的白方糖，注入少許白蘭地，緩緩斟滿冰鎮法國頂級香檳。苦精方糖在杯底持續釋放出如珠玉般升騰不息的綿密氣泡，入口高貴典雅、果香優雅，極具儀式感。</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>香檳雞尾酒  Champagne Cocktail</v>
+        <v>馬丁尼  Martini</v>
       </c>
       <c r="B149">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C149">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D149">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" t="str">
-        <v>其他, 有氣泡, 經典</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F149" t="str">
-        <v>香檳, 適量, 安格式原味苦精 1 dash, 方糖 1 顆</v>
+        <v>琴酒 60 ml, 法式不甜香艾酒 10 ml, 安格式柑橘苦精 1 dash, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲</v>
       </c>
       <c r="G149" t="str">
-        <v>加入已充分冰鎮的香檳約八分滿杯。檸檬皮捲</v>
+        <v/>
       </c>
       <c r="H149" t="str">
-        <v>杯中放入方糖，抖灑苦精。</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I149" t="str">
         <v>建議物</v>
       </c>
       <c r="J149" t="str">
-        <v>記載於1862年世界上第一本正式酒譜。在香檳杯底放入吸滿苦精的方糖，隨著香檳汽泡徐徐溶解，優雅、高貴且極具儀式感。</v>
+        <v>被全世界調酒界奉為神聖不容侵犯的「雞尾酒之王（The King of Cocktails）」。邱吉爾、海明威與政商文豪一生的精神圖騰。純粹精準的倫敦乾琴酒與干苦艾酒（Dry Vermouth）在冰塊中冷冽攪拌至如水晶般晶瑩透亮，滴入綠橄欖或抹上一圈檸檬皮油。酒體乾冽純粹、草本芬芳直透胸膛，演繹出極致的尊貴、冷靜與高雅。</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>馬丁尼  Martini</v>
+        <v>馬丁尼茲  Martinez</v>
       </c>
       <c r="B150">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C150">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D150">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150" t="str">
         <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F150" t="str">
-        <v>琴酒 60 ml, 法式不甜香艾酒 10 ml, 安格式柑橘苦精 1 dash, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲</v>
+        <v>琴酒 30 ml, 義式甜香艾酒 60 ml, 安格式柑橘苦精 1 dash, 勒薩多黑櫻桃酒2 dashes, 柳橙皮捲, 勒薩多糖漬櫻桃</v>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -5199,44 +5196,44 @@
         <v>建議物</v>
       </c>
       <c r="J150" t="str">
-        <v>被譽為「雞尾酒之王」。文學家、政治家們的靈感泉源，純粹的琴酒與苦艾酒結合，演繹出極致的乾冽與優雅。</v>
+        <v>誕生於1880年代，被公認為當代「馬丁尼（Martini）」的前身始祖。相傳是Jerry Thomas在舊金山西方大飯店為一位前往加州馬丁尼茲鎮的淘金客所創。採用口感微甜圓潤的老湯姆琴酒（Old Tom Gin），融入義大利紅甜苦艾酒、黑櫻桃利口酒與安格式苦精。酒液呈溫潤的琥珀紅，入口芳香醇厚、苦甜平衡，散發淘金年代的復古底蘊。</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>馬丁尼茲  Martinez</v>
+        <v>鮮乳派對酒  Milk Punch</v>
       </c>
       <c r="B151">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C151">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E151" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>威士忌, 白蘭地, 其他, 經典</v>
       </c>
       <c r="F151" t="str">
-        <v>琴酒 30 ml, 義式甜香艾酒 60 ml, 安格式柑橘苦精 1 dash, 勒薩多黑櫻桃酒2 dashes, 柳橙皮捲, 勒薩多糖漬櫻桃</v>
+        <v>波本威士忌 60 ml, 鮮奶 60 ml, 純糖漿 15 ml, 陳年蘭姆酒, 0.5 tsp, 將酒液倒入冰鎮過的可林杯，加入冰塊。, 荳蔻粉</v>
       </c>
       <c r="G151" t="str">
         <v/>
       </c>
       <c r="H151" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>冰鎮可林杯</v>
       </c>
       <c r="I151" t="str">
         <v>建議物</v>
       </c>
       <c r="J151" t="str">
-        <v>馬丁尼（Martini）的前身與始祖。1880年代使用帶甜味的老湯姆琴酒與紅苦艾酒、櫻桃酒調配，風味溫潤、苦甜且層次深邃。</v>
+        <v>歷史可深溯至17世紀英國查理二世宮廷的古老乳化名飲，連文豪狄更斯與班傑明·富蘭克林都曾私藏專屬配方。精選陳年干邑白蘭地或波本威士忌，調和濃醇鮮奶、天然糖漿與香草精，充分劇烈搖盪，頂部灑上現磨肉豆蔻粉。酒液絲滑綿密如液態天鵝絨，酒香被濃郁乳香溫柔包裹，帶來跨越數百年的溫暖慰藉。</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>鮮乳派對酒  Milk Punch</v>
+        <v>鱈魚角  Cape Cod</v>
       </c>
       <c r="B152">
         <v>12</v>
@@ -5245,30 +5242,30 @@
         <v>2</v>
       </c>
       <c r="D152">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E152" t="str">
-        <v>威士忌, 白蘭地, 其他, 經典</v>
+        <v>伏特加, 無氣泡, 經典</v>
       </c>
       <c r="F152" t="str">
-        <v>波本威士忌 60 ml, 鮮奶 60 ml, 純糖漿 15 ml, 陳年蘭姆酒, 0.5 tsp, 將酒液倒入冰鎮過的可林杯，加入冰塊。, 荳蔻粉</v>
+        <v>伏特加 40 ml, 蔓越莓汁 60 ml, 檸檬片</v>
       </c>
       <c r="G152" t="str">
-        <v/>
+        <v>放入冰塊，攪拌冰杯後將融水倒出。</v>
       </c>
       <c r="H152" t="str">
-        <v>冰鎮可林杯</v>
+        <v>可林杯</v>
       </c>
       <c r="I152" t="str">
         <v>建議物</v>
       </c>
       <c r="J152" t="str">
-        <v>歷史可追溯至17世紀英國宮廷的古老乳化傳統。白蘭地或波本威士忌與鮮奶、糖漿和肉荳蔻末混合，帶來極致絲滑的乳香。</v>
+        <v>以美國麻薩諸塞州盛產新鮮頂級蔓越莓的著名度假海灣「鱈魚角（Cape Cod）」命名。在裝滿晶亮冰塊的高球杯中，將極致純淨的伏特加與飽滿鮮紅的蔓越莓果汁相融，飾以一瓣新鮮萊姆角。紅寶石般的酒液酸甜清冽、果酸生津，伏特加的純淨讓蔓越莓果香淋漓盡致地綻放，是都會男女下班後最受歡迎的極簡果感長飲。</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>鱈魚角  Cape Cod</v>
+        <v>鳳梨可樂達  Pina colada</v>
       </c>
       <c r="B153">
         <v>12</v>
@@ -5277,30 +5274,30 @@
         <v>2</v>
       </c>
       <c r="D153">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E153" t="str">
-        <v>伏特加, 無氣泡, 經典</v>
+        <v>蘭姆酒, 其他, 經典</v>
       </c>
       <c r="F153" t="str">
-        <v>伏特加 40 ml, 蔓越莓汁 60 ml, 檸檬片</v>
+        <v>白蘭姆酒 45 ml, 椰漿 25 ml, 鳳梨汁 60 ml, 萊姆汁 15 ml, 純糖漿1tsp, 2．將酒液倒入冰鎮過的颶風杯，加入冰塊至滿杯。, 鳳梨片, 糖漬櫻桃</v>
       </c>
       <c r="G153" t="str">
-        <v>放入冰塊，攪拌冰杯後將融水倒出。</v>
+        <v/>
       </c>
       <c r="H153" t="str">
-        <v>可林杯</v>
+        <v>冰鎮颶風杯</v>
       </c>
       <c r="I153" t="str">
         <v>建議物</v>
       </c>
       <c r="J153" t="str">
-        <v>以美國麻薩諸塞州著名的蔓越莓產地鱈魚角命名。純淨的伏特加直接加入大把新鮮蔓越莓汁，酸甜乾淨，都會感十足。</v>
+        <v>1954年由波多黎各聖胡安希爾頓加勒比飯店調酒師Ramón "Monchito" Marrero歷時三個月研發調製，並被正式立法尊為「波多黎各國酒」。「Piña Colada」在西班牙語中意為「過濾的鳳梨」。加勒比白蘭姆酒融合濃郁椰漿與現榨新鮮鳳梨汁，打出濃稠泡沫。入口椰香馥郁、熱帶果香酸甜醉人，一口帶你置身加勒比海椰林沙灘。</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>鳳梨可樂達  Pina colada</v>
+        <v>鹹狗  Salty Dog</v>
       </c>
       <c r="B154">
         <v>12</v>
@@ -5309,173 +5306,173 @@
         <v>2</v>
       </c>
       <c r="D154">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E154" t="str">
-        <v>蘭姆酒, 其他, 經典</v>
+        <v>伏特加, 無氣泡, 經典</v>
       </c>
       <c r="F154" t="str">
-        <v>白蘭姆酒 45 ml, 椰漿 25 ml, 鳳梨汁 60 ml, 萊姆汁 15 ml, 純糖漿1tsp, 2．將酒液倒入冰鎮過的颶風杯，加入冰塊至滿杯。, 鳳梨片, 糖漬櫻桃</v>
+        <v>伏特加 30 ml, 葡萄柚汁 90 ml</v>
       </c>
       <c r="G154" t="str">
-        <v/>
+        <v>杯中放入冰塊，攪拌冰杯後將融水倒出。</v>
       </c>
       <c r="H154" t="str">
-        <v>冰鎮颶風杯</v>
+        <v>製作鹽口杯</v>
       </c>
       <c r="I154" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J154" t="str">
-        <v>波多黎各的國酒。椰奶、鳳梨汁與蘭姆酒的經典熱帶組合，讓人彷彿置身加勒比海的艷陽沙灘。</v>
+        <v>起源於英國海員與美國海軍橫渡大西洋時的經典調酒。「Salty Dog」在航海黑話中正是指「資深老海員」。以純淨伏特加（或乾琴酒）調和大把現榨新鮮葡萄柚汁，杯口精緻抹上一整圈細粒海鹽。入口海鹽的微鹹巧妙降伏了葡萄柚的酸澀與苦味，瞬間提煉出果汁深處的清甜甘美，回味帶有遼闊海洋的鹹鮮滋味。</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>鹹狗  Salty Dog</v>
+        <v>黑色俄羅斯  Black Russian</v>
       </c>
       <c r="B155">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C155">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D155">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E155" t="str">
         <v>伏特加, 無氣泡, 經典</v>
       </c>
       <c r="F155" t="str">
-        <v>伏特加 30 ml, 葡萄柚汁 90 ml</v>
+        <v>伏特加 60 ml, 咖啡香甜酒 20 ml</v>
       </c>
       <c r="G155" t="str">
-        <v>杯中放入冰塊，攪拌冰杯後將融水倒出。</v>
+        <v/>
       </c>
       <c r="H155" t="str">
-        <v>製作鹽口杯</v>
+        <v>美酒加咖啡，我只要喝一杯</v>
       </c>
       <c r="I155" t="str">
         <v/>
       </c>
       <c r="J155" t="str">
-        <v>英國海員的消暑良方。琴酒（或伏特加）與新鮮葡萄柚汁結合，精緻的杯口鹽圈完美勾勒出葡萄柚的甘甜，略帶海洋鹹感。</v>
+        <v>1949年由布魯塞爾大都會飯店傳奇調酒師Gustaaf Tops為當時美國駐盧森堡女大使Perle Mesta特別創作。在冷戰初期以象徵蘇聯的純淨伏特加，大膽混合墨西哥甘露（Kahlúa）咖啡利口酒，因而得名。深邃如黑曜石般的酒液在純冰中融化，咖啡豆濃郁的焦糖烘焙香與伏特加的冷冽完美交織，開啟了近代咖啡調酒的輝煌先河。</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>黑色俄羅斯  Black Russian</v>
+        <v>黛綺莉  Daiquiri</v>
       </c>
       <c r="B156">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C156">
         <v>4</v>
       </c>
       <c r="D156">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E156" t="str">
-        <v>伏特加, 無氣泡, 經典</v>
+        <v>蘭姆酒, 無氣泡, 經典</v>
       </c>
       <c r="F156" t="str">
-        <v>伏特加 60 ml, 咖啡香甜酒 20 ml</v>
+        <v>白蘭姆酒 60 ml, 萊姆汁 15 ml, 純糖漿 10 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲</v>
       </c>
       <c r="G156" t="str">
         <v/>
       </c>
       <c r="H156" t="str">
-        <v>美酒加咖啡，我只要喝一杯</v>
+        <v>冰鎮馬丁尼杯</v>
       </c>
       <c r="I156" t="str">
-        <v/>
+        <v>建議物</v>
       </c>
       <c r="J156" t="str">
-        <v>1949年由比利時調酒師為美國駐盧森堡大使特別創作。純淨伏特加與甘露咖啡香甜酒的冷冽組合，開啟了近代咖啡調酒的先河。</v>
+        <v>1898年美西戰爭期間由古巴同名鐵礦場的美國採礦工程師Jennings Cox首創，更是調酒界公認「測試調酒師平衡基本功的終極試金石」。古巴白蘭姆酒、新鮮現榨青檸汁與純白砂糖的黃金鐵三角，透過劇烈搖盪在冰塊中達成極致平衡。酒液清亮透明，入口酸甜明快、甘蔗果香純粹，是加勒比海最偉大的經典傳奇。</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>黛綺莉  Daiquiri</v>
+        <v>龍舌蘭日出  Tequila Sunrise</v>
       </c>
       <c r="B157">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C157">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D157">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E157" t="str">
-        <v>蘭姆酒, 無氣泡, 經典</v>
+        <v>龍舌蘭, 無氣泡, 經典</v>
       </c>
       <c r="F157" t="str">
-        <v>白蘭姆酒 60 ml, 萊姆汁 15 ml, 純糖漿 10 ml, 2．濾掉冰塊，將酒液倒入冰鎮過的馬丁尼杯。, 檸檬皮捲</v>
+        <v>龍舌蘭 40 ml, 柳橙汁 120 ml, 紅石榴糖漿, 適量</v>
       </c>
       <c r="G157" t="str">
-        <v/>
+        <v>放入冰塊，攪拌冰杯後將融水倒出。。倒入龍舌蘭及柳橙汁，攪拌均勻。。緩緩倒入紅石榴糖漿沉底。。檸檬皮捲</v>
       </c>
       <c r="H157" t="str">
-        <v>冰鎮馬丁尼杯</v>
+        <v>可林杯</v>
       </c>
       <c r="I157" t="str">
         <v>建議物</v>
       </c>
       <c r="J157" t="str">
-        <v>誕生於古巴同名礦場。古巴白蘭姆酒、新鮮砂糖與青檸汁的黃金鐵三角，是所有調酒師用來測試蘭姆酒平衡度的終極基本功。</v>
+        <v>1970年代初由加州索薩利托三叉戟酒吧調酒師Bobby Lozoff與Billy Rice創作，後因傳奇搖滾樂團「滾石樂隊（The Rolling Stones）」主唱米克·傑格在1972年巡演上的狂熱追捧而名揚世界。龍舌蘭酒與新鮮柳橙汁中注入濃稠紅石榴糖漿，糖漿徐徐沉底，在杯中渲染出如同墨西哥荒漠日出般絢爛壯麗的漸層朝霞。</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>龍舌蘭日出  Tequila Sunrise</v>
+        <v>京沖抹茶啤酒  Matcha Beer</v>
       </c>
       <c r="B158">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C158">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D158">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E158" t="str">
-        <v>龍舌蘭, 無氣泡, 經典</v>
+        <v>其他, 有氣泡</v>
       </c>
       <c r="F158" t="str">
-        <v>龍舌蘭 40 ml, 柳橙汁 120 ml, 紅石榴糖漿, 適量</v>
+        <v>冷泡抹茶30ml, 啤酒 200ml</v>
       </c>
       <c r="G158" t="str">
-        <v>放入冰塊，攪拌冰杯後將融水倒出。。倒入龍舌蘭及柳橙汁，攪拌均勻。。緩緩倒入紅石榴糖漿沉底。。檸檬皮捲</v>
+        <v/>
       </c>
       <c r="H158" t="str">
-        <v>可林杯</v>
+        <v/>
       </c>
       <c r="I158" t="str">
-        <v>建議物</v>
+        <v/>
       </c>
       <c r="J158" t="str">
-        <v>因傳奇搖滾樂團「滾石樂隊」在1972年巡迴演唱會上的狂熱追捧而紅遍全球。紅石榴糖漿在龍舌蘭與柳橙汁中下沉，渲染出絕美的墨西哥日出。</v>
+        <v>京都當代茶道與精釀啤酒工藝撞擊出的驚艷和風跨界之作！精選宇治或靜岡頂級手作抹茶粉，以茶筅現場現刷出細膩翠綠的抹茶茶湯，徐徐注入冰鎮的高品質精釀拉格或白啤酒中。翠綠微苦的抹茶清香與啤酒花麥芽甜味在泡沫中奇蹟交融，入口先是微苦回甘的深邃茶韻，隨後迎來麥芽氣泡的暢快，回味無窮。</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>京沖抹茶啤酒  Matcha Beer</v>
+        <v>獻給神的綠茶</v>
       </c>
       <c r="B159">
         <v>15</v>
       </c>
       <c r="C159">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D159">
         <v>1</v>
       </c>
       <c r="E159" t="str">
-        <v>其他, 有氣泡</v>
+        <v>其他, 無氣泡</v>
       </c>
       <c r="F159" t="str">
-        <v>冷泡抹茶30ml, 啤酒 200ml</v>
+        <v>班尼迪克丁 45ml, 綠茶 120ml</v>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -5487,15 +5484,15 @@
         <v/>
       </c>
       <c r="J159" t="str">
-        <v>極具京都和風創意的當代融合！將現刷的宇治靜岡抹茶細緻液體徐徐注入冰鎮精釀啤酒中，茶香的微苦與麥芽甜味完美撞擊。</v>
+        <v>帶有東方神道與禪宗靜謐意象的茶系秘調。精選台灣高山清香高冷綠茶低溫慢萃，融入帶有杜松子與植物草本芬芳的頂級乾琴酒，佐以少許桂花蜜糖與接骨木花香。酒液澄澈如清泉，入口茶香高雅幽遠、草本甘美，宛如清晨山林神社前獻給神明的甘露祭禮，能瞬間撫平心靈所有浮躁與塵囂。</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>獻給神的綠茶</v>
+        <v>玫莓冰茶  Rose Berry Icetea</v>
       </c>
       <c r="B160">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C160">
         <v>3</v>
@@ -5504,10 +5501,10 @@
         <v>1</v>
       </c>
       <c r="E160" t="str">
-        <v>其他, 無氣泡</v>
+        <v>白蘭地, 有氣泡</v>
       </c>
       <c r="F160" t="str">
-        <v>班尼迪克丁 45ml, 綠茶 120ml</v>
+        <v>白蘭地 45ml, 玻瑰檸檬碳酸飲</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -5519,15 +5516,15 @@
         <v/>
       </c>
       <c r="J160" t="str">
-        <v>帶有神秘東方禪意的茶系條酒，將優雅的綠茶茶韻與草本基酒完美交融，風味乾淨、清幽，宛如獻給神明的清晨祭禮。</v>
+        <v>專為追求優雅浪漫情調的都會靈魂量身調配的沙龍花果茶調酒。以大馬士革玫瑰蒸餾花露、綜合野莓果泥與頂級阿薩姆冰紅茶為基底，佐以純淨伏特加與少許檸檬汁。杯中玫瑰花瓣輕舞，入口迎來馥郁深情的玫瑰芬芳與酸甜多汁的綜合莓果香氣，茶感解膩柔順，散發著英法午後莊園般無盡的優雅與浪漫。</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>玫莓冰茶  Rose Berry Icetea</v>
+        <v>琥珀冰茶  Amber Iced Tea</v>
       </c>
       <c r="B161">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C161">
         <v>3</v>
@@ -5536,10 +5533,10 @@
         <v>1</v>
       </c>
       <c r="E161" t="str">
-        <v>白蘭地, 有氣泡</v>
+        <v>威士忌, 無氣泡</v>
       </c>
       <c r="F161" t="str">
-        <v>白蘭地 45ml, 玻瑰檸檬碳酸飲</v>
+        <v>紅茶香甜酒 45ml, 蜜多麗 15ml , 日本威士忌25ml</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -5551,27 +5548,27 @@
         <v/>
       </c>
       <c r="J161" t="str">
-        <v>專為女性設計的花果茶系輕微醺。優雅的玫瑰花瓣香氣、綜合酸甜莓果與頂級紅茶底結合，散發滿滿的午後莊園浪漫。</v>
+        <v>獻給成熟靈魂的深度烘焙茶感調酒。以台灣炭焙重發酵凍頂烏龍茶或正山小種紅茶為靈魂，低溫浸漬萃取波本威士忌特有的香草橡木桶木質香，調和少許天然蜂蜜與橙皮香。酒液在光線下呈現通透深邃的金黃琥珀色澤，入口茶韻濃郁厚實、木質煙燻回甘悠長，在微醺中品味歲月沉澱後的沉穩從容。</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>琥珀冰茶  Amber Iced Tea</v>
+        <v>皮斯可樂 Piscola</v>
       </c>
       <c r="B162">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C162">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D162">
         <v>1</v>
       </c>
       <c r="E162" t="str">
-        <v>威士忌, 無氣泡</v>
+        <v>皮斯可, 有氣泡, 經典</v>
       </c>
       <c r="F162" t="str">
-        <v>紅茶香甜酒 45ml, 蜜多麗 15ml , 日本威士忌25ml</v>
+        <v>皮斯可 45ml, 可口可樂 120ml</v>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -5583,27 +5580,27 @@
         <v/>
       </c>
       <c r="J162" t="str">
-        <v>成熟風味的重茶感調酒，利用深度烘焙的烏龍茶或紅茶，帶出金黃如琥珀般的通透酒液，木質煙燻與茶感尾韻悠長。</v>
+        <v>南美洲智利的國家級國民派對狂歡長飲，智利甚至立法將每年的2月8日定為「全國皮斯可樂日（Día de la Piscola）」！將產自智利安地斯山麓的皮斯可（Pisco）葡萄蒸餾白蘭地倒入裝滿冰塊的大球杯中，填滿冰涼的可口可樂與新鮮青檸角。葡萄果香與可樂焦糖氣泡熱烈碰撞，是南美洲青年派對徹夜狂歡的靈魂燃料。</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>皮斯可樂 Piscola</v>
+        <v>纜車  Cable Car</v>
       </c>
       <c r="B163">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C163">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E163" t="str">
-        <v>皮斯可, 有氣泡, 經典</v>
+        <v>蘭姆酒, 無氣泡, 經典</v>
       </c>
       <c r="F163" t="str">
-        <v>皮斯可 45ml, 可口可樂 120ml</v>
+        <v>香料蘭姆酒 45ml, 檸檬汁 30ml, 糖漿 15ml</v>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -5615,27 +5612,27 @@
         <v/>
       </c>
       <c r="J163" t="str">
-        <v>南美洲智利最普及的國民級瘋狂長飲！皮斯可（Pisco）葡萄白蘭地直接填滿冰鎮可樂與萊姆，是當地派對不可或缺的微醺燃料。</v>
+        <v>1996年由雞尾酒復興巨匠Tony Abou-Ganim在舊金山傳奇天際線「星光酒吧（Starlight Room）」創作。向舊金山街道上行駛超過百年的歷史遺產「叮叮纜車」致敬。將經典側車（Sidecar）中的白蘭地創新替換為摩根船長香料蘭姆酒，杯口滾上肉桂糖粉圈。辛香肉桂糖粉與蘭姆酒的香草香甜完美呼應，溫暖宜人。</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>纜車  Cable Car</v>
+        <v>荔枝烏龍  Lychee Oolong Tea</v>
       </c>
       <c r="B164">
         <v>15</v>
       </c>
       <c r="C164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D164">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E164" t="str">
-        <v>蘭姆酒, 無氣泡, 經典</v>
+        <v>其他, 無氣泡</v>
       </c>
       <c r="F164" t="str">
-        <v>香料蘭姆酒 45ml, 檸檬汁 30ml, 糖漿 15ml</v>
+        <v>荔枝香甜酒 45ml, 烏龍茶 120ml</v>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -5647,27 +5644,27 @@
         <v/>
       </c>
       <c r="J164" t="str">
-        <v>1996年由調酒大師Tony Abou-Ganim在舊金山星光酒吧創作，向當地的叮叮車致敬。用摩根船長香料蘭姆酒取代白蘭地調製側車，溫暖辛香。</v>
+        <v>風靡亞洲極簡酒吧與當代居酒屋的當紅茶果調酒。以台灣炭焙重烘焙烏龍茶的厚實茶韻為骨架，融入飽滿多汁、甜美如蜜的頂級荔枝利口酒與純淨伏特加。荔枝甜美的熱帶果香，被烏龍茶深沉的烘焙焙火香氣完美包覆，入口甜美多汁、入喉生津回甘，甜而不膩，是佐餐與放鬆小酌的最佳良伴。</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>荔枝烏龍  Lychee Oolong Tea</v>
+        <v>費茲傑羅  Fitzgerald</v>
       </c>
       <c r="B165">
         <v>15</v>
       </c>
       <c r="C165">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E165" t="str">
-        <v>其他, 無氣泡</v>
+        <v>琴酒, 無氣泡, 經典</v>
       </c>
       <c r="F165" t="str">
-        <v>荔枝香甜酒 45ml, 烏龍茶 120ml</v>
+        <v>琴酒 50ml, 檸檬汁25ml, 糖漿15ml, 安格式原味苦精 2dash</v>
       </c>
       <c r="G165" t="str">
         <v/>
@@ -5679,27 +5676,27 @@
         <v/>
       </c>
       <c r="J165" t="str">
-        <v>風靡亞洲當代居酒屋與極簡酒吧的必喝茶調酒。甜美飽滿的荔枝果香，被台灣重烘焙烏龍茶的炭焙香氣完美包覆，回甘解膩。</v>
+        <v>1990年代由「現代雞尾酒教父」Dale DeGroff在紐約著名的彩虹酒吧（Rainbow Room）創作，以《大亨小傳》名作家史考特·費茲傑羅命名。在傳統琴酒酸酒（Gin Sour）的純粹架構中，大膽滴入大量安格式苦精。杜松子草本在酸甜中多了苦精繁複的香料沉澱，幹練深沉，宛如重返1920年代紙醉金迷的爵士爵士名流盛宴。</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>費茲傑羅  Fitzgerald</v>
+        <v>來一杯shot</v>
       </c>
       <c r="B166">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C166">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D166">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E166" t="str">
-        <v>琴酒, 無氣泡, 經典</v>
+        <v>其他</v>
       </c>
       <c r="F166" t="str">
-        <v>琴酒 50ml, 檸檬汁25ml, 糖漿15ml, 安格式原味苦精 2dash</v>
+        <v>隨意調隨意尻。杯型：Shot杯</v>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -5711,12 +5708,76 @@
         <v/>
       </c>
       <c r="J166" t="str">
-        <v>由雞尾酒復興教父Dale DeGroff於紐約紐約創製，以《大亨小傳》作者命名。琴酒酸酒（Gin Sour）中滴入大量安格式苦精，幹練且充滿爵士時代風情。</v>
+        <v>吧台今夜專屬的狂歡驚喜盲盒！沒有一成不變的教條公式，只有調酒師根據你當下的眼神、心情與派對氛圍量身打造的即興靈魂之作。或許是草本野烈的烈酒撞擊，或許是酸甜爆發的水果炸彈，一飲而盡的瞬間，讓所有的疲憊與防備隨喉頭的微醺火焰化為烏有，舉杯向今夜不可複製的狂歡致敬！</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>水色維爾瓦  Aqua Velva</v>
+      </c>
+      <c r="B167">
+        <v>16</v>
+      </c>
+      <c r="C167">
+        <v>2</v>
+      </c>
+      <c r="D167">
+        <v>3</v>
+      </c>
+      <c r="E167" t="str">
+        <v>琴酒, 伏特加, 有氣泡, 酸甜, 長飲, 經典</v>
+      </c>
+      <c r="F167" t="str">
+        <v>伏特加 35 ml, 琴酒 35 ml, 藍柑橘香甜酒 20 ml, 雪碧 適量</v>
+      </c>
+      <c r="G167" t="str">
+        <v>搖盪法 (Shake)</v>
+      </c>
+      <c r="H167" t="str">
+        <v>古巴颶風杯 (Hurricane Glass)</v>
+      </c>
+      <c r="I167" t="str">
+        <v>糖漬櫻桃、新鮮柳橙半月片、小雨傘</v>
+      </c>
+      <c r="J167" t="str">
+        <v>靈感源自1917年著名男性鬍後水「Aqua Velva」經典的冰藍色澤。在2007年大衛芬奇名導電影《索命黃道帶》（Zodiac）中，由傑克葛倫霍飾演的主角頻繁點用而風靡影壇。外表如碧藍海洋般純粹透亮，散發柑橘甜香與沁涼氣泡，巧妙包覆伏特加與琴酒的紮實雙烈酒骨架，是一杯外表清爽無害、後勁卻深邃迷人的傳奇高球！</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>淘金熱  Gold Rush</v>
+      </c>
+      <c r="B168">
+        <v>28</v>
+      </c>
+      <c r="C168">
+        <v>4</v>
+      </c>
+      <c r="D168">
+        <v>3</v>
+      </c>
+      <c r="E168" t="str">
+        <v>威士忌, 無氣泡, 酸甜, 經典</v>
+      </c>
+      <c r="F168" t="str">
+        <v>波本威士忌 60 ml, 現榨檸檬汁 25 ml, 蜂蜜 25 ml</v>
+      </c>
+      <c r="G168" t="str">
+        <v>搖盪法 (Shake)</v>
+      </c>
+      <c r="H168" t="str">
+        <v>古典杯 (Old Fashioned Glass)</v>
+      </c>
+      <c r="I168" t="str">
+        <v>檸檬皮捲</v>
+      </c>
+      <c r="J168" t="str">
+        <v>由紐約傳奇酒吧 Milk &amp; Honey 的調酒師 T.J. Siegal 於 2001 年創作。本質上是威士忌酸酒（Whiskey Sour）的現代經典變奏，巧妙將傳統糖漿替換為濃郁溫潤的優質蜂蜜，搭配強勁厚實的波本威士忌與新鮮檸檬汁。琥珀金黃的酒液宛如淘金熱時代璀璨耀眼的希望，口感絲滑酸甜、圓潤飽滿。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J166"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J168"/>
   </ignoredErrors>
 </worksheet>
 </file>